--- a/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDDB491-F090-42F4-8E34-BB21369B9C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F315056-74B9-4FD9-A47F-3DFD3BFCFF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,43 +356,43 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.67015864678428949</c:v>
+                  <c:v>0.17624938992497577</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.67399433743759052</c:v>
+                  <c:v>0.82691997712063736</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.67258163487423628</c:v>
+                  <c:v>0.53604618365050316</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.69883311557825745</c:v>
+                  <c:v>0.67249847128047058</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.73244907600666376</c:v>
+                  <c:v>0.61540498338945215</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.76691398093902452</c:v>
+                  <c:v>0.680803562830266</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.79412199858198884</c:v>
+                  <c:v>0.77246629253567023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.82771654679092965</c:v>
+                  <c:v>0.72867315835336177</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.87277793951821403</c:v>
+                  <c:v>0.8200846093262375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.90774216971761523</c:v>
+                  <c:v>0.84652881228569787</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.96885985849430767</c:v>
+                  <c:v>0.94926751684278332</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0035052756769365</c:v>
+                  <c:v>0.91067388980847419</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0159556160581653</c:v>
+                  <c:v>0.897241060657194</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -880,43 +880,43 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0001629351709587</c:v>
+                  <c:v>1.0119378821291016</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0000650261216626</c:v>
+                  <c:v>1.0179707921448478</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99996036360746876</c:v>
+                  <c:v>1.027861427431511</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0005266084564297</c:v>
+                  <c:v>0.98075710537859517</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0018467149465879</c:v>
+                  <c:v>0.97199820729613373</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.002287048308576</c:v>
+                  <c:v>1.0175104699823445</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0038025582102672</c:v>
+                  <c:v>1.0048750533338346</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0036838050286592</c:v>
+                  <c:v>0.9979952120781076</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.002467577491776</c:v>
+                  <c:v>1.011050091074648</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.000596548769378</c:v>
+                  <c:v>1.0131574726669086</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0015290596941282</c:v>
+                  <c:v>1.0184379609619567</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0029865814925498</c:v>
+                  <c:v>0.9965086561044354</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0003513071302839</c:v>
+                  <c:v>0.97509536567142829</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2982,43 +2982,43 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.67015864678428949</c:v>
+                  <c:v>0.17624938992497577</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.67399433743759052</c:v>
+                  <c:v>0.82691997712063736</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.67258163487423628</c:v>
+                  <c:v>0.53604618365050316</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.69883311557825745</c:v>
+                  <c:v>0.67249847128047058</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.73244907600666376</c:v>
+                  <c:v>0.61540498338945215</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.76691398093902452</c:v>
+                  <c:v>0.680803562830266</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.79412199858198884</c:v>
+                  <c:v>0.77246629253567023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.82771654679092965</c:v>
+                  <c:v>0.72867315835336177</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.87277793951821403</c:v>
+                  <c:v>0.8200846093262375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.90774216971761523</c:v>
+                  <c:v>0.84652881228569787</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.96885985849430767</c:v>
+                  <c:v>0.94926751684278332</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0035052756769365</c:v>
+                  <c:v>0.91067388980847419</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0159556160581653</c:v>
+                  <c:v>0.897241060657194</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7312,24 +7312,24 @@
       </c>
       <c r="B5" s="4"/>
       <c r="D5">
-        <v>1.3891095589010301</v>
+        <v>1.3681371012949699</v>
       </c>
       <c r="E5">
-        <v>1.02494314460544E-4</v>
+        <v>1.1475260729751101E-2</v>
       </c>
       <c r="F5">
-        <v>1.38933589370449</v>
+        <v>1.38446976074668</v>
       </c>
       <c r="G5">
-        <v>1.1377551521665301E-4</v>
+        <v>1.12587768842507E-2</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" ref="H5:H17" si="0">F5/D5</f>
-        <v>1.0001629351709587</v>
+        <v>1.0119378821291016</v>
       </c>
       <c r="I5">
         <f>H5*((E5/D5)^2 +(G5/F5)^2)^0.5</f>
-        <v>1.1024684824037706E-4</v>
+        <v>1.182205369797695E-2</v>
       </c>
       <c r="J5" s="3"/>
       <c r="L5">
@@ -7359,24 +7359,24 @@
       </c>
       <c r="B6" s="4"/>
       <c r="D6">
-        <v>1.38907673010083</v>
+        <v>1.36116575463441</v>
       </c>
       <c r="E6">
-        <v>1.52707495750366E-4</v>
+        <v>1.1125190871760801E-2</v>
       </c>
       <c r="F6">
-        <v>1.3891670563732801</v>
+        <v>1.3856269814856299</v>
       </c>
       <c r="G6">
-        <v>1.6878154642812701E-4</v>
+        <v>1.0321337384108399E-2</v>
       </c>
       <c r="H6" s="7">
         <f t="shared" si="0"/>
-        <v>1.0000650261216626</v>
+        <v>1.0179707921448478</v>
       </c>
       <c r="I6">
         <f t="shared" ref="I6:I16" si="2">H6*((E6/D6)^2 +(G6/F6)^2)^0.5</f>
-        <v>1.6386259048946993E-4</v>
+        <v>1.1257118632435607E-2</v>
       </c>
       <c r="J6" s="3"/>
       <c r="L6">
@@ -7406,24 +7406,24 @@
       </c>
       <c r="B7" s="4"/>
       <c r="D7">
-        <v>1.3889139640202901</v>
+        <v>1.3663565821363799</v>
       </c>
       <c r="E7">
-        <v>1.8201886596701201E-4</v>
+        <v>1.6432050614063699E-2</v>
       </c>
       <c r="F7">
-        <v>1.3888589124812201</v>
+        <v>1.40442522689514</v>
       </c>
       <c r="G7">
-        <v>1.54337152453701E-4</v>
+        <v>1.3826122129943601E-2</v>
       </c>
       <c r="H7" s="7">
         <f t="shared" si="0"/>
-        <v>0.99996036360746876</v>
+        <v>1.027861427431511</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>1.7181641313147609E-4</v>
+        <v>1.5974792343773782E-2</v>
       </c>
       <c r="J7" s="3"/>
       <c r="L7">
@@ -7453,24 +7453,24 @@
       </c>
       <c r="B8" s="4"/>
       <c r="D8">
-        <v>1.38607567014507</v>
+        <v>1.39704864054061</v>
       </c>
       <c r="E8">
-        <v>3.8958612319318502E-4</v>
+        <v>1.23281362355317E-2</v>
       </c>
       <c r="F8">
-        <v>1.3868055893142199</v>
+        <v>1.3701653807697101</v>
       </c>
       <c r="G8">
-        <v>4.0944327607914799E-4</v>
+        <v>1.18088772589459E-2</v>
       </c>
       <c r="H8" s="7">
         <f t="shared" si="0"/>
-        <v>1.0005266084564297</v>
+        <v>0.98075710537859517</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>4.0785290749755253E-4</v>
+        <v>1.2097557519592871E-2</v>
       </c>
       <c r="J8" s="3"/>
       <c r="L8">
@@ -7501,24 +7501,24 @@
       <c r="B9" s="4"/>
       <c r="C9"/>
       <c r="D9">
-        <v>1.37947186689904</v>
+        <v>1.39382815633733</v>
       </c>
       <c r="E9">
-        <v>8.86091661857925E-4</v>
+        <v>1.27595827530817E-2</v>
       </c>
       <c r="F9">
-        <v>1.3820193582140401</v>
+        <v>1.35479846923876</v>
       </c>
       <c r="G9">
-        <v>1.17898543365087E-3</v>
+        <v>1.49502540503268E-2</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
-        <v>1.0018467149465879</v>
+        <v>0.97199820729613373</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>1.0698498708561776E-3</v>
+        <v>1.3936370030626408E-2</v>
       </c>
       <c r="K9"/>
       <c r="L9">
@@ -7548,24 +7548,24 @@
       </c>
       <c r="B10" s="4"/>
       <c r="D10">
-        <v>1.37231900559378</v>
+        <v>1.36790794333796</v>
       </c>
       <c r="E10">
-        <v>9.8135892237590492E-4</v>
+        <v>1.2545386712593301E-2</v>
       </c>
       <c r="F10">
-        <v>1.3754575654543499</v>
+        <v>1.39186065431839</v>
       </c>
       <c r="G10">
-        <v>7.1929329253824501E-4</v>
+        <v>1.3451922716281201E-2</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="0"/>
-        <v>1.002287048308576</v>
+        <v>1.0175104699823445</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>8.8794780325578441E-4</v>
+        <v>1.3556883805699941E-2</v>
       </c>
       <c r="J10" s="3"/>
       <c r="L10">
@@ -7596,24 +7596,24 @@
       <c r="B11" s="4"/>
       <c r="C11"/>
       <c r="D11">
-        <v>1.3652125452841399</v>
+        <v>1.35845231954227</v>
       </c>
       <c r="E11">
-        <v>9.36891207849102E-4</v>
+        <v>1.5737099383174798E-2</v>
       </c>
       <c r="F11">
-        <v>1.37040384545697</v>
+        <v>1.3650748470515099</v>
       </c>
       <c r="G11">
-        <v>1.1043763633645899E-3</v>
+        <v>1.2589958922203499E-2</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="0"/>
-        <v>1.0038025582102672</v>
+        <v>1.0048750533338346</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>1.0625098571799413E-3</v>
+        <v>1.4879770666968438E-2</v>
       </c>
       <c r="K11"/>
       <c r="L11">
@@ -7643,24 +7643,24 @@
       </c>
       <c r="B12" s="4"/>
       <c r="D12">
-        <v>1.35996558693921</v>
+        <v>1.3545568399108701</v>
       </c>
       <c r="E12">
-        <v>8.2269713778889005E-4</v>
+        <v>1.6297468246439701E-2</v>
       </c>
       <c r="F12">
-        <v>1.3649754350071801</v>
+        <v>1.3518412407186999</v>
       </c>
       <c r="G12">
-        <v>1.0934621564654399E-3</v>
+        <v>1.40724264166723E-2</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="0"/>
-        <v>1.0036838050286592</v>
+        <v>0.9979952120781076</v>
       </c>
       <c r="I12">
         <f t="shared" si="2"/>
-        <v>1.0075356465859516E-3</v>
+        <v>1.5877958663557092E-2</v>
       </c>
       <c r="J12" s="3"/>
       <c r="L12">
@@ -7690,24 +7690,24 @@
       </c>
       <c r="B13" s="4"/>
       <c r="D13">
-        <v>1.3471169036955299</v>
+        <v>1.34755153312925</v>
       </c>
       <c r="E13">
-        <v>3.4192473007070602E-3</v>
+        <v>1.50714507765111E-2</v>
       </c>
       <c r="F13">
-        <v>1.35044101904588</v>
+        <v>1.36244210029811</v>
       </c>
       <c r="G13">
-        <v>3.6209913911154899E-3</v>
+        <v>1.27279533228061E-2</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="0"/>
-        <v>1.002467577491776</v>
+        <v>1.011050091074648</v>
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
-        <v>3.7012678767904027E-3</v>
+        <v>1.4733684895401899E-2</v>
       </c>
       <c r="J13" s="3"/>
       <c r="L13">
@@ -7738,24 +7738,24 @@
       <c r="B14" s="4"/>
       <c r="C14"/>
       <c r="D14">
-        <v>1.3301704109246899</v>
+        <v>1.31707186586173</v>
       </c>
       <c r="E14">
-        <v>2.6701333301032298E-3</v>
+        <v>1.8033196660722998E-2</v>
       </c>
       <c r="F14">
-        <v>1.3309639224463901</v>
+        <v>1.3344012029371599</v>
       </c>
       <c r="G14">
-        <v>2.6466416072152398E-3</v>
+        <v>1.0229483755041201E-2</v>
       </c>
       <c r="H14" s="7">
         <f t="shared" si="0"/>
-        <v>1.000596548769378</v>
+        <v>1.0131574726669086</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>2.8272285541985462E-3</v>
+        <v>1.5898337852427311E-2</v>
       </c>
       <c r="K14"/>
       <c r="L14">
@@ -7785,24 +7785,24 @@
       </c>
       <c r="B15" s="4"/>
       <c r="D15">
-        <v>1.2881810524951001</v>
+        <v>1.28457233028475</v>
       </c>
       <c r="E15">
-        <v>2.82817615567389E-3</v>
+        <v>1.0625495333578599E-2</v>
       </c>
       <c r="F15">
-        <v>1.2901507582212099</v>
+        <v>1.3082572247633499</v>
       </c>
       <c r="G15">
-        <v>3.6382982434454399E-3</v>
+        <v>1.23666556549391E-2</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="0"/>
-        <v>1.0015290596941282</v>
+        <v>1.0184379609619567</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
-        <v>3.579377630249193E-3</v>
+        <v>1.2792431657530358E-2</v>
       </c>
       <c r="J15" s="3"/>
       <c r="L15">
@@ -7833,24 +7833,24 @@
       <c r="B16" s="4"/>
       <c r="C16"/>
       <c r="D16">
-        <v>1.24999214529804</v>
+        <v>1.2590558964513201</v>
       </c>
       <c r="E16">
-        <v>2.36320017159778E-3</v>
+        <v>1.6651460486491101E-2</v>
       </c>
       <c r="F16">
-        <v>1.2537253487050199</v>
+        <v>1.2546600993330701</v>
       </c>
       <c r="G16">
-        <v>3.5797440463882701E-3</v>
+        <v>1.314485012796E-2</v>
       </c>
       <c r="H16" s="7">
         <f t="shared" si="0"/>
-        <v>1.0029865814925498</v>
+        <v>0.9965086561044354</v>
       </c>
       <c r="I16">
         <f t="shared" si="2"/>
-        <v>3.4346863492251559E-3</v>
+        <v>1.6813371889030006E-2</v>
       </c>
       <c r="K16"/>
       <c r="L16">
@@ -7880,24 +7880,24 @@
       </c>
       <c r="B17" s="4"/>
       <c r="D17">
-        <v>1.2159170927577201</v>
+        <v>1.22750944273163</v>
       </c>
       <c r="E17">
-        <v>3.1109769949112399E-3</v>
+        <v>1.30680187336338E-2</v>
       </c>
       <c r="F17">
-        <v>1.2163442531022399</v>
+        <v>1.19693876892553</v>
       </c>
       <c r="G17">
-        <v>3.18424238805618E-3</v>
+        <v>1.11150087961693E-2</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="0"/>
-        <v>1.0003513071302839</v>
+        <v>0.97509536567142829</v>
       </c>
       <c r="I17">
         <f>H17*((E17/D17)^2 +(G17/F17)^2)^0.5</f>
-        <v>3.6618101886275135E-3</v>
+        <v>1.377509712299383E-2</v>
       </c>
       <c r="J17" s="3"/>
       <c r="L17">
@@ -8012,24 +8012,24 @@
       <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2">
-        <v>3.4601339198647797E-5</v>
+        <v>3.3571202768168298E-5</v>
       </c>
       <c r="E24" s="2">
-        <v>1.22883732368375E-8</v>
+        <v>9.9159126214562193E-7</v>
       </c>
       <c r="F24" s="2">
-        <v>2.3188386654289999E-5</v>
+        <v>5.9169040069373203E-6</v>
       </c>
       <c r="G24" s="2">
-        <v>2.5713213345718999E-7</v>
+        <v>1.2392053149366401E-6</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" ref="H24:H36" si="4">F24/D24</f>
-        <v>0.67015864678428949</v>
+        <v>0.17624938992497577</v>
       </c>
       <c r="I24">
         <f>H24*((E24/D24)^2 +(G24/F24)^2)^0.5</f>
-        <v>7.4350871718769813E-3</v>
+        <v>3.7278036250492967E-2</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="2"/>
@@ -8059,25 +8059,25 @@
         <v>0.5</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="D25">
-        <v>1.7267075850167999E-4</v>
+      <c r="D25" s="2">
+        <v>1.67215009194801E-4</v>
       </c>
       <c r="E25" s="2">
-        <v>7.3730405114227898E-8</v>
-      </c>
-      <c r="F25">
-        <v>1.16379113471186E-4</v>
+        <v>6.3599673665714699E-6</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1.3827343157759201E-4</v>
       </c>
       <c r="G25" s="2">
-        <v>4.9685826902563597E-7</v>
+        <v>3.1803156900076102E-5</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="4"/>
-        <v>0.67399433743759052</v>
+        <v>0.82691997712063736</v>
       </c>
       <c r="I25">
         <f t="shared" ref="I25:I35" si="6">H25*((E25/D25)^2 +(G25/F25)^2)^0.5</f>
-        <v>2.8918456475792078E-3</v>
+        <v>0.19277618205248812</v>
       </c>
       <c r="J25" s="3"/>
       <c r="L25">
@@ -8106,25 +8106,25 @@
         <v>1</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="D26">
-        <v>3.4444202449192702E-4</v>
+      <c r="D26" s="2">
+        <v>3.4693843594753001E-4</v>
       </c>
       <c r="E26" s="2">
-        <v>1.02701859340892E-7</v>
-      </c>
-      <c r="F26">
-        <v>2.31665379952172E-4</v>
+        <v>8.7539530299504897E-6</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1.85975024551348E-4</v>
       </c>
       <c r="G26" s="2">
-        <v>6.9232886194979901E-7</v>
+        <v>3.83737519740559E-5</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0.67258163487423628</v>
+        <v>0.53604618365050316</v>
       </c>
       <c r="I26">
         <f t="shared" si="6"/>
-        <v>2.0199806972425911E-3</v>
+        <v>0.11143071864844456</v>
       </c>
       <c r="J26" s="3"/>
       <c r="L26">
@@ -8153,25 +8153,25 @@
         <v>10</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="D27">
-        <v>3.33054467027722E-3</v>
+      <c r="D27" s="2">
+        <v>3.2447100360010698E-3</v>
       </c>
       <c r="E27" s="2">
-        <v>3.1023196230951202E-6</v>
-      </c>
-      <c r="F27">
-        <v>2.3274949085023899E-3</v>
+        <v>9.6341313668401696E-5</v>
+      </c>
+      <c r="F27" s="2">
+        <v>2.1820625389591202E-3</v>
       </c>
       <c r="G27" s="2">
-        <v>7.3576810457546899E-6</v>
+        <v>2.65966276223607E-4</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="4"/>
-        <v>0.69883311557825745</v>
+        <v>0.67249847128047058</v>
       </c>
       <c r="I27">
         <f t="shared" si="6"/>
-        <v>2.3030599218682355E-3</v>
+        <v>8.4366214657354846E-2</v>
       </c>
       <c r="J27" s="3"/>
       <c r="L27">
@@ -8200,25 +8200,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="D28">
-        <v>7.9007108136224906E-3</v>
+      <c r="D28" s="2">
+        <v>8.1578715103711296E-3</v>
       </c>
       <c r="E28" s="2">
-        <v>2.1579374269995798E-5</v>
-      </c>
-      <c r="F28">
-        <v>5.7868683352336496E-3</v>
+        <v>2.7906538103478998E-4</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5.02039478133323E-3</v>
       </c>
       <c r="G28" s="2">
-        <v>2.2153397083295701E-5</v>
+        <v>3.0805666033860603E-4</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="4"/>
-        <v>0.73244907600666376</v>
+        <v>0.61540498338945215</v>
       </c>
       <c r="I28">
         <f t="shared" si="6"/>
-        <v>3.444486925796071E-3</v>
+        <v>4.323355798647284E-2</v>
       </c>
       <c r="J28" s="3"/>
       <c r="L28">
@@ -8247,25 +8247,25 @@
         <v>50</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="D29">
-        <v>1.48099690035684E-2</v>
+      <c r="D29" s="2">
+        <v>1.49266627971049E-2</v>
       </c>
       <c r="E29" s="2">
-        <v>3.5619384608241799E-5</v>
-      </c>
-      <c r="F29">
-        <v>1.1357972286110201E-2</v>
+        <v>4.9518780486686295E-4</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1.0162125213435E-2</v>
       </c>
       <c r="G29" s="2">
-        <v>3.9960656049596501E-5</v>
+        <v>5.80825745840268E-4</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="4"/>
-        <v>0.76691398093902452</v>
+        <v>0.680803562830266</v>
       </c>
       <c r="I29">
         <f t="shared" si="6"/>
-        <v>3.2684265997479276E-3</v>
+        <v>4.4991600045113711E-2</v>
       </c>
       <c r="J29" s="3"/>
       <c r="L29">
@@ -8294,25 +8294,25 @@
         <v>75</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="D30">
-        <v>2.1060130702738999E-2</v>
+      <c r="D30" s="2">
+        <v>2.1432078952745001E-2</v>
       </c>
       <c r="E30" s="2">
-        <v>3.0830038687911403E-5</v>
-      </c>
-      <c r="F30">
-        <v>1.6724313084056999E-2</v>
+        <v>5.7708761237754895E-4</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1.65555585699587E-2</v>
       </c>
       <c r="G30" s="2">
-        <v>4.6773312275541899E-5</v>
+        <v>8.4894750486791501E-4</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="4"/>
-        <v>0.79412199858198884</v>
+        <v>0.77246629253567023</v>
       </c>
       <c r="I30">
         <f t="shared" si="6"/>
-        <v>2.506797039006772E-3</v>
+        <v>4.473995917320344E-2</v>
       </c>
       <c r="J30" s="3"/>
       <c r="L30">
@@ -8341,25 +8341,25 @@
         <v>100</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="D31">
-        <v>2.67600755292417E-2</v>
+      <c r="D31" s="2">
+        <v>2.7913216674849899E-2</v>
       </c>
       <c r="E31" s="2">
-        <v>6.1301138330409899E-5</v>
-      </c>
-      <c r="F31">
-        <v>2.2149757308928399E-2</v>
+        <v>6.6669793207153904E-4</v>
+      </c>
+      <c r="F31" s="2">
+        <v>2.0339611754264599E-2</v>
       </c>
       <c r="G31" s="2">
-        <v>5.1020148947823797E-5</v>
+        <v>7.3633525085197403E-4</v>
       </c>
       <c r="H31" s="13">
         <f t="shared" si="4"/>
-        <v>0.82771654679092965</v>
+        <v>0.72867315835336177</v>
       </c>
       <c r="I31">
         <f t="shared" si="6"/>
-        <v>2.6889139523652702E-3</v>
+        <v>3.1603458194463079E-2</v>
       </c>
       <c r="J31" s="3"/>
       <c r="L31">
@@ -8388,25 +8388,25 @@
         <v>150</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="D32">
-        <v>3.6782709718709998E-2</v>
-      </c>
-      <c r="E32">
-        <v>1.97489580151579E-4</v>
-      </c>
-      <c r="F32">
-        <v>3.2103137598192298E-2</v>
-      </c>
-      <c r="G32">
-        <v>2.08831333646651E-4</v>
+      <c r="D32" s="2">
+        <v>3.6427579453755798E-2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1.0472429250006801E-3</v>
+      </c>
+      <c r="F32" s="2">
+        <v>2.9873697265033802E-2</v>
+      </c>
+      <c r="G32" s="2">
+        <v>8.5514874767622401E-4</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="4"/>
-        <v>0.87277793951821403</v>
+        <v>0.8200846093262375</v>
       </c>
       <c r="I32">
         <f t="shared" si="6"/>
-        <v>7.3615233968889766E-3</v>
+        <v>3.327059479181485E-2</v>
       </c>
       <c r="J32" s="3"/>
       <c r="L32">
@@ -8435,25 +8435,25 @@
         <v>250</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="D33">
-        <v>5.6309750104400702E-2</v>
-      </c>
-      <c r="E33">
-        <v>2.51687827781958E-4</v>
-      </c>
-      <c r="F33">
-        <v>5.1114734736025402E-2</v>
-      </c>
-      <c r="G33">
-        <v>2.8833834514146198E-4</v>
+      <c r="D33" s="2">
+        <v>5.53819360171761E-2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1.4584466490748199E-3</v>
+      </c>
+      <c r="F33" s="2">
+        <v>4.6882404518702597E-2</v>
+      </c>
+      <c r="G33" s="2">
+        <v>9.0297433456597396E-4</v>
       </c>
       <c r="H33" s="13">
         <f t="shared" si="4"/>
-        <v>0.90774216971761523</v>
+        <v>0.84652881228569787</v>
       </c>
       <c r="I33">
         <f t="shared" si="6"/>
-        <v>6.5331679556135417E-3</v>
+        <v>2.7618912628068853E-2</v>
       </c>
       <c r="J33" s="3"/>
       <c r="L33">
@@ -8482,25 +8482,25 @@
         <v>500</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="D34">
-        <v>9.4384365104793602E-2</v>
-      </c>
-      <c r="E34">
-        <v>3.7802904257795602E-4</v>
-      </c>
-      <c r="F34">
-        <v>9.1445222619505398E-2</v>
-      </c>
-      <c r="G34">
-        <v>4.4906828447954003E-4</v>
+      <c r="D34" s="2">
+        <v>9.4183377970993604E-2</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1.5799693791771401E-3</v>
+      </c>
+      <c r="F34" s="2">
+        <v>8.9405221334390397E-2</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1.70807591224624E-3</v>
       </c>
       <c r="H34" s="13">
         <f t="shared" si="4"/>
-        <v>0.96885985849430767</v>
+        <v>0.94926751684278332</v>
       </c>
       <c r="I34">
         <f t="shared" si="6"/>
-        <v>6.1396636178584303E-3</v>
+        <v>2.4134786583998237E-2</v>
       </c>
       <c r="J34" s="3"/>
       <c r="L34">
@@ -8529,25 +8529,25 @@
         <v>750</v>
       </c>
       <c r="B35" s="4"/>
-      <c r="D35">
-        <v>0.12681392305883499</v>
-      </c>
-      <c r="E35">
-        <v>3.7117560576619898E-4</v>
-      </c>
-      <c r="F35">
-        <v>0.12725844081883</v>
-      </c>
-      <c r="G35">
-        <v>3.9277512684765298E-4</v>
+      <c r="D35" s="2">
+        <v>0.12938440937586501</v>
+      </c>
+      <c r="E35" s="2">
+        <v>2.1442760752734399E-3</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.117827003366891</v>
+      </c>
+      <c r="G35" s="2">
+        <v>2.1418785805969601E-3</v>
       </c>
       <c r="H35" s="13">
         <f t="shared" si="4"/>
-        <v>1.0035052756769365</v>
+        <v>0.91067388980847419</v>
       </c>
       <c r="I35">
         <f t="shared" si="6"/>
-        <v>4.2684987159538603E-3</v>
+        <v>2.2401595997311816E-2</v>
       </c>
       <c r="J35" s="3"/>
       <c r="L35">
@@ -8576,25 +8576,25 @@
         <v>999.99</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="D36">
-        <v>0.15510900896549801</v>
-      </c>
-      <c r="E36">
-        <v>5.7851797067085496E-4</v>
-      </c>
-      <c r="F36">
-        <v>0.157583868759714</v>
-      </c>
-      <c r="G36">
-        <v>5.8700051779191705E-4</v>
+      <c r="D36" s="2">
+        <v>0.15752496538125499</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2.4554689207597698E-3</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.14133786701866499</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1.8390528502879599E-3</v>
       </c>
       <c r="H36" s="13">
         <f t="shared" si="4"/>
-        <v>1.0159556160581653</v>
+        <v>0.897241060657194</v>
       </c>
       <c r="I36">
         <f>H36*((E36/D36)^2 +(G36/F36)^2)^0.5</f>
-        <v>5.3554157048239367E-3</v>
+        <v>1.8218310636367537E-2</v>
       </c>
       <c r="J36" s="3"/>
       <c r="L36">
@@ -8715,24 +8715,24 @@
       <c r="B42" s="4"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2">
-        <v>3.1823783667320202E-6</v>
+        <v>3.2508308570749199E-6</v>
       </c>
       <c r="E42" s="2">
-        <v>4.1159886287402301E-10</v>
+        <v>2.9879791871820602E-8</v>
       </c>
       <c r="F42" s="2">
-        <v>3.4389546303583601E-6</v>
+        <v>2.4077020934709801E-6</v>
       </c>
       <c r="G42" s="2">
-        <v>7.2754924795352899E-9</v>
+        <v>4.5116812236236001E-7</v>
       </c>
       <c r="H42" s="13">
         <f t="shared" ref="H42:H54" si="8">F42/D42</f>
-        <v>1.0806240597625159</v>
+        <v>0.74064206946694777</v>
       </c>
       <c r="I42">
         <f>H42*((E42/D42)^2 +(G42/F42)^2)^0.5</f>
-        <v>2.2904490835581361E-3</v>
+        <v>0.13895233886852032</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="2"/>
@@ -8763,24 +8763,24 @@
       </c>
       <c r="B43" s="4"/>
       <c r="D43" s="2">
-        <v>1.6000871976086401E-5</v>
+        <v>1.6123275821852999E-5</v>
       </c>
       <c r="E43" s="2">
-        <v>1.8077035460066801E-9</v>
+        <v>2.0263996088365101E-7</v>
       </c>
       <c r="F43" s="2">
-        <v>1.7406241259005801E-5</v>
+        <v>1.5829821996247301E-5</v>
       </c>
       <c r="G43" s="2">
-        <v>1.6560027342357799E-8</v>
+        <v>1.9692674060295302E-6</v>
       </c>
       <c r="H43" s="13">
         <f t="shared" si="8"/>
-        <v>1.0878307935354867</v>
+        <v>0.98179936702391701</v>
       </c>
       <c r="I43">
         <f t="shared" ref="I43:I53" si="10">H43*((E43/D43)^2 +(G43/F43)^2)^0.5</f>
-        <v>1.0422167294252094E-3</v>
+        <v>0.12275990292260608</v>
       </c>
       <c r="J43" s="3"/>
       <c r="L43" s="2">
@@ -8810,24 +8810,24 @@
       </c>
       <c r="B44" s="4"/>
       <c r="D44" s="2">
-        <v>3.2035093398018297E-5</v>
+        <v>3.1996604066933298E-5</v>
       </c>
       <c r="E44" s="2">
-        <v>3.6301326712904198E-9</v>
+        <v>4.1792496489736701E-7</v>
       </c>
       <c r="F44" s="2">
-        <v>3.4905945803773603E-5</v>
+        <v>3.2983010764906299E-5</v>
       </c>
       <c r="G44" s="2">
-        <v>3.0128552778278198E-8</v>
+        <v>2.2398843673895399E-6</v>
       </c>
       <c r="H44" s="13">
         <f t="shared" si="8"/>
-        <v>1.0896158587735816</v>
+        <v>1.030828480919711</v>
       </c>
       <c r="I44">
         <f t="shared" si="10"/>
-        <v>9.4855633081543855E-4</v>
+        <v>7.1286878880722632E-2</v>
       </c>
       <c r="J44" s="3"/>
       <c r="L44" s="2">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="B45" s="4"/>
       <c r="D45">
-        <v>3.2041283539142699E-4</v>
+        <v>3.17520187164021E-4</v>
       </c>
       <c r="E45" s="2">
-        <v>1.03089800141475E-7</v>
+        <v>3.5903642084798401E-6</v>
       </c>
       <c r="F45">
-        <v>3.5175355668395599E-4</v>
+        <v>3.2190498140927299E-4</v>
       </c>
       <c r="G45" s="2">
-        <v>3.24163031926656E-7</v>
+        <v>1.0083144680763101E-5</v>
       </c>
       <c r="H45" s="13">
         <f t="shared" si="8"/>
-        <v>1.0978135637239441</v>
+        <v>1.0138094975453857</v>
       </c>
       <c r="I45">
         <f t="shared" si="10"/>
-        <v>1.0715892980094322E-3</v>
+        <v>3.3761722320914872E-2</v>
       </c>
       <c r="J45" s="3"/>
       <c r="L45" s="2">
@@ -8904,24 +8904,24 @@
       </c>
       <c r="B46" s="4"/>
       <c r="D46">
-        <v>7.9832852090792796E-4</v>
+        <v>8.1568502250048002E-4</v>
       </c>
       <c r="E46" s="2">
-        <v>6.4380828459592396E-7</v>
+        <v>5.3855794471320103E-6</v>
       </c>
       <c r="F46">
-        <v>8.7467769000268295E-4</v>
+        <v>8.0308685347477604E-4</v>
       </c>
       <c r="G46" s="2">
-        <v>1.03125836480735E-6</v>
+        <v>1.5815547986996E-5</v>
       </c>
       <c r="H46" s="13">
         <f t="shared" si="8"/>
-        <v>1.0956362789192651</v>
+        <v>0.98455510561284509</v>
       </c>
       <c r="I46">
         <f t="shared" si="10"/>
-        <v>1.5650469392181556E-3</v>
+        <v>2.044997390903704E-2</v>
       </c>
       <c r="J46" s="3"/>
       <c r="L46">
@@ -8951,24 +8951,24 @@
       </c>
       <c r="B47" s="4"/>
       <c r="D47">
-        <v>1.5863990621956901E-3</v>
+        <v>1.60165101199415E-3</v>
       </c>
       <c r="E47" s="2">
-        <v>6.9872049483164404E-7</v>
+        <v>1.68217601711865E-5</v>
       </c>
       <c r="F47">
-        <v>1.7451813935783799E-3</v>
+        <v>1.64322981589001E-3</v>
       </c>
       <c r="G47" s="2">
-        <v>2.15270592824618E-6</v>
+        <v>2.5755780859259001E-5</v>
       </c>
       <c r="H47" s="13">
         <f t="shared" si="8"/>
-        <v>1.1000897789002244</v>
+        <v>1.025959964801628</v>
       </c>
       <c r="I47">
         <f t="shared" si="10"/>
-        <v>1.4408859671880526E-3</v>
+        <v>1.9357187123934069E-2</v>
       </c>
       <c r="J47" s="3"/>
       <c r="L47">
@@ -8998,24 +8998,24 @@
       </c>
       <c r="B48" s="4"/>
       <c r="D48">
-        <v>2.3694633374357899E-3</v>
+        <v>2.3979320506641501E-3</v>
       </c>
       <c r="E48" s="2">
-        <v>2.0409182758839298E-6</v>
+        <v>3.1169443646373198E-5</v>
       </c>
       <c r="F48">
-        <v>2.6035551899146001E-3</v>
+        <v>2.3274282513085498E-3</v>
       </c>
       <c r="G48" s="2">
-        <v>1.69836561383817E-6</v>
+        <v>3.8598219967931103E-5</v>
       </c>
       <c r="H48" s="13">
         <f t="shared" si="8"/>
-        <v>1.098795304734338</v>
+        <v>0.97059808290394511</v>
       </c>
       <c r="I48">
         <f t="shared" si="10"/>
-        <v>1.1872271872232696E-3</v>
+        <v>2.0451571874940244E-2</v>
       </c>
       <c r="J48" s="3"/>
       <c r="L48">
@@ -9045,24 +9045,24 @@
       </c>
       <c r="B49" s="4"/>
       <c r="D49">
-        <v>3.1410862514606899E-3</v>
+        <v>3.1150452266862499E-3</v>
       </c>
       <c r="E49" s="2">
-        <v>3.27513526933276E-6</v>
+        <v>3.0375204510835499E-5</v>
       </c>
       <c r="F49">
-        <v>3.4466944423003402E-3</v>
+        <v>3.1491175964614999E-3</v>
       </c>
       <c r="G49" s="2">
-        <v>3.2445791725811299E-6</v>
+        <v>3.7025405401571998E-5</v>
       </c>
       <c r="H49" s="13">
         <f t="shared" si="8"/>
-        <v>1.0972937915020748</v>
+        <v>1.0109380016326426</v>
       </c>
       <c r="I49">
         <f t="shared" si="10"/>
-        <v>1.541426865977242E-3</v>
+        <v>1.5441915923900233E-2</v>
       </c>
       <c r="J49" s="3"/>
       <c r="L49">
@@ -9092,24 +9092,24 @@
       </c>
       <c r="B50" s="4"/>
       <c r="D50">
-        <v>4.6445716846820698E-3</v>
+        <v>4.6543407829659003E-3</v>
       </c>
       <c r="E50" s="2">
-        <v>9.6466217564299792E-6</v>
+        <v>4.7462851945895098E-5</v>
       </c>
       <c r="F50">
-        <v>5.1102808521361299E-3</v>
+        <v>4.6288384862751501E-3</v>
       </c>
       <c r="G50" s="2">
-        <v>1.2123213047497999E-5</v>
+        <v>5.6491200849806098E-5</v>
       </c>
       <c r="H50" s="13">
         <f t="shared" si="8"/>
-        <v>1.1002695617746587</v>
+        <v>0.99452075000952134</v>
       </c>
       <c r="I50">
         <f t="shared" si="10"/>
-        <v>3.4691982513368859E-3</v>
+        <v>1.581669692140476E-2</v>
       </c>
       <c r="J50" s="3"/>
       <c r="L50">
@@ -9139,24 +9139,24 @@
       </c>
       <c r="B51" s="4"/>
       <c r="D51">
-        <v>7.5610462202649401E-3</v>
+        <v>7.6150959878939798E-3</v>
       </c>
       <c r="E51" s="2">
-        <v>1.57081565413314E-5</v>
+        <v>7.5030193636514299E-5</v>
       </c>
       <c r="F51">
-        <v>8.3558566219651704E-3</v>
+        <v>7.66287134998351E-3</v>
       </c>
       <c r="G51" s="2">
-        <v>2.3966742759134201E-5</v>
+        <v>7.5060793105698198E-5</v>
       </c>
       <c r="H51" s="13">
         <f t="shared" si="8"/>
-        <v>1.1051191036989032</v>
+        <v>1.0062737701751205</v>
       </c>
       <c r="I51">
         <f t="shared" si="10"/>
-        <v>3.9138927052399545E-3</v>
+        <v>1.398060647072992E-2</v>
       </c>
       <c r="J51" s="3"/>
       <c r="L51">
@@ -9186,24 +9186,24 @@
       </c>
       <c r="B52" s="4"/>
       <c r="D52">
-        <v>1.4415070472640399E-2</v>
-      </c>
-      <c r="E52" s="2">
-        <v>3.9280138415606102E-5</v>
+        <v>1.4555744618778E-2</v>
+      </c>
+      <c r="E52">
+        <v>1.2950150523133701E-4</v>
       </c>
       <c r="F52">
-        <v>1.57632575158239E-2</v>
-      </c>
-      <c r="G52" s="2">
-        <v>4.6556836615973601E-5</v>
+        <v>1.43182113525849E-2</v>
+      </c>
+      <c r="G52">
+        <v>1.4705046376382701E-4</v>
       </c>
       <c r="H52" s="13">
         <f t="shared" si="8"/>
-        <v>1.0935262193648196</v>
+        <v>0.9836811326102366</v>
       </c>
       <c r="I52">
         <f t="shared" si="10"/>
-        <v>4.3943507224962841E-3</v>
+        <v>1.3366190039228829E-2</v>
       </c>
       <c r="J52" s="3"/>
       <c r="L52">
@@ -9233,24 +9233,24 @@
       </c>
       <c r="B53" s="4"/>
       <c r="D53">
-        <v>2.0534104630709499E-2</v>
-      </c>
-      <c r="E53" s="2">
-        <v>5.1678598638391099E-5</v>
+        <v>2.0743350143341999E-2</v>
+      </c>
+      <c r="E53">
+        <v>2.4538469022951099E-4</v>
       </c>
       <c r="F53">
-        <v>2.23393057358535E-2</v>
-      </c>
-      <c r="G53" s="2">
-        <v>5.7826696670158199E-5</v>
+        <v>2.0707732271304301E-2</v>
+      </c>
+      <c r="G53">
+        <v>2.6747352499092303E-4</v>
       </c>
       <c r="H53" s="13">
         <f t="shared" si="8"/>
-        <v>1.0879123359702889</v>
+        <v>0.99828292576697741</v>
       </c>
       <c r="I53">
         <f t="shared" si="10"/>
-        <v>3.927730995428016E-3</v>
+        <v>1.7484977915483216E-2</v>
       </c>
       <c r="J53" s="3"/>
       <c r="L53">
@@ -9280,24 +9280,24 @@
       </c>
       <c r="B54" s="4"/>
       <c r="D54">
-        <v>2.6037643908025699E-2</v>
-      </c>
-      <c r="E54" s="2">
-        <v>7.16762407558917E-5</v>
+        <v>2.61827077319201E-2</v>
+      </c>
+      <c r="E54">
+        <v>3.1898400948727698E-4</v>
       </c>
       <c r="F54">
-        <v>2.8423944908042901E-2</v>
-      </c>
-      <c r="G54" s="2">
-        <v>6.8045831633092906E-5</v>
+        <v>2.5981087494686798E-2</v>
+      </c>
+      <c r="G54">
+        <v>4.3258976581349399E-4</v>
       </c>
       <c r="H54" s="13">
         <f t="shared" si="8"/>
-        <v>1.0916481156454276</v>
+        <v>0.99229948868170348</v>
       </c>
       <c r="I54">
         <f>H54*((E54/D54)^2 +(G54/F54)^2)^0.5</f>
-        <v>3.9824844315028184E-3</v>
+        <v>2.047251252301235E-2</v>
       </c>
       <c r="J54" s="3"/>
       <c r="L54">

--- a/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F315056-74B9-4FD9-A47F-3DFD3BFCFF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCF5112-228B-4CCD-9797-84B902552570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,9 +84,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -187,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -209,6 +210,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -303,7 +305,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
+              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -351,48 +353,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$24:$H$36</c:f>
+              <c:f>'Sheet 1'!$H$22:$H$34</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.17624938992497577</c:v>
+                  <c:v>0.60921857304058236</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.82691997712063736</c:v>
+                  <c:v>0.6202561947395715</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.53604618365050316</c:v>
+                  <c:v>0.61752137885807601</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.67249847128047058</c:v>
+                  <c:v>0.63758916509434371</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.61540498338945215</c:v>
+                  <c:v>0.66203600474217295</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.680803562830266</c:v>
+                  <c:v>0.70507179114481311</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.77246629253567023</c:v>
+                  <c:v>0.7294127014308962</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.72867315835336177</c:v>
+                  <c:v>0.75883175130100222</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.8200846093262375</c:v>
+                  <c:v>0.79545758961655577</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.84652881228569787</c:v>
+                  <c:v>0.84382782080221264</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.94926751684278332</c:v>
+                  <c:v>0.90466917724369844</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91067388980847419</c:v>
+                  <c:v>0.93426211404435788</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.897241060657194</c:v>
+                  <c:v>0.94461149030720559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -431,7 +433,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
+              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -479,48 +481,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$24:$P$36</c:f>
+              <c:f>'Sheet 1'!$P$22:$P$34</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.85719868916492581</c:v>
+                  <c:v>0.79502846395901039</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86272360378029123</c:v>
+                  <c:v>0.79868938528194633</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86473422707265823</c:v>
+                  <c:v>0.79518763707084539</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.87150263943790185</c:v>
+                  <c:v>0.80345865035736497</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.8842176678721938</c:v>
+                  <c:v>0.81088238286163838</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.89942526896969821</c:v>
+                  <c:v>0.82902260635681613</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.92270745337377136</c:v>
+                  <c:v>0.83691230418362095</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.92487302633259483</c:v>
+                  <c:v>0.85434998565560982</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.95280649072651702</c:v>
+                  <c:v>0.87107729502555376</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.96680285364811647</c:v>
+                  <c:v>0.89761675786997808</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.996195710817117</c:v>
+                  <c:v>0.93561261604161028</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0164077631511579</c:v>
+                  <c:v>0.94942620263109356</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.025113077347247</c:v>
+                  <c:v>0.95529529971486393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -880,43 +882,43 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0119378821291016</c:v>
+                  <c:v>0.9998603042189127</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0179707921448478</c:v>
+                  <c:v>1.0000344135667951</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.027861427431511</c:v>
+                  <c:v>0.99972875209679635</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.98075710537859517</c:v>
+                  <c:v>1.0004307004310948</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.97199820729613373</c:v>
+                  <c:v>0.99987294859246889</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0175104699823445</c:v>
+                  <c:v>1.0034908088336543</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0048750533338346</c:v>
+                  <c:v>1.0033956670138846</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.9979952120781076</c:v>
+                  <c:v>1.0064230040690332</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.011050091074648</c:v>
+                  <c:v>1.0033930501844626</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0131574726669086</c:v>
+                  <c:v>1.0056561246790048</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0184379609619567</c:v>
+                  <c:v>1.0084253334590485</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9965086561044354</c:v>
+                  <c:v>1.0092132738126995</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.97509536567142829</c:v>
+                  <c:v>1.0067671917223222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1008,43 +1010,43 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0001778209825207</c:v>
+                  <c:v>0.99985164204500476</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0000381873265614</c:v>
+                  <c:v>1.000048307802117</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99990753724213677</c:v>
+                  <c:v>0.99965590519960335</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0002355998584036</c:v>
+                  <c:v>1.0000262657831211</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0004553713443167</c:v>
+                  <c:v>0.99791427508006425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0005898491614427</c:v>
+                  <c:v>1.0019971917206978</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0011630341173221</c:v>
+                  <c:v>1.0001887595608641</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0006238901134941</c:v>
+                  <c:v>1.0035315741212536</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0042585132338837</c:v>
+                  <c:v>1.0026365736292491</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.99880156437237411</c:v>
+                  <c:v>1.0060724035768513</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.99475053432196514</c:v>
+                  <c:v>1.0087754771104167</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0016645335554861</c:v>
+                  <c:v>1.0084712891808669</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.99641459582252734</c:v>
+                  <c:v>1.003839398792538</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1351,7 +1353,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$61:$A$73</c:f>
+              <c:f>'Sheet 1'!$A$59:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1399,48 +1401,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$61:$H$73</c:f>
+              <c:f>'Sheet 1'!$H$59:$H$71</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0119494333277688</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0046216143420734</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0048022391924298</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0074201952385748</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.99855232576426989</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0062589046099648</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0053817035380381</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0072027374599906</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.9742849264690957</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.97616456219725189</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9799423091236853</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0188709591230252</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.99844143416244169</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1479,7 +1481,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$61:$A$73</c:f>
+              <c:f>'Sheet 1'!$A$59:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1527,48 +1529,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$61:$P$73</c:f>
+              <c:f>'Sheet 1'!$P$59:$P$71</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0000859211924744</c:v>
+                  <c:v>0.99993184010427161</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0001619611909021</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0001147967856605</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99972727168909759</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0009621278127161</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.99965798036547726</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.99728610985822141</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.99904092814030765</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.99984894845423344</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9997025557725211</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0016101422064423</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.99432829011273149</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.98920834124726476</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1875,7 +1877,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
+              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1923,48 +1925,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$79:$H$91</c:f>
+              <c:f>'Sheet 1'!$H$76:$H$88</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.95760453346929775</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0295651696337502</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98378540418597427</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9920173474307975</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.99158974208705197</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.99092060967905771</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.99975516228721106</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.9915894249927204</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.96038498372370706</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.97623391752832367</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.96511013750571617</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0142137623728962</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.98390804304704371</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2003,7 +2005,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
+              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2051,48 +2053,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$79:$P$91</c:f>
+              <c:f>'Sheet 1'!$P$76:$P$88</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0421829854714089</c:v>
+                  <c:v>0.98943213465866797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0468679184142133</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0491120103788383</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0548236283228316</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0592976963273675</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0599512468140793</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0559969197962629</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0610351455367648</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0635211665810387</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0673679820985291</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0749164325098632</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0676051493877452</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0682957802000932</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2402,7 +2404,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
+              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2450,48 +2452,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$79:$H$91</c:f>
+              <c:f>'Sheet 1'!$H$76:$H$88</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.95760453346929775</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0295651696337502</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98378540418597427</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9920173474307975</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.99158974208705197</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.99092060967905771</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.99975516228721106</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.9915894249927204</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.96038498372370706</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.97623391752832367</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.96511013750571617</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0142137623728962</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.98390804304704371</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2530,7 +2532,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
+              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2578,48 +2580,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$79:$P$91</c:f>
+              <c:f>'Sheet 1'!$P$76:$P$88</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0421829854714089</c:v>
+                  <c:v>0.98943213465866797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0468679184142133</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0491120103788383</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0548236283228316</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0592976963273675</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0599512468140793</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0559969197962629</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0610351455367648</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0635211665810387</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0673679820985291</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0749164325098632</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0676051493877452</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0682957802000932</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2929,7 +2931,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
+              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2977,48 +2979,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$24:$H$36</c:f>
+              <c:f>'Sheet 1'!$H$22:$H$34</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.17624938992497577</c:v>
+                  <c:v>0.60921857304058236</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.82691997712063736</c:v>
+                  <c:v>0.6202561947395715</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.53604618365050316</c:v>
+                  <c:v>0.61752137885807601</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.67249847128047058</c:v>
+                  <c:v>0.63758916509434371</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.61540498338945215</c:v>
+                  <c:v>0.66203600474217295</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.680803562830266</c:v>
+                  <c:v>0.70507179114481311</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.77246629253567023</c:v>
+                  <c:v>0.7294127014308962</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.72867315835336177</c:v>
+                  <c:v>0.75883175130100222</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.8200846093262375</c:v>
+                  <c:v>0.79545758961655577</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.84652881228569787</c:v>
+                  <c:v>0.84382782080221264</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.94926751684278332</c:v>
+                  <c:v>0.90466917724369844</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91067388980847419</c:v>
+                  <c:v>0.93426211404435788</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.897241060657194</c:v>
+                  <c:v>0.94461149030720559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3057,7 +3059,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
+              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -3105,48 +3107,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$24:$P$36</c:f>
+              <c:f>'Sheet 1'!$P$22:$P$34</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.85719868916492581</c:v>
+                  <c:v>0.79502846395901039</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86272360378029123</c:v>
+                  <c:v>0.79868938528194633</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.86473422707265823</c:v>
+                  <c:v>0.79518763707084539</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.87150263943790185</c:v>
+                  <c:v>0.80345865035736497</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.8842176678721938</c:v>
+                  <c:v>0.81088238286163838</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.89942526896969821</c:v>
+                  <c:v>0.82902260635681613</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.92270745337377136</c:v>
+                  <c:v>0.83691230418362095</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.92487302633259483</c:v>
+                  <c:v>0.85434998565560982</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.95280649072651702</c:v>
+                  <c:v>0.87107729502555376</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.96680285364811647</c:v>
+                  <c:v>0.89761675786997808</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.996195710817117</c:v>
+                  <c:v>0.93561261604161028</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0164077631511579</c:v>
+                  <c:v>0.94942620263109356</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.025113077347247</c:v>
+                  <c:v>0.95529529971486393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6718,13 +6720,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>583097</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>278297</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>145775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6790,14 +6792,14 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>53010</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>159027</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>357810</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>119270</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6826,13 +6828,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>417444</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>112644</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>112644</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6862,13 +6864,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>417444</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>112644</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>112644</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6900,13 +6902,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>583097</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>278297</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>145775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7200,7 +7202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -7312,45 +7314,45 @@
       </c>
       <c r="B5" s="4"/>
       <c r="D5">
-        <v>1.3681371012949699</v>
+        <v>1.38568705105649</v>
       </c>
       <c r="E5">
-        <v>1.1475260729751101E-2</v>
+        <v>1.06766711697189E-4</v>
       </c>
       <c r="F5">
-        <v>1.38446976074668</v>
+        <v>1.3854934764215501</v>
       </c>
       <c r="G5">
-        <v>1.12587768842507E-2</v>
+        <v>1.21692112817596E-4</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" ref="H5:H17" si="0">F5/D5</f>
-        <v>1.0119378821291016</v>
+        <v>0.9998603042189127</v>
       </c>
       <c r="I5">
         <f>H5*((E5/D5)^2 +(G5/F5)^2)^0.5</f>
-        <v>1.182205369797695E-2</v>
+        <v>1.1682242876687881E-4</v>
       </c>
       <c r="J5" s="3"/>
       <c r="L5">
-        <v>1.38908077443087</v>
+        <v>1.38569542224164</v>
       </c>
       <c r="M5">
-        <v>1.0124318874365601E-4</v>
+        <v>1.04524729364728E-4</v>
       </c>
       <c r="N5">
-        <v>1.38932778213898</v>
+        <v>1.38548984330255</v>
       </c>
       <c r="O5">
-        <v>1.14700118954492E-4</v>
+        <v>1.21508776325718E-4</v>
       </c>
       <c r="P5" s="7">
         <f t="shared" ref="P5:P17" si="1">N5/L5</f>
-        <v>1.0001778209825207</v>
+        <v>0.99985164204500476</v>
       </c>
       <c r="Q5">
         <f>P5*((M5/L5)^2 +(O5/N5)^2)^0.5</f>
-        <v>1.1014700886063438E-4</v>
+        <v>1.1566053404779838E-4</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -7359,45 +7361,45 @@
       </c>
       <c r="B6" s="4"/>
       <c r="D6">
-        <v>1.36116575463441</v>
+        <v>1.38557490985293</v>
       </c>
       <c r="E6">
-        <v>1.1125190871760801E-2</v>
+        <v>1.4744979759760099E-4</v>
       </c>
       <c r="F6">
-        <v>1.3856269814856299</v>
+        <v>1.38562259242764</v>
       </c>
       <c r="G6">
-        <v>1.0321337384108399E-2</v>
+        <v>1.41590198134267E-4</v>
       </c>
       <c r="H6" s="7">
         <f t="shared" si="0"/>
-        <v>1.0179707921448478</v>
+        <v>1.0000344135667951</v>
       </c>
       <c r="I6">
         <f t="shared" ref="I6:I16" si="2">H6*((E6/D6)^2 +(G6/F6)^2)^0.5</f>
-        <v>1.1257118632435607E-2</v>
+        <v>1.475400526786516E-4</v>
       </c>
       <c r="J6" s="3"/>
       <c r="L6">
-        <v>1.3890751130454999</v>
+        <v>1.3855158356775501</v>
       </c>
       <c r="M6">
-        <v>1.5633111145029499E-4</v>
+        <v>1.45139969687137E-4</v>
       </c>
       <c r="N6">
-        <v>1.38912815811046</v>
+        <v>1.3855827669023699</v>
       </c>
       <c r="O6">
-        <v>1.6988497331219999E-4</v>
+        <v>1.42153780318111E-4</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" si="1"/>
-        <v>1.0000381873265614</v>
+        <v>1.000048307802117</v>
       </c>
       <c r="Q6">
         <f t="shared" ref="Q6:Q16" si="3">P6*((M6/L6)^2 +(O6/N6)^2)^0.5</f>
-        <v>1.6620603320820275E-4</v>
+        <v>1.4663372036719969E-4</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -7406,45 +7408,45 @@
       </c>
       <c r="B7" s="4"/>
       <c r="D7">
-        <v>1.3663565821363799</v>
+        <v>1.3854701997740699</v>
       </c>
       <c r="E7">
-        <v>1.6432050614063699E-2</v>
+        <v>1.18590366266381E-4</v>
       </c>
       <c r="F7">
-        <v>1.40442522689514</v>
+        <v>1.3850943938874301</v>
       </c>
       <c r="G7">
-        <v>1.3826122129943601E-2</v>
+        <v>1.15687396918844E-4</v>
       </c>
       <c r="H7" s="7">
         <f t="shared" si="0"/>
-        <v>1.027861427431511</v>
+        <v>0.99972875209679635</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>1.5974792343773782E-2</v>
+        <v>1.1956163903207409E-4</v>
       </c>
       <c r="J7" s="3"/>
       <c r="L7">
-        <v>1.3889046123851001</v>
+        <v>1.3855004644369999</v>
       </c>
       <c r="M7">
-        <v>1.70335691939932E-4</v>
+        <v>1.17489357633876E-4</v>
       </c>
       <c r="N7">
-        <v>1.38877619043423</v>
+        <v>1.3850237209312399</v>
       </c>
       <c r="O7">
-        <v>1.5373454905333599E-4</v>
+        <v>1.1898853718211701E-4</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" si="1"/>
-        <v>0.99990753724213677</v>
+        <v>0.99965590519960335</v>
       </c>
       <c r="Q7">
         <f t="shared" si="3"/>
-        <v>1.6519568405949642E-4</v>
+        <v>1.2067125581283931E-4</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -7453,45 +7455,45 @@
       </c>
       <c r="B8" s="4"/>
       <c r="D8">
-        <v>1.39704864054061</v>
+        <v>1.38182742466079</v>
       </c>
       <c r="E8">
-        <v>1.23281362355317E-2</v>
+        <v>5.8826992728855398E-4</v>
       </c>
       <c r="F8">
-        <v>1.3701653807697101</v>
+        <v>1.38242257832829</v>
       </c>
       <c r="G8">
-        <v>1.18088772589459E-2</v>
+        <v>4.0062708048543301E-4</v>
       </c>
       <c r="H8" s="7">
         <f t="shared" si="0"/>
-        <v>0.98075710537859517</v>
+        <v>1.0004307004310948</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>1.2097557519592871E-2</v>
+        <v>5.1521789831282798E-4</v>
       </c>
       <c r="J8" s="3"/>
       <c r="L8">
-        <v>1.3856175235925701</v>
+        <v>1.3814926812914099</v>
       </c>
       <c r="M8">
-        <v>4.5540286699321999E-4</v>
+        <v>6.1199152441115403E-4</v>
       </c>
       <c r="N8">
-        <v>1.38594397488493</v>
+        <v>1.38152896727856</v>
       </c>
       <c r="O8">
-        <v>4.3477128848851398E-4</v>
+        <v>4.2009791734311198E-4</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" si="1"/>
-        <v>1.0002355998584036</v>
+        <v>1.0000262657831211</v>
       </c>
       <c r="Q8">
         <f t="shared" si="3"/>
-        <v>4.5445068306877072E-4</v>
+        <v>5.3733016877644728E-4</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -7501,45 +7503,45 @@
       <c r="B9" s="4"/>
       <c r="C9"/>
       <c r="D9">
-        <v>1.39382815633733</v>
+        <v>1.3774171053326401</v>
       </c>
       <c r="E9">
-        <v>1.27595827530817E-2</v>
+        <v>1.4417544606322699E-3</v>
       </c>
       <c r="F9">
-        <v>1.35479846923876</v>
+        <v>1.37724210255065</v>
       </c>
       <c r="G9">
-        <v>1.49502540503268E-2</v>
+        <v>1.2746675419086099E-3</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
-        <v>0.97199820729613373</v>
+        <v>0.99987294859246889</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>1.3936370030626408E-2</v>
+        <v>1.397030280451807E-3</v>
       </c>
       <c r="K9"/>
       <c r="L9">
-        <v>1.37951144335299</v>
+        <v>1.37697576952697</v>
       </c>
       <c r="M9">
-        <v>9.6051663666235599E-4</v>
+        <v>1.12026925426321E-3</v>
       </c>
       <c r="N9">
-        <v>1.3801396333334499</v>
+        <v>1.3741037768503199</v>
       </c>
       <c r="O9">
-        <v>1.0536694518052999E-3</v>
+        <v>1.51167839369038E-3</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" si="1"/>
-        <v>1.0004553713443167</v>
+        <v>0.99791427508006425</v>
       </c>
       <c r="Q9">
         <f t="shared" si="3"/>
-        <v>1.0337440128011612E-3</v>
+        <v>1.3654161494401974E-3</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -7548,45 +7550,45 @@
       </c>
       <c r="B10" s="4"/>
       <c r="D10">
-        <v>1.36790794333796</v>
+        <v>1.3679348508498099</v>
       </c>
       <c r="E10">
-        <v>1.2545386712593301E-2</v>
+        <v>1.3306686755892199E-3</v>
       </c>
       <c r="F10">
-        <v>1.39186065431839</v>
+        <v>1.3727100499110201</v>
       </c>
       <c r="G10">
-        <v>1.3451922716281201E-2</v>
+        <v>1.3206530177016201E-3</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="0"/>
-        <v>1.0175104699823445</v>
+        <v>1.0034908088336543</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>1.3556883805699941E-2</v>
+        <v>1.3729314284567464E-3</v>
       </c>
       <c r="J10" s="3"/>
       <c r="L10">
-        <v>1.3703576195701299</v>
+        <v>1.3661603659296999</v>
       </c>
       <c r="M10">
-        <v>9.5714052610468097E-4</v>
+        <v>1.34646090112148E-3</v>
       </c>
       <c r="N10">
-        <v>1.3711659238629099</v>
+        <v>1.36888885010168</v>
       </c>
       <c r="O10">
-        <v>7.5549871036543397E-4</v>
+        <v>1.3723349104996601E-3</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" si="1"/>
-        <v>1.0005898491614427</v>
+        <v>1.0019971917206978</v>
       </c>
       <c r="Q10">
         <f t="shared" si="3"/>
-        <v>8.901521419890664E-4</v>
+        <v>1.4086562192379159E-3</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -7596,45 +7598,45 @@
       <c r="B11" s="4"/>
       <c r="C11"/>
       <c r="D11">
-        <v>1.35845231954227</v>
+        <v>1.3609940904226101</v>
       </c>
       <c r="E11">
-        <v>1.5737099383174798E-2</v>
+        <v>1.35720173161716E-3</v>
       </c>
       <c r="F11">
-        <v>1.3650748470515099</v>
+        <v>1.36561557316155</v>
       </c>
       <c r="G11">
-        <v>1.2589958922203499E-2</v>
+        <v>1.1747450384018E-3</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="0"/>
-        <v>1.0048750533338346</v>
+        <v>1.0033956670138846</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>1.4879770666968438E-2</v>
+        <v>1.3214505512160488E-3</v>
       </c>
       <c r="K11"/>
       <c r="L11">
-        <v>1.3619357177992399</v>
+        <v>1.3591069629303201</v>
       </c>
       <c r="M11">
-        <v>1.14642500606108E-3</v>
+        <v>1.19600014120634E-3</v>
       </c>
       <c r="N11">
-        <v>1.36351969550464</v>
+        <v>1.35936350736381</v>
       </c>
       <c r="O11">
-        <v>1.0122047275674399E-3</v>
+        <v>1.67778722661321E-3</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" si="1"/>
-        <v>1.0011630341173221</v>
+        <v>1.0001887595608641</v>
       </c>
       <c r="Q11">
         <f t="shared" si="3"/>
-        <v>1.1236427897777903E-3</v>
+        <v>1.5161165627240361E-3</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -7643,45 +7645,45 @@
       </c>
       <c r="B12" s="4"/>
       <c r="D12">
-        <v>1.3545568399108701</v>
+        <v>1.3547132810815301</v>
       </c>
       <c r="E12">
-        <v>1.6297468246439701E-2</v>
+        <v>1.4726289986260401E-3</v>
       </c>
       <c r="F12">
-        <v>1.3518412407186999</v>
+        <v>1.36341460999829</v>
       </c>
       <c r="G12">
-        <v>1.40724264166723E-2</v>
+        <v>1.4008126144078501E-3</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="0"/>
-        <v>0.9979952120781076</v>
+        <v>1.0064230040690332</v>
       </c>
       <c r="I12">
         <f t="shared" si="2"/>
-        <v>1.5877958663557092E-2</v>
+        <v>1.505357873796738E-3</v>
       </c>
       <c r="J12" s="3"/>
       <c r="L12">
-        <v>1.35524292294785</v>
+        <v>1.3486259679520101</v>
       </c>
       <c r="M12">
-        <v>9.843423979622231E-4</v>
+        <v>1.4224880114464199E-3</v>
       </c>
       <c r="N12">
-        <v>1.35608844560886</v>
+        <v>1.3533887405196801</v>
       </c>
       <c r="O12">
-        <v>1.04376153989015E-3</v>
+        <v>1.2958061153248699E-3</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" si="1"/>
-        <v>1.0006238901134941</v>
+        <v>1.0035315741212536</v>
       </c>
       <c r="Q12">
         <f t="shared" si="3"/>
-        <v>1.0589413837370333E-3</v>
+        <v>1.4295491548200695E-3</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -7690,45 +7692,45 @@
       </c>
       <c r="B13" s="4"/>
       <c r="D13">
-        <v>1.34755153312925</v>
+        <v>1.3468248513376599</v>
       </c>
       <c r="E13">
-        <v>1.50714507765111E-2</v>
+        <v>1.45615044289173E-3</v>
       </c>
       <c r="F13">
-        <v>1.36244210029811</v>
+        <v>1.3513946956479299</v>
       </c>
       <c r="G13">
-        <v>1.27279533228061E-2</v>
+        <v>1.14533435975163E-3</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="0"/>
-        <v>1.011050091074648</v>
+        <v>1.0033930501844626</v>
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
-        <v>1.4733684895401899E-2</v>
+        <v>1.3784244221301813E-3</v>
       </c>
       <c r="J13" s="3"/>
       <c r="L13">
-        <v>1.3391565484202601</v>
+        <v>1.3366107593110099</v>
       </c>
       <c r="M13">
-        <v>3.4513629910370401E-3</v>
+        <v>1.1588900508539501E-3</v>
       </c>
       <c r="N13">
-        <v>1.3448593643039499</v>
+        <v>1.34013483199158</v>
       </c>
       <c r="O13">
-        <v>3.5460245721196499E-3</v>
+        <v>1.4207730259459101E-3</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" si="1"/>
-        <v>1.0042585132338837</v>
+        <v>1.0026365736292491</v>
       </c>
       <c r="Q13">
         <f t="shared" si="3"/>
-        <v>3.7027899524461018E-3</v>
+        <v>1.3731787771009375E-3</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -7738,45 +7740,45 @@
       <c r="B14" s="4"/>
       <c r="C14"/>
       <c r="D14">
-        <v>1.31707186586173</v>
+        <v>1.3240510132155701</v>
       </c>
       <c r="E14">
-        <v>1.8033196660722998E-2</v>
+        <v>9.8796030501752401E-4</v>
       </c>
       <c r="F14">
-        <v>1.3344012029371599</v>
+        <v>1.33154001082768</v>
       </c>
       <c r="G14">
-        <v>1.0229483755041201E-2</v>
+        <v>1.0862969111495599E-3</v>
       </c>
       <c r="H14" s="7">
         <f t="shared" si="0"/>
-        <v>1.0131574726669086</v>
+        <v>1.0056561246790048</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>1.5898337852427311E-2</v>
+        <v>1.1118410400524582E-3</v>
       </c>
       <c r="K14"/>
       <c r="L14">
-        <v>1.3112710657587101</v>
+        <v>1.30722047006895</v>
       </c>
       <c r="M14">
-        <v>2.67520556095646E-3</v>
+        <v>1.29401515382388E-3</v>
       </c>
       <c r="N14">
-        <v>1.3096995917960299</v>
+        <v>1.3151584403271299</v>
       </c>
       <c r="O14">
-        <v>2.9409916078694401E-3</v>
+        <v>1.2557754907824E-3</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" si="1"/>
-        <v>0.99880156437237411</v>
+        <v>1.0060724035768513</v>
       </c>
       <c r="Q14">
         <f t="shared" si="3"/>
-        <v>3.030295719604469E-3</v>
+        <v>1.3837178252034666E-3</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -7785,45 +7787,45 @@
       </c>
       <c r="B15" s="4"/>
       <c r="D15">
-        <v>1.28457233028475</v>
+        <v>1.2813997486989701</v>
       </c>
       <c r="E15">
-        <v>1.0625495333578599E-2</v>
+        <v>1.7413146739448299E-3</v>
       </c>
       <c r="F15">
-        <v>1.3082572247633499</v>
+        <v>1.2921959688761</v>
       </c>
       <c r="G15">
-        <v>1.23666556549391E-2</v>
+        <v>1.47528947786596E-3</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="0"/>
-        <v>1.0184379609619567</v>
+        <v>1.0084253334590485</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
-        <v>1.2792431657530358E-2</v>
+        <v>1.7898094809989675E-3</v>
       </c>
       <c r="J15" s="3"/>
       <c r="L15">
-        <v>1.2563576950633499</v>
+        <v>1.2475103334797899</v>
       </c>
       <c r="M15">
-        <v>2.5050181564410701E-3</v>
+        <v>1.7483187944625899E-3</v>
       </c>
       <c r="N15">
-        <v>1.2497624884637799</v>
+        <v>1.25845783185625</v>
       </c>
       <c r="O15">
-        <v>2.6845051290129399E-3</v>
+        <v>1.6525826585459999E-3</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" si="1"/>
-        <v>0.99475053432196514</v>
+        <v>1.0087754771104167</v>
       </c>
       <c r="Q15">
         <f t="shared" si="3"/>
-        <v>2.9153977252420692E-3</v>
+        <v>1.9373993710566338E-3</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -7833,45 +7835,45 @@
       <c r="B16" s="4"/>
       <c r="C16"/>
       <c r="D16">
-        <v>1.2590558964513201</v>
+        <v>1.2411843638183799</v>
       </c>
       <c r="E16">
-        <v>1.6651460486491101E-2</v>
+        <v>1.47544283326764E-3</v>
       </c>
       <c r="F16">
-        <v>1.2546600993330701</v>
+        <v>1.2526197352142801</v>
       </c>
       <c r="G16">
-        <v>1.314485012796E-2</v>
+        <v>1.37557999364616E-3</v>
       </c>
       <c r="H16" s="7">
         <f t="shared" si="0"/>
-        <v>0.9965086561044354</v>
+        <v>1.0092132738126995</v>
       </c>
       <c r="I16">
         <f t="shared" si="2"/>
-        <v>1.6813371889030006E-2</v>
+        <v>1.6332608585574488E-3</v>
       </c>
       <c r="K16"/>
       <c r="L16">
-        <v>1.20021968581256</v>
+        <v>1.19470771257209</v>
       </c>
       <c r="M16">
-        <v>2.9794094197858E-3</v>
+        <v>1.57262330104692E-3</v>
       </c>
       <c r="N16">
-        <v>1.20221749175355</v>
+        <v>1.2048284270919001</v>
       </c>
       <c r="O16">
-        <v>2.7545952721865301E-3</v>
+        <v>1.34046299939426E-3</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" si="1"/>
-        <v>1.0016645335554861</v>
+        <v>1.0084712891808669</v>
       </c>
       <c r="Q16">
         <f t="shared" si="3"/>
-        <v>3.3838068565250718E-3</v>
+        <v>1.7381247050213394E-3</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -7880,3563 +7882,3116 @@
       </c>
       <c r="B17" s="4"/>
       <c r="D17">
-        <v>1.22750944273163</v>
+        <v>1.2104169038614301</v>
       </c>
       <c r="E17">
-        <v>1.30680187336338E-2</v>
+        <v>1.4188935052501001E-3</v>
       </c>
       <c r="F17">
-        <v>1.19693876892553</v>
+        <v>1.2186080271138</v>
       </c>
       <c r="G17">
-        <v>1.11150087961693E-2</v>
+        <v>1.2526044597517001E-3</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="0"/>
-        <v>0.97509536567142829</v>
+        <v>1.0067671917223222</v>
       </c>
       <c r="I17">
         <f>H17*((E17/D17)^2 +(G17/F17)^2)^0.5</f>
-        <v>1.377509712299383E-2</v>
+        <v>1.5696238500205091E-3</v>
       </c>
       <c r="J17" s="3"/>
       <c r="L17">
-        <v>1.1566240021210601</v>
+        <v>1.15260452976926</v>
       </c>
       <c r="M17">
-        <v>2.5884299434418999E-3</v>
+        <v>1.2188214945693099E-3</v>
       </c>
       <c r="N17">
-        <v>1.1524770375920901</v>
+        <v>1.15702983820913</v>
       </c>
       <c r="O17">
-        <v>3.9762001692155704E-3</v>
+        <v>1.10294900031489E-3</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" si="1"/>
-        <v>0.99641459582252734</v>
+        <v>1.003839398792538</v>
       </c>
       <c r="Q17">
         <f>P17*((M17/L17)^2 +(O17/N17)^2)^0.5</f>
-        <v>4.0976394678384738E-3</v>
-      </c>
+        <v>1.4291594730581141E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C19" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="14"/>
+      <c r="K20" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="17"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N21" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q21" s="19" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C22" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14"/>
-      <c r="K22" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
+      <c r="A22">
+        <v>0.1</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2">
+        <v>3.4733623076722298E-5</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.30389231676172E-8</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2.1160368287330199E-5</v>
+      </c>
+      <c r="G22" s="2">
+        <v>2.0927702439166299E-7</v>
+      </c>
+      <c r="H22" s="13">
+        <f t="shared" ref="H22:H34" si="4">F22/D22</f>
+        <v>0.60921857304058236</v>
+      </c>
+      <c r="I22">
+        <f>H22*((E22/D22)^2 +(G22/F22)^2)^0.5</f>
+        <v>6.0295387816750243E-3</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2">
+        <v>3.03395026477764E-5</v>
+      </c>
+      <c r="M22" s="2">
+        <v>6.6974630812900604E-9</v>
+      </c>
+      <c r="N22" s="2">
+        <v>2.4120768187342001E-5</v>
+      </c>
+      <c r="O22" s="2">
+        <v>1.9145364499554299E-7</v>
+      </c>
+      <c r="P22" s="7">
+        <f t="shared" ref="P22:P34" si="5">N22/L22</f>
+        <v>0.79502846395901039</v>
+      </c>
+      <c r="Q22">
+        <f>P22*((M22/L22)^2 +(O22/N22)^2)^0.5</f>
+        <v>6.3128152538764219E-3</v>
+      </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N23" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P23" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q23" s="19" t="s">
-        <v>12</v>
+      <c r="A23">
+        <v>0.5</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="D23">
+        <v>1.73404176042568E-4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>6.8621557155502793E-8</v>
+      </c>
+      <c r="F23">
+        <v>1.07555014384114E-4</v>
+      </c>
+      <c r="G23" s="2">
+        <v>5.7726857720944404E-7</v>
+      </c>
+      <c r="H23" s="13">
+        <f t="shared" si="4"/>
+        <v>0.6202561947395715</v>
+      </c>
+      <c r="I23">
+        <f t="shared" ref="I23:I33" si="6">H23*((E23/D23)^2 +(G23/F23)^2)^0.5</f>
+        <v>3.3380716719281452E-3</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="L23">
+        <v>1.5160590000534599E-4</v>
+      </c>
+      <c r="M23" s="2">
+        <v>3.4761339275604597E-8</v>
+      </c>
+      <c r="N23">
+        <v>1.21086023080386E-4</v>
+      </c>
+      <c r="O23" s="2">
+        <v>4.68863518091893E-7</v>
+      </c>
+      <c r="P23" s="7">
+        <f t="shared" si="5"/>
+        <v>0.79868938528194633</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" ref="Q23:Q33" si="7">P23*((M23/L23)^2 +(O23/N23)^2)^0.5</f>
+        <v>3.0980641245473535E-3</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2">
-        <v>3.3571202768168298E-5</v>
+      <c r="D24">
+        <v>3.4620055489565998E-4</v>
       </c>
       <c r="E24" s="2">
-        <v>9.9159126214562193E-7</v>
-      </c>
-      <c r="F24" s="2">
-        <v>5.9169040069373203E-6</v>
+        <v>1.2197857023302799E-7</v>
+      </c>
+      <c r="F24">
+        <v>2.1378624402059899E-4</v>
       </c>
       <c r="G24" s="2">
-        <v>1.2392053149366401E-6</v>
+        <v>5.2379806742420601E-7</v>
       </c>
       <c r="H24" s="13">
-        <f t="shared" ref="H24:H36" si="4">F24/D24</f>
-        <v>0.17624938992497577</v>
+        <f t="shared" si="4"/>
+        <v>0.61752137885807601</v>
       </c>
       <c r="I24">
-        <f>H24*((E24/D24)^2 +(G24/F24)^2)^0.5</f>
-        <v>3.7278036250492967E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.5285542650612621E-3</v>
       </c>
       <c r="J24" s="3"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2">
-        <v>3.0213736630210799E-5</v>
+      <c r="L24">
+        <v>3.0294258379583801E-4</v>
       </c>
       <c r="M24" s="2">
-        <v>6.2814290600429797E-9</v>
-      </c>
-      <c r="N24" s="2">
-        <v>2.5899175434190999E-5</v>
+        <v>6.6476745692023094E-8</v>
+      </c>
+      <c r="N24">
+        <v>2.40896197376749E-4</v>
       </c>
       <c r="O24" s="2">
-        <v>2.22045923443069E-7</v>
+        <v>9.0505031340599802E-7</v>
       </c>
       <c r="P24" s="7">
-        <f t="shared" ref="P24:P36" si="5">N24/L24</f>
-        <v>0.85719868916492581</v>
+        <f t="shared" si="5"/>
+        <v>0.79518763707084539</v>
       </c>
       <c r="Q24">
-        <f>P24*((M24/L24)^2 +(O24/N24)^2)^0.5</f>
-        <v>7.3513316350502867E-3</v>
+        <f t="shared" si="7"/>
+        <v>2.9926223455543194E-3</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="D25" s="2">
-        <v>1.67215009194801E-4</v>
+      <c r="D25">
+        <v>3.3406484225683799E-3</v>
       </c>
       <c r="E25" s="2">
-        <v>6.3599673665714699E-6</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1.3827343157759201E-4</v>
+        <v>4.6993656095804102E-6</v>
+      </c>
+      <c r="F25">
+        <v>2.1299612386191098E-3</v>
       </c>
       <c r="G25" s="2">
-        <v>3.1803156900076102E-5</v>
+        <v>7.9830127854263004E-6</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="4"/>
-        <v>0.82691997712063736</v>
+        <v>0.63758916509434371</v>
       </c>
       <c r="I25">
-        <f t="shared" ref="I25:I35" si="6">H25*((E25/D25)^2 +(G25/F25)^2)^0.5</f>
-        <v>0.19277618205248812</v>
+        <f t="shared" si="6"/>
+        <v>2.5524346806044579E-3</v>
       </c>
       <c r="J25" s="3"/>
       <c r="L25">
-        <v>1.50989540407932E-4</v>
+        <v>2.9840640787729901E-3</v>
       </c>
       <c r="M25" s="2">
-        <v>4.1276616778068897E-8</v>
+        <v>2.3224778044521701E-6</v>
       </c>
       <c r="N25">
-        <v>1.3026224043386099E-4</v>
+        <v>2.3975720973108401E-3</v>
       </c>
       <c r="O25" s="2">
-        <v>5.73466194555137E-7</v>
+        <v>5.9219411899510302E-6</v>
       </c>
       <c r="P25" s="7">
         <f t="shared" si="5"/>
-        <v>0.86272360378029123</v>
+        <v>0.80345865035736497</v>
       </c>
       <c r="Q25">
-        <f t="shared" ref="Q25:Q35" si="7">P25*((M25/L25)^2 +(O25/N25)^2)^0.5</f>
-        <v>3.8053680353437123E-3</v>
+        <f t="shared" si="7"/>
+        <v>2.0807117833009201E-3</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="D26" s="2">
-        <v>3.4693843594753001E-4</v>
+      <c r="D26">
+        <v>7.9773077049013E-3</v>
       </c>
       <c r="E26" s="2">
-        <v>8.7539530299504897E-6</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1.85975024551348E-4</v>
+        <v>3.0966508168675198E-5</v>
+      </c>
+      <c r="F26">
+        <v>5.2812649215518096E-3</v>
       </c>
       <c r="G26" s="2">
-        <v>3.83737519740559E-5</v>
+        <v>3.8471504916950201E-5</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0.53604618365050316</v>
+        <v>0.66203600474217295</v>
       </c>
       <c r="I26">
         <f t="shared" si="6"/>
-        <v>0.11143071864844456</v>
+        <v>5.4646194580225092E-3</v>
       </c>
       <c r="J26" s="3"/>
       <c r="L26">
-        <v>3.0170617519809301E-4</v>
+        <v>7.2878020288280601E-3</v>
       </c>
       <c r="M26" s="2">
-        <v>8.1667143013063195E-8</v>
+        <v>1.7978747934444101E-5</v>
       </c>
       <c r="N26">
-        <v>2.6089565621297098E-4</v>
+        <v>5.9095502749599797E-3</v>
       </c>
       <c r="O26" s="2">
-        <v>6.2257504496774401E-7</v>
+        <v>3.18696827410922E-5</v>
       </c>
       <c r="P26" s="7">
         <f t="shared" si="5"/>
-        <v>0.86473422707265823</v>
+        <v>0.81088238286163838</v>
       </c>
       <c r="Q26">
         <f t="shared" si="7"/>
-        <v>2.0767475932791379E-3</v>
+        <v>4.8088408512878518E-3</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="D27" s="2">
-        <v>3.2447100360010698E-3</v>
+      <c r="D27">
+        <v>1.4888786588183199E-2</v>
       </c>
       <c r="E27" s="2">
-        <v>9.6341313668401696E-5</v>
-      </c>
-      <c r="F27" s="2">
-        <v>2.1820625389591202E-3</v>
+        <v>4.0982429834026501E-5</v>
+      </c>
+      <c r="F27">
+        <v>1.04976634277032E-2</v>
       </c>
       <c r="G27" s="2">
-        <v>2.65966276223607E-4</v>
+        <v>4.5047478405430597E-5</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="4"/>
-        <v>0.67249847128047058</v>
+        <v>0.70507179114481311</v>
       </c>
       <c r="I27">
         <f t="shared" si="6"/>
-        <v>8.4366214657354846E-2</v>
+        <v>3.5945499258486073E-3</v>
       </c>
       <c r="J27" s="3"/>
       <c r="L27">
-        <v>2.97750983471892E-3</v>
+        <v>1.41015088967267E-2</v>
       </c>
       <c r="M27" s="2">
-        <v>2.7512545520394498E-6</v>
+        <v>3.2103914470105902E-5</v>
       </c>
       <c r="N27">
-        <v>2.5949076799098498E-3</v>
+        <v>1.16904696591282E-2</v>
       </c>
       <c r="O27" s="2">
-        <v>5.6804576370084801E-6</v>
+        <v>3.9763991456282801E-5</v>
       </c>
       <c r="P27" s="7">
         <f t="shared" si="5"/>
-        <v>0.87150263943790185</v>
+        <v>0.82902260635681613</v>
       </c>
       <c r="Q27">
         <f t="shared" si="7"/>
-        <v>2.0707798442735998E-3</v>
+        <v>3.3931826596209033E-3</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="D28" s="2">
-        <v>8.1578715103711296E-3</v>
+      <c r="D28">
+        <v>2.1127279055374901E-2</v>
       </c>
       <c r="E28" s="2">
-        <v>2.7906538103478998E-4</v>
-      </c>
-      <c r="F28" s="2">
-        <v>5.02039478133323E-3</v>
+        <v>6.9218675953497698E-5</v>
+      </c>
+      <c r="F28">
+        <v>1.5410505689665401E-2</v>
       </c>
       <c r="G28" s="2">
-        <v>3.0805666033860603E-4</v>
+        <v>5.7019554655065601E-5</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="4"/>
-        <v>0.61540498338945215</v>
+        <v>0.7294127014308962</v>
       </c>
       <c r="I28">
         <f t="shared" si="6"/>
-        <v>4.323355798647284E-2</v>
+        <v>3.6048248029861962E-3</v>
       </c>
       <c r="J28" s="3"/>
       <c r="L28">
-        <v>7.2854691465075302E-3</v>
+        <v>2.0589600884999198E-2</v>
       </c>
       <c r="M28" s="2">
-        <v>1.0595331155121401E-5</v>
+        <v>5.0929027162677503E-5</v>
       </c>
       <c r="N28">
-        <v>6.4419405380797103E-3</v>
+        <v>1.7231690318885801E-2</v>
       </c>
       <c r="O28" s="2">
-        <v>3.0640812604159097E-5</v>
+        <v>7.9317497610751093E-5</v>
       </c>
       <c r="P28" s="7">
         <f t="shared" si="5"/>
-        <v>0.8842176678721938</v>
+        <v>0.83691230418362095</v>
       </c>
       <c r="Q28">
         <f t="shared" si="7"/>
-        <v>4.3979408323316831E-3</v>
+        <v>4.3732957749830943E-3</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="D29" s="2">
-        <v>1.49266627971049E-2</v>
+      <c r="D29">
+        <v>2.6938831195993999E-2</v>
       </c>
       <c r="E29" s="2">
-        <v>4.9518780486686295E-4</v>
-      </c>
-      <c r="F29" s="2">
-        <v>1.0162125213435E-2</v>
+        <v>5.92615592377973E-5</v>
+      </c>
+      <c r="F29">
+        <v>2.0442040454458198E-2</v>
       </c>
       <c r="G29" s="2">
-        <v>5.80825745840268E-4</v>
+        <v>6.7768751133343504E-5</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="4"/>
-        <v>0.680803562830266</v>
+        <v>0.75883175130100222</v>
       </c>
       <c r="I29">
         <f t="shared" si="6"/>
-        <v>4.4991600045113711E-2</v>
+        <v>3.0191293561420119E-3</v>
       </c>
       <c r="J29" s="3"/>
       <c r="L29">
-        <v>1.4085686693042001E-2</v>
+        <v>2.6787777537410701E-2</v>
       </c>
       <c r="M29" s="2">
-        <v>2.6440325603855101E-5</v>
+        <v>5.6311212680318198E-5</v>
       </c>
       <c r="N29">
-        <v>1.26690225425122E-2</v>
+        <v>2.2886137354832501E-2</v>
       </c>
       <c r="O29" s="2">
-        <v>3.9839492384589098E-5</v>
+        <v>7.3233726308046104E-5</v>
       </c>
       <c r="P29" s="7">
         <f t="shared" si="5"/>
-        <v>0.89942526896969821</v>
+        <v>0.85434998565560982</v>
       </c>
       <c r="Q29">
         <f t="shared" si="7"/>
-        <v>3.2939448706370833E-3</v>
+        <v>3.270987741553931E-3</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="D30" s="2">
-        <v>2.1432078952745001E-2</v>
+      <c r="D30">
+        <v>3.7562773914964001E-2</v>
       </c>
       <c r="E30" s="2">
-        <v>5.7708761237754895E-4</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1.65555585699587E-2</v>
+        <v>8.7101865481060996E-5</v>
+      </c>
+      <c r="F30">
+        <v>2.9879593597708899E-2</v>
       </c>
       <c r="G30" s="2">
-        <v>8.4894750486791501E-4</v>
+        <v>8.6284137744803305E-5</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="4"/>
-        <v>0.77246629253567023</v>
+        <v>0.79545758961655577</v>
       </c>
       <c r="I30">
         <f t="shared" si="6"/>
-        <v>4.473995917320344E-2</v>
+        <v>2.9459831002593344E-3</v>
       </c>
       <c r="J30" s="3"/>
       <c r="L30">
-        <v>2.04540679886334E-2</v>
+        <v>3.8388966155989197E-2</v>
       </c>
       <c r="M30" s="2">
-        <v>4.0017362438723199E-5</v>
+        <v>7.9638315518280094E-5</v>
       </c>
       <c r="N30">
-        <v>1.8873120984925901E-2</v>
+        <v>3.3439756797986601E-2</v>
       </c>
       <c r="O30" s="2">
-        <v>3.9932428547215201E-5</v>
+        <v>9.2508457557128094E-5</v>
       </c>
       <c r="P30" s="7">
         <f t="shared" si="5"/>
-        <v>0.92270745337377136</v>
+        <v>0.87107729502555376</v>
       </c>
       <c r="Q30">
         <f t="shared" si="7"/>
-        <v>2.6590083093148533E-3</v>
+        <v>3.0120489033709811E-3</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="D31" s="2">
-        <v>2.7913216674849899E-2</v>
-      </c>
-      <c r="E31" s="2">
-        <v>6.6669793207153904E-4</v>
-      </c>
-      <c r="F31" s="2">
-        <v>2.0339611754264599E-2</v>
-      </c>
-      <c r="G31" s="2">
-        <v>7.3633525085197403E-4</v>
+      <c r="D31">
+        <v>5.5951441895259801E-2</v>
+      </c>
+      <c r="E31">
+        <v>1.22026544952069E-4</v>
+      </c>
+      <c r="F31">
+        <v>4.72133832852187E-2</v>
+      </c>
+      <c r="G31">
+        <v>1.02719911855704E-4</v>
       </c>
       <c r="H31" s="13">
         <f t="shared" si="4"/>
-        <v>0.72867315835336177</v>
+        <v>0.84382782080221264</v>
       </c>
       <c r="I31">
         <f t="shared" si="6"/>
-        <v>3.1603458194463079E-2</v>
+        <v>2.5994756291734564E-3</v>
       </c>
       <c r="J31" s="3"/>
       <c r="L31">
-        <v>2.6686341725694201E-2</v>
+        <v>5.92508857062954E-2</v>
       </c>
       <c r="M31" s="2">
-        <v>4.6488373284998899E-5</v>
+        <v>8.1216551004011802E-5</v>
       </c>
       <c r="N31">
-        <v>2.4681477633588599E-2</v>
-      </c>
-      <c r="O31" s="2">
-        <v>4.3554638662226E-5</v>
+        <v>5.31845879286095E-2</v>
+      </c>
+      <c r="O31">
+        <v>1.27660413881626E-4</v>
       </c>
       <c r="P31" s="7">
         <f t="shared" si="5"/>
-        <v>0.92487302633259483</v>
+        <v>0.89761675786997808</v>
       </c>
       <c r="Q31">
         <f t="shared" si="7"/>
-        <v>2.2933719536386309E-3</v>
+        <v>2.4811355128425004E-3</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="D32" s="2">
-        <v>3.6427579453755798E-2</v>
-      </c>
-      <c r="E32" s="2">
-        <v>1.0472429250006801E-3</v>
-      </c>
-      <c r="F32" s="2">
-        <v>2.9873697265033802E-2</v>
-      </c>
-      <c r="G32" s="2">
-        <v>8.5514874767622401E-4</v>
+      <c r="D32">
+        <v>9.4555187534606303E-2</v>
+      </c>
+      <c r="E32">
+        <v>2.0538142419059999E-4</v>
+      </c>
+      <c r="F32">
+        <v>8.5541163711055898E-2</v>
+      </c>
+      <c r="G32">
+        <v>1.76730090656541E-4</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="4"/>
-        <v>0.8200846093262375</v>
+        <v>0.90466917724369844</v>
       </c>
       <c r="I32">
         <f t="shared" si="6"/>
-        <v>3.327059479181485E-2</v>
+        <v>2.7119540652458946E-3</v>
       </c>
       <c r="J32" s="3"/>
       <c r="L32">
-        <v>3.7924637387248702E-2</v>
+        <v>0.102657381127848</v>
       </c>
       <c r="M32">
-        <v>1.8428567575269999E-4</v>
+        <v>1.7911241504214699E-4</v>
       </c>
       <c r="N32">
-        <v>3.6134840661020101E-2</v>
+        <v>9.6047540913006504E-2</v>
       </c>
       <c r="O32">
-        <v>2.42482884021072E-4</v>
+        <v>1.98888364809949E-4</v>
       </c>
       <c r="P32" s="7">
         <f t="shared" si="5"/>
-        <v>0.95280649072651702</v>
+        <v>0.93561261604161028</v>
       </c>
       <c r="Q32">
         <f t="shared" si="7"/>
-        <v>7.8941171734471308E-3</v>
+        <v>2.5334379936179344E-3</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="D33" s="2">
-        <v>5.53819360171761E-2</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1.4584466490748199E-3</v>
-      </c>
-      <c r="F33" s="2">
-        <v>4.6882404518702597E-2</v>
-      </c>
-      <c r="G33" s="2">
-        <v>9.0297433456597396E-4</v>
+      <c r="D33">
+        <v>0.12642175357316501</v>
+      </c>
+      <c r="E33">
+        <v>1.90477545095321E-4</v>
+      </c>
+      <c r="F33">
+        <v>0.11811105475446</v>
+      </c>
+      <c r="G33">
+        <v>2.1338189128953199E-4</v>
       </c>
       <c r="H33" s="13">
         <f t="shared" si="4"/>
-        <v>0.84652881228569787</v>
+        <v>0.93426211404435788</v>
       </c>
       <c r="I33">
         <f t="shared" si="6"/>
-        <v>2.7618912628068853E-2</v>
+        <v>2.1977954537779378E-3</v>
       </c>
       <c r="J33" s="3"/>
       <c r="L33">
-        <v>5.9331126295057199E-2</v>
+        <v>0.13878044422879701</v>
       </c>
       <c r="M33">
-        <v>2.7677924057614001E-4</v>
+        <v>2.6306120381277501E-4</v>
       </c>
       <c r="N33">
-        <v>5.7361502212218099E-2</v>
+        <v>0.13176179016360301</v>
       </c>
       <c r="O33">
-        <v>2.3849126374357799E-4</v>
+        <v>1.9611456455849799E-4</v>
       </c>
       <c r="P33" s="7">
         <f t="shared" si="5"/>
-        <v>0.96680285364811647</v>
+        <v>0.94942620263109356</v>
       </c>
       <c r="Q33">
         <f t="shared" si="7"/>
-        <v>6.041436975368881E-3</v>
+        <v>2.2881645006526826E-3</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>500</v>
+        <v>999.99</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="D34" s="2">
-        <v>9.4183377970993604E-2</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1.5799693791771401E-3</v>
-      </c>
-      <c r="F34" s="2">
-        <v>8.9405221334390397E-2</v>
-      </c>
-      <c r="G34" s="2">
-        <v>1.70807591224624E-3</v>
+      <c r="D34">
+        <v>0.155598782023254</v>
+      </c>
+      <c r="E34">
+        <v>2.5210481083492401E-4</v>
+      </c>
+      <c r="F34">
+        <v>0.14698039737697199</v>
+      </c>
+      <c r="G34">
+        <v>2.5258738046347602E-4</v>
       </c>
       <c r="H34" s="13">
         <f t="shared" si="4"/>
-        <v>0.94926751684278332</v>
+        <v>0.94461149030720559</v>
       </c>
       <c r="I34">
-        <f t="shared" si="6"/>
-        <v>2.4134786583998237E-2</v>
+        <f>H34*((E34/D34)^2 +(G34/F34)^2)^0.5</f>
+        <v>2.2310442130252868E-3</v>
       </c>
       <c r="J34" s="3"/>
       <c r="L34">
-        <v>0.102482458976092</v>
+        <v>0.170245597165261</v>
       </c>
       <c r="M34">
-        <v>2.9595828587883197E-4</v>
+        <v>2.4604975183776102E-4</v>
       </c>
       <c r="N34">
-        <v>0.102092586065974</v>
+        <v>0.162634818769124</v>
       </c>
       <c r="O34">
-        <v>4.88706826404386E-4</v>
+        <v>2.6397948509944901E-4</v>
       </c>
       <c r="P34" s="7">
         <f t="shared" si="5"/>
-        <v>0.996195710817117</v>
+        <v>0.95529529971486393</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="7"/>
-        <v>5.5692878927237057E-3</v>
+        <f>P34*((M34/L34)^2 +(O34/N34)^2)^0.5</f>
+        <v>2.0761752123647477E-3</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>750</v>
-      </c>
       <c r="B35" s="4"/>
-      <c r="D35" s="2">
-        <v>0.12938440937586501</v>
-      </c>
-      <c r="E35" s="2">
-        <v>2.1442760752734399E-3</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0.117827003366891</v>
-      </c>
-      <c r="G35" s="2">
-        <v>2.1418785805969601E-3</v>
-      </c>
-      <c r="H35" s="13">
-        <f t="shared" si="4"/>
-        <v>0.91067388980847419</v>
-      </c>
-      <c r="I35">
-        <f t="shared" si="6"/>
-        <v>2.2401595997311816E-2</v>
-      </c>
+      <c r="H35" s="13"/>
       <c r="J35" s="3"/>
-      <c r="L35">
-        <v>0.13877899849488601</v>
-      </c>
-      <c r="M35">
-        <v>4.2009114228035198E-4</v>
-      </c>
-      <c r="N35">
-        <v>0.14105605143254499</v>
-      </c>
-      <c r="O35">
-        <v>6.4618904182841804E-4</v>
-      </c>
-      <c r="P35" s="7">
-        <f t="shared" si="5"/>
-        <v>1.0164077631511579</v>
-      </c>
-      <c r="Q35">
-        <f t="shared" si="7"/>
-        <v>5.5809331857695158E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>999.99</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="D36" s="2">
-        <v>0.15752496538125499</v>
-      </c>
-      <c r="E36" s="2">
-        <v>2.4554689207597698E-3</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0.14133786701866499</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1.8390528502879599E-3</v>
-      </c>
-      <c r="H36" s="13">
-        <f t="shared" si="4"/>
-        <v>0.897241060657194</v>
-      </c>
-      <c r="I36">
-        <f>H36*((E36/D36)^2 +(G36/F36)^2)^0.5</f>
-        <v>1.8218310636367537E-2</v>
-      </c>
-      <c r="J36" s="3"/>
-      <c r="L36">
-        <v>0.16969831628755799</v>
-      </c>
-      <c r="M36">
-        <v>6.3046734962274005E-4</v>
-      </c>
-      <c r="N36">
-        <v>0.17395996323018501</v>
-      </c>
-      <c r="O36">
-        <v>7.9326262337449101E-4</v>
-      </c>
-      <c r="P36" s="7">
-        <f t="shared" si="5"/>
-        <v>1.025113077347247</v>
-      </c>
-      <c r="Q36">
-        <f>P36*((M36/L36)^2 +(O36/N36)^2)^0.5</f>
-        <v>6.0296141732043276E-3</v>
-      </c>
+      <c r="P35" s="7"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="4"/>
-      <c r="H37" s="13"/>
-      <c r="J37" s="3"/>
-      <c r="P37" s="7"/>
+      <c r="C37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C38" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="14"/>
+      <c r="K38" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="17"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
+      <c r="A39" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M39" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N39" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P39" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q39" s="19" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C40" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="14"/>
-      <c r="K40" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L40" s="17"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
+      <c r="A40">
+        <v>0.1</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2">
+        <v>3.2099701190028201E-6</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3.5131059351727902E-10</v>
+      </c>
+      <c r="F40" s="2">
+        <v>3.17759079120563E-6</v>
+      </c>
+      <c r="G40" s="2">
+        <v>7.4892039905947602E-9</v>
+      </c>
+      <c r="H40" s="21">
+        <f t="shared" ref="H40:H52" si="8">F40/D40</f>
+        <v>0.98991288809652567</v>
+      </c>
+      <c r="I40">
+        <f>H40*((E40/D40)^2 +(G40/F40)^2)^0.5</f>
+        <v>2.3356211349544811E-3</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2">
+        <v>9.0972584130535695E-7</v>
+      </c>
+      <c r="M40" s="2">
+        <v>9.7452881785433401E-11</v>
+      </c>
+      <c r="N40" s="2">
+        <v>8.9914371527988803E-7</v>
+      </c>
+      <c r="O40" s="2">
+        <v>2.24423174811288E-9</v>
+      </c>
+      <c r="P40" s="7">
+        <f t="shared" ref="P40:P52" si="9">N40/L40</f>
+        <v>0.98836778560639249</v>
+      </c>
+      <c r="Q40">
+        <f>P40*((M40/L40)^2 +(O40/N40)^2)^0.5</f>
+        <v>2.4692029617883636E-3</v>
+      </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I41" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J41" s="6"/>
-      <c r="K41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L41" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N41" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O41" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P41" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q41" s="19" t="s">
-        <v>12</v>
+      <c r="A41">
+        <v>0.5</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="D41" s="2">
+        <v>1.6134855890052599E-5</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1.4663512326686101E-9</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.5981198165598299E-5</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1.4864419278170099E-8</v>
+      </c>
+      <c r="H41" s="21">
+        <f t="shared" si="8"/>
+        <v>0.99047665963046916</v>
+      </c>
+      <c r="I41">
+        <f t="shared" ref="I41:I51" si="10">H41*((E41/D41)^2 +(G41/F41)^2)^0.5</f>
+        <v>9.2564857174139148E-4</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="L41" s="2">
+        <v>4.5736608105268603E-6</v>
+      </c>
+      <c r="M41" s="2">
+        <v>4.4439460683920398E-10</v>
+      </c>
+      <c r="N41" s="2">
+        <v>4.5248201671970701E-6</v>
+      </c>
+      <c r="O41" s="2">
+        <v>4.3753358266758202E-9</v>
+      </c>
+      <c r="P41" s="7">
+        <f t="shared" si="9"/>
+        <v>0.98932132369383907</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" ref="Q41:Q51" si="11">P41*((M41/L41)^2 +(O41/N41)^2)^0.5</f>
+        <v>9.6145500722271619E-4</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="B42" s="4"/>
-      <c r="C42" s="2"/>
       <c r="D42" s="2">
-        <v>3.2508308570749199E-6</v>
+        <v>3.2313738532959303E-5</v>
       </c>
       <c r="E42" s="2">
-        <v>2.9879791871820602E-8</v>
+        <v>3.1962942854569601E-9</v>
       </c>
       <c r="F42" s="2">
-        <v>2.4077020934709801E-6</v>
+        <v>3.2065564782420801E-5</v>
       </c>
       <c r="G42" s="2">
-        <v>4.5116812236236001E-7</v>
-      </c>
-      <c r="H42" s="13">
-        <f t="shared" ref="H42:H54" si="8">F42/D42</f>
-        <v>0.74064206946694777</v>
+        <v>2.3626963147609399E-8</v>
+      </c>
+      <c r="H42" s="21">
+        <f t="shared" si="8"/>
+        <v>0.99231986882961964</v>
       </c>
       <c r="I42">
-        <f>H42*((E42/D42)^2 +(G42/F42)^2)^0.5</f>
-        <v>0.13895233886852032</v>
+        <f t="shared" si="10"/>
+        <v>7.3773278699735829E-4</v>
       </c>
       <c r="J42" s="3"/>
-      <c r="K42" s="2"/>
       <c r="L42" s="2">
-        <v>8.9904449370964804E-7</v>
+        <v>9.1603462828245198E-6</v>
       </c>
       <c r="M42" s="2">
-        <v>1.2821299860299399E-10</v>
+        <v>9.3941163470923E-10</v>
       </c>
       <c r="N42" s="2">
-        <v>9.7063326902119801E-7</v>
+        <v>9.0779232505914901E-6</v>
       </c>
       <c r="O42" s="2">
-        <v>2.34278184812804E-9</v>
+        <v>6.6276429568322101E-9</v>
       </c>
       <c r="P42" s="7">
-        <f t="shared" ref="P42:P54" si="9">N42/L42</f>
-        <v>1.0796276222283054</v>
+        <f t="shared" si="9"/>
+        <v>0.9910021925276371</v>
       </c>
       <c r="Q42">
-        <f>P42*((M42/L42)^2 +(O42/N42)^2)^0.5</f>
-        <v>2.6104020588503659E-3</v>
+        <f t="shared" si="11"/>
+        <v>7.3061732078473008E-4</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="B43" s="4"/>
-      <c r="D43" s="2">
-        <v>1.6123275821852999E-5</v>
+      <c r="D43">
+        <v>3.2313466424565402E-4</v>
       </c>
       <c r="E43" s="2">
-        <v>2.0263996088365101E-7</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.5829821996247301E-5</v>
+        <v>1.07210572664496E-7</v>
+      </c>
+      <c r="F43">
+        <v>3.2203551019660299E-4</v>
       </c>
       <c r="G43" s="2">
-        <v>1.9692674060295302E-6</v>
-      </c>
-      <c r="H43" s="13">
+        <v>2.0328657361107299E-7</v>
+      </c>
+      <c r="H43" s="21">
         <f t="shared" si="8"/>
-        <v>0.98179936702391701</v>
+        <v>0.9965984644463417</v>
       </c>
       <c r="I43">
-        <f t="shared" ref="I43:I53" si="10">H43*((E43/D43)^2 +(G43/F43)^2)^0.5</f>
-        <v>0.12275990292260608</v>
+        <f t="shared" si="10"/>
+        <v>7.1071026643292393E-4</v>
       </c>
       <c r="J43" s="3"/>
       <c r="L43" s="2">
-        <v>4.5212579889347804E-6</v>
+        <v>9.1589301211133205E-5</v>
       </c>
       <c r="M43" s="2">
-        <v>5.3867868502524305E-10</v>
+        <v>3.0347199669865102E-8</v>
       </c>
       <c r="N43" s="2">
-        <v>4.9130489454613299E-6</v>
+        <v>9.1214157329342301E-5</v>
       </c>
       <c r="O43" s="2">
-        <v>4.9708765251656597E-9</v>
+        <v>6.40943486895766E-8</v>
       </c>
       <c r="P43" s="7">
         <f t="shared" si="9"/>
-        <v>1.0866552975931498</v>
+        <v>0.99590406437400247</v>
       </c>
       <c r="Q43">
-        <f t="shared" ref="Q43:Q53" si="11">P43*((M43/L43)^2 +(O43/N43)^2)^0.5</f>
-        <v>1.1070421177898828E-3</v>
+        <f t="shared" si="11"/>
+        <v>7.736996230761808E-4</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="D44" s="2">
-        <v>3.1996604066933298E-5</v>
+      <c r="D44">
+        <v>8.0491667998632097E-4</v>
       </c>
       <c r="E44" s="2">
-        <v>4.1792496489736701E-7</v>
-      </c>
-      <c r="F44" s="2">
-        <v>3.2983010764906299E-5</v>
+        <v>9.736275950164889E-7</v>
+      </c>
+      <c r="F44">
+        <v>8.03016350656239E-4</v>
       </c>
       <c r="G44" s="2">
-        <v>2.2398843673895399E-6</v>
-      </c>
-      <c r="H44" s="13">
+        <v>1.71923510353115E-6</v>
+      </c>
+      <c r="H44" s="21">
         <f t="shared" si="8"/>
-        <v>1.030828480919711</v>
+        <v>0.99763909808638296</v>
       </c>
       <c r="I44">
         <f t="shared" si="10"/>
-        <v>7.1286878880722632E-2</v>
+        <v>2.4532373787551002E-3</v>
       </c>
       <c r="J44" s="3"/>
-      <c r="L44" s="2">
-        <v>9.0521934433886801E-6</v>
+      <c r="L44">
+        <v>2.2814984705325501E-4</v>
       </c>
       <c r="M44" s="2">
-        <v>1.0936079336944401E-9</v>
-      </c>
-      <c r="N44" s="2">
-        <v>9.8552203174057406E-6</v>
+        <v>3.1680978680584301E-7</v>
+      </c>
+      <c r="N44">
+        <v>2.2747099914478301E-4</v>
       </c>
       <c r="O44" s="2">
-        <v>8.7519244572112492E-9</v>
+        <v>5.1766354897946596E-7</v>
       </c>
       <c r="P44" s="7">
         <f t="shared" si="9"/>
-        <v>1.0887107504981077</v>
+        <v>0.99702455242797716</v>
       </c>
       <c r="Q44">
         <f t="shared" si="11"/>
-        <v>9.7573479056481415E-4</v>
+        <v>2.657998552514734E-3</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B45" s="4"/>
       <c r="D45">
-        <v>3.17520187164021E-4</v>
+        <v>1.6028552618401299E-3</v>
       </c>
       <c r="E45" s="2">
-        <v>3.5903642084798401E-6</v>
+        <v>1.94658668768657E-6</v>
       </c>
       <c r="F45">
-        <v>3.2190498140927299E-4</v>
+        <v>1.5995099007293299E-3</v>
       </c>
       <c r="G45" s="2">
-        <v>1.0083144680763101E-5</v>
-      </c>
-      <c r="H45" s="13">
+        <v>2.61096709145502E-6</v>
+      </c>
+      <c r="H45" s="21">
         <f t="shared" si="8"/>
-        <v>1.0138094975453857</v>
+        <v>0.99791287386300909</v>
       </c>
       <c r="I45">
         <f t="shared" si="10"/>
-        <v>3.3761722320914872E-2</v>
+        <v>2.0303219773658665E-3</v>
       </c>
       <c r="J45" s="3"/>
-      <c r="L45" s="2">
-        <v>9.05395895200175E-5</v>
+      <c r="L45">
+        <v>4.53914678418702E-4</v>
       </c>
       <c r="M45" s="2">
-        <v>3.0609885520008502E-8</v>
-      </c>
-      <c r="N45" s="2">
-        <v>9.9327854603406304E-5</v>
+        <v>6.4832174109510199E-7</v>
+      </c>
+      <c r="N45">
+        <v>4.515470476236E-4</v>
       </c>
       <c r="O45" s="2">
-        <v>9.6867588469887695E-8</v>
+        <v>8.0551677883601002E-7</v>
       </c>
       <c r="P45" s="7">
         <f t="shared" si="9"/>
-        <v>1.0970654398808137</v>
+        <v>0.99478397393239171</v>
       </c>
       <c r="Q45">
         <f t="shared" si="11"/>
-        <v>1.1323582189431058E-3</v>
+        <v>2.2733212468731513E-3</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B46" s="4"/>
       <c r="D46">
-        <v>8.1568502250048002E-4</v>
+        <v>2.3922480224080099E-3</v>
       </c>
       <c r="E46" s="2">
-        <v>5.3855794471320103E-6</v>
+        <v>2.30362531217378E-6</v>
       </c>
       <c r="F46">
-        <v>8.0308685347477604E-4</v>
+        <v>2.3832071578495199E-3</v>
       </c>
       <c r="G46" s="2">
-        <v>1.5815547986996E-5</v>
-      </c>
-      <c r="H46" s="13">
+        <v>2.9328311472635502E-6</v>
+      </c>
+      <c r="H46" s="21">
         <f t="shared" si="8"/>
-        <v>0.98455510561284509</v>
+        <v>0.99622076621077549</v>
       </c>
       <c r="I46">
         <f t="shared" si="10"/>
-        <v>2.044997390903704E-2</v>
+        <v>1.5566935117403559E-3</v>
       </c>
       <c r="J46" s="3"/>
       <c r="L46">
-        <v>2.25447641878588E-4</v>
+        <v>6.7626891461544203E-4</v>
       </c>
       <c r="M46" s="2">
-        <v>1.7922454183224899E-7</v>
+        <v>7.9860980174835503E-7</v>
       </c>
       <c r="N46">
-        <v>2.4682978389793902E-4</v>
+        <v>6.7325507529300901E-4</v>
       </c>
       <c r="O46" s="2">
-        <v>3.0793317165798302E-7</v>
+        <v>9.3889317052476902E-7</v>
       </c>
       <c r="P46" s="7">
         <f t="shared" si="9"/>
-        <v>1.0948430502141429</v>
+        <v>0.99554343064231066</v>
       </c>
       <c r="Q46">
         <f t="shared" si="11"/>
-        <v>1.6196160028921747E-3</v>
+        <v>1.8192394881123154E-3</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="B47" s="4"/>
       <c r="D47">
-        <v>1.60165101199415E-3</v>
+        <v>3.1688203926765E-3</v>
       </c>
       <c r="E47" s="2">
-        <v>1.68217601711865E-5</v>
+        <v>3.8700195546849801E-6</v>
       </c>
       <c r="F47">
-        <v>1.64322981589001E-3</v>
+        <v>3.1541405310738201E-3</v>
       </c>
       <c r="G47" s="2">
-        <v>2.5755780859259001E-5</v>
-      </c>
-      <c r="H47" s="13">
+        <v>5.7204379219245103E-6</v>
+      </c>
+      <c r="H47" s="21">
         <f t="shared" si="8"/>
-        <v>1.025959964801628</v>
+        <v>0.99536740496980936</v>
       </c>
       <c r="I47">
         <f t="shared" si="10"/>
-        <v>1.9357187123934069E-2</v>
+        <v>2.1763688947192732E-3</v>
       </c>
       <c r="J47" s="3"/>
       <c r="L47">
-        <v>4.4798082499880598E-4</v>
+        <v>8.9635371842954504E-4</v>
       </c>
       <c r="M47" s="2">
-        <v>2.3058578537097299E-7</v>
+        <v>1.0741074178410501E-6</v>
       </c>
       <c r="N47">
-        <v>4.9222836447885903E-4</v>
+        <v>8.9292512144540401E-4</v>
       </c>
       <c r="O47" s="2">
-        <v>6.1981830802032001E-7</v>
+        <v>1.5443417647520601E-6</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="9"/>
-        <v>1.098771056730321</v>
+        <v>0.99617495089979868</v>
       </c>
       <c r="Q47">
         <f t="shared" si="11"/>
-        <v>1.4947107742180631E-3</v>
+        <v>2.09604744411438E-3</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="B48" s="4"/>
       <c r="D48">
-        <v>2.3979320506641501E-3</v>
+        <v>4.7002672379747703E-3</v>
       </c>
       <c r="E48" s="2">
-        <v>3.1169443646373198E-5</v>
+        <v>5.5830943137030297E-6</v>
       </c>
       <c r="F48">
-        <v>2.3274282513085498E-3</v>
+        <v>4.6888544824096002E-3</v>
       </c>
       <c r="G48" s="2">
-        <v>3.8598219967931103E-5</v>
-      </c>
-      <c r="H48" s="13">
+        <v>6.9665355992869402E-6</v>
+      </c>
+      <c r="H48" s="21">
         <f t="shared" si="8"/>
-        <v>0.97059808290394511</v>
+        <v>0.99757189219520048</v>
       </c>
       <c r="I48">
         <f t="shared" si="10"/>
-        <v>2.0451571874940244E-2</v>
+        <v>1.8975971265847125E-3</v>
       </c>
       <c r="J48" s="3"/>
       <c r="L48">
-        <v>6.6839992871854095E-4</v>
+        <v>1.32567671857899E-3</v>
       </c>
       <c r="M48" s="2">
-        <v>5.4020479758105504E-7</v>
+        <v>1.5318368895278E-6</v>
       </c>
       <c r="N48">
-        <v>7.3347330304254701E-4</v>
+        <v>1.3245956550701E-3</v>
       </c>
       <c r="O48" s="2">
-        <v>5.1651453397623897E-7</v>
+        <v>2.0064771481250101E-6</v>
       </c>
       <c r="P48" s="7">
         <f t="shared" si="9"/>
-        <v>1.0973569438416384</v>
+        <v>0.99918451950333054</v>
       </c>
       <c r="Q48">
         <f t="shared" si="11"/>
-        <v>1.176323419733072E-3</v>
+        <v>1.9036453265773162E-3</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="B49" s="4"/>
       <c r="D49">
-        <v>3.1150452266862499E-3</v>
+        <v>7.6621384469752396E-3</v>
       </c>
       <c r="E49" s="2">
-        <v>3.0375204510835499E-5</v>
+        <v>8.9439539283184293E-6</v>
       </c>
       <c r="F49">
-        <v>3.1491175964614999E-3</v>
+        <v>7.6581425799841299E-3</v>
       </c>
       <c r="G49" s="2">
-        <v>3.7025405401571998E-5</v>
-      </c>
-      <c r="H49" s="13">
+        <v>9.5373623923301102E-6</v>
+      </c>
+      <c r="H49" s="21">
         <f t="shared" si="8"/>
-        <v>1.0109380016326426</v>
+        <v>0.99947849193553961</v>
       </c>
       <c r="I49">
         <f t="shared" si="10"/>
-        <v>1.5441915923900233E-2</v>
+        <v>1.7060261538065647E-3</v>
       </c>
       <c r="J49" s="3"/>
       <c r="L49">
-        <v>8.85793670637662E-4</v>
+        <v>2.1556137545463202E-3</v>
       </c>
       <c r="M49" s="2">
-        <v>9.8356058025338391E-7</v>
+        <v>2.8917617520134201E-6</v>
       </c>
       <c r="N49">
-        <v>9.7084534758771503E-4</v>
+        <v>2.1557775197990998E-3</v>
       </c>
       <c r="O49" s="2">
-        <v>9.6980794977708597E-7</v>
+        <v>3.4267184077591398E-6</v>
       </c>
       <c r="P49" s="7">
         <f t="shared" si="9"/>
-        <v>1.0960174810109293</v>
+        <v>1.0000759715196816</v>
       </c>
       <c r="Q49">
         <f t="shared" si="11"/>
-        <v>1.6369931020509556E-3</v>
+        <v>2.08013448905876E-3</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="B50" s="4"/>
       <c r="D50">
-        <v>4.6543407829659003E-3</v>
+        <v>1.4528827469945001E-2</v>
       </c>
       <c r="E50" s="2">
-        <v>4.7462851945895098E-5</v>
+        <v>1.9512128215526801E-5</v>
       </c>
       <c r="F50">
-        <v>4.6288384862751501E-3</v>
+        <v>1.4510294900252E-2</v>
       </c>
       <c r="G50" s="2">
-        <v>5.6491200849806098E-5</v>
-      </c>
-      <c r="H50" s="13">
+        <v>1.7632674389988701E-5</v>
+      </c>
+      <c r="H50" s="21">
         <f t="shared" si="8"/>
-        <v>0.99452075000952134</v>
+        <v>0.99872442771232994</v>
       </c>
       <c r="I50">
         <f t="shared" si="10"/>
-        <v>1.581669692140476E-2</v>
+        <v>1.808850802137127E-3</v>
       </c>
       <c r="J50" s="3"/>
       <c r="L50">
-        <v>1.3081330620107799E-3</v>
+        <v>4.0692513404583797E-3</v>
       </c>
       <c r="M50" s="2">
-        <v>2.80171745622202E-6</v>
+        <v>5.5675919373717998E-6</v>
       </c>
       <c r="N50">
-        <v>1.4366091704730399E-3</v>
+        <v>4.0569357875227304E-3</v>
       </c>
       <c r="O50" s="2">
-        <v>3.9642356132896798E-6</v>
+        <v>5.2496418363288303E-6</v>
       </c>
       <c r="P50" s="7">
         <f t="shared" si="9"/>
-        <v>1.0982133333322945</v>
+        <v>0.99697350890735048</v>
       </c>
       <c r="Q50">
         <f t="shared" si="11"/>
-        <v>3.8361574919628999E-3</v>
+        <v>1.8774931839575925E-3</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="B51" s="4"/>
       <c r="D51">
-        <v>7.6150959878939798E-3</v>
+        <v>2.0701772563261001E-2</v>
       </c>
       <c r="E51" s="2">
-        <v>7.5030193636514299E-5</v>
+        <v>1.94778367259042E-5</v>
       </c>
       <c r="F51">
-        <v>7.66287134998351E-3</v>
+        <v>2.0670832742657502E-2</v>
       </c>
       <c r="G51" s="2">
-        <v>7.5060793105698198E-5</v>
-      </c>
-      <c r="H51" s="13">
+        <v>2.4165486313225001E-5</v>
+      </c>
+      <c r="H51" s="21">
         <f t="shared" si="8"/>
-        <v>1.0062737701751205</v>
+        <v>0.99850545065602703</v>
       </c>
       <c r="I51">
         <f t="shared" si="10"/>
-        <v>1.398060647072992E-2</v>
+        <v>1.498409392449824E-3</v>
       </c>
       <c r="J51" s="3"/>
       <c r="L51">
-        <v>2.12547254000897E-3</v>
+        <v>5.7649672577643396E-3</v>
       </c>
       <c r="M51" s="2">
-        <v>4.3461545058756504E-6</v>
+        <v>6.73190263055258E-6</v>
       </c>
       <c r="N51">
-        <v>2.34981119128888E-3</v>
+        <v>5.7622824448929303E-3</v>
       </c>
       <c r="O51" s="2">
-        <v>6.0470823655424403E-6</v>
+        <v>7.5386609948647098E-6</v>
       </c>
       <c r="P51" s="7">
         <f t="shared" si="9"/>
-        <v>1.105547659194394</v>
+        <v>0.99953428827062407</v>
       </c>
       <c r="Q51">
         <f t="shared" si="11"/>
-        <v>3.6338299450917248E-3</v>
+        <v>1.7528003368185298E-3</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>500</v>
+        <v>999.99</v>
       </c>
       <c r="B52" s="4"/>
       <c r="D52">
-        <v>1.4555744618778E-2</v>
-      </c>
-      <c r="E52">
-        <v>1.2950150523133701E-4</v>
+        <v>2.6254111956257101E-2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3.1518519557492703E-5</v>
       </c>
       <c r="F52">
-        <v>1.43182113525849E-2</v>
-      </c>
-      <c r="G52">
-        <v>1.4705046376382701E-4</v>
-      </c>
-      <c r="H52" s="13">
+        <v>2.6241236871756501E-2</v>
+      </c>
+      <c r="G52" s="2">
+        <v>3.3019156397098597E-5</v>
+      </c>
+      <c r="H52" s="21">
         <f t="shared" si="8"/>
-        <v>0.9836811326102366</v>
+        <v>0.9995095974100342</v>
       </c>
       <c r="I52">
-        <f t="shared" si="10"/>
-        <v>1.3366190039228829E-2</v>
+        <f>H52*((E52/D52)^2 +(G52/F52)^2)^0.5</f>
+        <v>1.7382683540267973E-3</v>
       </c>
       <c r="J52" s="3"/>
       <c r="L52">
-        <v>4.0263446679611103E-3</v>
+        <v>7.3065547855977898E-3</v>
       </c>
       <c r="M52" s="2">
-        <v>9.8284022533362494E-6</v>
+        <v>7.6217629536129497E-6</v>
       </c>
       <c r="N52">
-        <v>4.4001147340224003E-3</v>
+        <v>7.2989569527415503E-3</v>
       </c>
       <c r="O52" s="2">
-        <v>1.2233005270844601E-5</v>
+        <v>8.3743748627356196E-6</v>
       </c>
       <c r="P52" s="7">
         <f t="shared" si="9"/>
-        <v>1.0928311152881411</v>
+        <v>0.99896013469012568</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="11"/>
-        <v>4.0431595724590682E-3</v>
+        <f>P52*((M52/L52)^2 +(O52/N52)^2)^0.5</f>
+        <v>1.5490415302505404E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>750</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="D53">
-        <v>2.0743350143341999E-2</v>
-      </c>
-      <c r="E53">
-        <v>2.4538469022951099E-4</v>
-      </c>
-      <c r="F53">
-        <v>2.0707732271304301E-2</v>
-      </c>
-      <c r="G53">
-        <v>2.6747352499092303E-4</v>
-      </c>
-      <c r="H53" s="13">
-        <f t="shared" si="8"/>
-        <v>0.99828292576697741</v>
-      </c>
-      <c r="I53">
-        <f t="shared" si="10"/>
-        <v>1.7484977915483216E-2</v>
-      </c>
-      <c r="J53" s="3"/>
-      <c r="L53">
-        <v>5.7060236110456197E-3</v>
-      </c>
-      <c r="M53" s="2">
-        <v>1.35378322351975E-5</v>
-      </c>
-      <c r="N53">
-        <v>6.2061024296920604E-3</v>
-      </c>
-      <c r="O53" s="2">
-        <v>1.42865721950832E-5</v>
-      </c>
-      <c r="P53" s="7">
-        <f t="shared" si="9"/>
-        <v>1.0876405098777364</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="11"/>
-        <v>3.5955188836270442E-3</v>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C55" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>999.99</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="D54">
-        <v>2.61827077319201E-2</v>
-      </c>
-      <c r="E54">
-        <v>3.1898400948727698E-4</v>
-      </c>
-      <c r="F54">
-        <v>2.5981087494686798E-2</v>
-      </c>
-      <c r="G54">
-        <v>4.3258976581349399E-4</v>
-      </c>
-      <c r="H54" s="13">
-        <f t="shared" si="8"/>
-        <v>0.99229948868170348</v>
-      </c>
-      <c r="I54">
-        <f>H54*((E54/D54)^2 +(G54/F54)^2)^0.5</f>
-        <v>2.047251252301235E-2</v>
-      </c>
-      <c r="J54" s="3"/>
-      <c r="L54">
-        <v>7.2100975409337296E-3</v>
-      </c>
-      <c r="M54" s="2">
-        <v>1.5881717337174401E-5</v>
-      </c>
-      <c r="N54">
-        <v>7.8337967364074702E-3</v>
-      </c>
-      <c r="O54" s="2">
-        <v>1.6587191792760698E-5</v>
-      </c>
-      <c r="P54" s="7">
-        <f t="shared" si="9"/>
-        <v>1.0865035725151881</v>
-      </c>
-      <c r="Q54">
-        <f>P54*((M54/L54)^2 +(O54/N54)^2)^0.5</f>
-        <v>3.3196628738700355E-3</v>
-      </c>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C57" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="C57" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="14"/>
+      <c r="K57" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="17"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C58" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
+      <c r="A58" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" s="6"/>
+      <c r="K58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L58" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M58" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N58" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O58" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P58" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q58" s="19" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C59" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="14"/>
-      <c r="K59" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="17"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
+      <c r="A59">
+        <v>0.1</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="D59">
+        <v>1.35349035541185</v>
+      </c>
+      <c r="E59" s="2">
+        <v>9.6553174997388497E-5</v>
+      </c>
+      <c r="H59" s="7">
+        <f t="shared" ref="H59:H71" si="12">F59/D59</f>
+        <v>0</v>
+      </c>
+      <c r="I59" t="e">
+        <f>H59*((E59/D59)^2 +(G59/F59)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J59" s="3"/>
+      <c r="L59">
+        <v>1.3534796781066101</v>
+      </c>
+      <c r="M59" s="2">
+        <v>9.4365811729444995E-5</v>
+      </c>
+      <c r="N59">
+        <v>1.3533874250728799</v>
+      </c>
+      <c r="O59" s="2">
+        <v>9.25744561728887E-5</v>
+      </c>
+      <c r="P59" s="7">
+        <f t="shared" ref="P59:P71" si="13">N59/L59</f>
+        <v>0.99993184010427161</v>
+      </c>
+      <c r="Q59">
+        <f>P59*((M59/L59)^2 +(O59/N59)^2)^0.5</f>
+        <v>9.766545498253321E-5</v>
+      </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
+      <c r="A60">
+        <v>0.5</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="D60">
+        <v>1.3525055888533599</v>
+      </c>
+      <c r="E60">
+        <v>1.3350945350493499E-4</v>
+      </c>
+      <c r="H60" s="7">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H60" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I60" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J60" s="6"/>
-      <c r="K60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L60" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N60" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O60" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P60" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q60" s="19" t="s">
-        <v>12</v>
+      <c r="I60" t="e">
+        <f t="shared" ref="I60:I70" si="14">H60*((E60/D60)^2 +(G60/F60)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60">
+        <v>1.3523816661130299</v>
+      </c>
+      <c r="M60">
+        <v>1.49314446515367E-4</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" t="e">
+        <f t="shared" ref="Q60:Q70" si="15">P60*((M60/L60)^2 +(O60/N60)^2)^0.5</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="B61" s="4"/>
       <c r="D61">
-        <v>1.34549093815081</v>
+        <v>1.35196691014248</v>
       </c>
       <c r="E61">
-        <v>9.6602395136610505E-3</v>
-      </c>
-      <c r="F61">
-        <v>1.36156879240936</v>
-      </c>
-      <c r="G61">
-        <v>1.6290148897183901E-2</v>
+        <v>1.06286820978399E-4</v>
       </c>
       <c r="H61" s="7">
-        <f t="shared" ref="H61:H73" si="12">F61/D61</f>
-        <v>1.0119494333277688</v>
-      </c>
-      <c r="I61">
-        <f>H61*((E61/D61)^2 +(G61/F61)^2)^0.5</f>
-        <v>1.4119924316759918E-2</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I61" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="J61" s="3"/>
       <c r="L61">
-        <v>1.3352318967644701</v>
-      </c>
-      <c r="M61" s="2">
-        <v>9.7356481692860994E-5</v>
-      </c>
-      <c r="N61">
-        <v>1.3353466214812699</v>
-      </c>
-      <c r="O61">
-        <v>1.2505601665707E-4</v>
+        <v>1.3518170844189801</v>
+      </c>
+      <c r="M61">
+        <v>1.14380157051306E-4</v>
       </c>
       <c r="P61" s="7">
-        <f t="shared" ref="P61:P73" si="13">N61/L61</f>
-        <v>1.0000859211924744</v>
-      </c>
-      <c r="Q61">
-        <f>P61*((M61/L61)^2 +(O61/N61)^2)^0.5</f>
-        <v>1.1869810586467566E-4</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q61" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="B62" s="4"/>
       <c r="D62">
-        <v>1.3416927793087801</v>
+        <v>1.3496449964439701</v>
       </c>
       <c r="E62">
-        <v>1.2246180909233399E-2</v>
-      </c>
-      <c r="F62">
-        <v>1.34789356590029</v>
-      </c>
-      <c r="G62">
-        <v>1.0563454700490801E-2</v>
+        <v>3.34573859265803E-4</v>
       </c>
       <c r="H62" s="7">
         <f t="shared" si="12"/>
-        <v>1.0046216143420734</v>
-      </c>
-      <c r="I62">
-        <f t="shared" ref="I62:I72" si="14">H62*((E62/D62)^2 +(G62/F62)^2)^0.5</f>
-        <v>1.2085908780077301E-2</v>
+        <v>0</v>
+      </c>
+      <c r="I62" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62">
-        <v>1.33328060850382</v>
+        <v>1.3484991014567</v>
       </c>
       <c r="M62">
-        <v>1.11744636942801E-4</v>
-      </c>
-      <c r="N62">
-        <v>1.33349654821898</v>
-      </c>
-      <c r="O62" s="2">
-        <v>9.9388022927045995E-5</v>
+        <v>3.7805904699346899E-4</v>
       </c>
       <c r="P62" s="8">
         <f t="shared" si="13"/>
-        <v>1.0001619611909021</v>
-      </c>
-      <c r="Q62">
-        <f t="shared" ref="Q62:Q72" si="15">P62*((M62/L62)^2 +(O62/N62)^2)^0.5</f>
-        <v>1.1217617716941135E-4</v>
+        <v>0</v>
+      </c>
+      <c r="Q62" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B63" s="4"/>
       <c r="D63">
-        <v>1.347132670311</v>
+        <v>1.34878568413012</v>
       </c>
       <c r="E63">
-        <v>1.062357119247E-2</v>
-      </c>
-      <c r="F63">
-        <v>1.3536019236177701</v>
-      </c>
-      <c r="G63">
-        <v>1.05499843650719E-2</v>
+        <v>1.09258372127255E-3</v>
       </c>
       <c r="H63" s="7">
         <f t="shared" si="12"/>
-        <v>1.0048022391924298</v>
-      </c>
-      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="e">
         <f t="shared" si="14"/>
-        <v>1.1140920335378206E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J63" s="3"/>
       <c r="L63">
-        <v>1.3325160160175999</v>
+        <v>1.34496639056255</v>
       </c>
       <c r="M63">
-        <v>1.2990361944337101E-4</v>
-      </c>
-      <c r="N63">
-        <v>1.3326689845730799</v>
-      </c>
-      <c r="O63">
-        <v>1.0526827110579401E-4</v>
+        <v>1.6184768350052301E-3</v>
       </c>
       <c r="P63" s="7">
         <f t="shared" si="13"/>
-        <v>1.0001147967856605</v>
-      </c>
-      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="e">
         <f t="shared" si="15"/>
-        <v>1.2548677612360951E-4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B64" s="4"/>
       <c r="D64">
-        <v>1.3602364546608099</v>
+        <v>1.3474610818274699</v>
       </c>
       <c r="E64">
-        <v>1.05925047285835E-2</v>
-      </c>
-      <c r="F64">
-        <v>1.37032967472502</v>
-      </c>
-      <c r="G64">
-        <v>1.2843682749925801E-2</v>
+        <v>1.17516294196242E-3</v>
       </c>
       <c r="H64" s="7">
         <f t="shared" si="12"/>
-        <v>1.0074201952385748</v>
-      </c>
-      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="e">
         <f t="shared" si="14"/>
-        <v>1.2276014350788962E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64">
-        <v>1.32875591199513</v>
+        <v>1.34058997335879</v>
       </c>
       <c r="M64">
-        <v>3.6656386812860002E-4</v>
-      </c>
-      <c r="N64">
-        <v>1.3283935226396499</v>
-      </c>
-      <c r="O64">
-        <v>4.6050432456435497E-4</v>
+        <v>1.0490060790073401E-3</v>
       </c>
       <c r="P64" s="8">
         <f t="shared" si="13"/>
-        <v>0.99972727168909759</v>
-      </c>
-      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="e">
         <f t="shared" si="15"/>
-        <v>4.4291324537064109E-4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B65" s="4"/>
       <c r="D65">
-        <v>1.35583826189331</v>
+        <v>1.3427752965748101</v>
       </c>
       <c r="E65">
-        <v>1.3634366593388399E-2</v>
-      </c>
-      <c r="F65">
-        <v>1.35387544977375</v>
-      </c>
-      <c r="G65">
-        <v>1.12790222687198E-2</v>
+        <v>1.07490457255542E-3</v>
       </c>
       <c r="H65" s="7">
         <f t="shared" si="12"/>
-        <v>0.99855232576426989</v>
-      </c>
-      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="e">
         <f t="shared" si="14"/>
-        <v>1.3039737640761582E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J65" s="3"/>
       <c r="L65">
-        <v>1.3245110745965301</v>
+        <v>1.3360765153922001</v>
       </c>
       <c r="M65">
-        <v>6.3753145972632905E-4</v>
-      </c>
-      <c r="N65">
-        <v>1.32578542353965</v>
-      </c>
-      <c r="O65">
-        <v>1.0645660109259701E-3</v>
+        <v>1.1632843834853399E-3</v>
       </c>
       <c r="P65" s="7">
         <f t="shared" si="13"/>
-        <v>1.0009621278127161</v>
-      </c>
-      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="e">
         <f t="shared" si="15"/>
-        <v>9.3708596837583497E-4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="B66" s="4"/>
       <c r="D66">
-        <v>1.3376814283365499</v>
+        <v>1.34074242473516</v>
       </c>
       <c r="E66">
-        <v>1.46996351657998E-2</v>
-      </c>
-      <c r="F66">
-        <v>1.34605384879503</v>
-      </c>
-      <c r="G66">
-        <v>1.1123574086638799E-2</v>
+        <v>1.39655871426836E-3</v>
       </c>
       <c r="H66" s="7">
         <f t="shared" si="12"/>
-        <v>1.0062589046099648</v>
-      </c>
-      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="I66" t="e">
         <f t="shared" si="14"/>
-        <v>1.3835484656453595E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66">
-        <v>1.3197871026024</v>
+        <v>1.32701226510564</v>
       </c>
       <c r="M66">
-        <v>8.8312138374329295E-4</v>
-      </c>
-      <c r="N66">
-        <v>1.3193357094999201</v>
-      </c>
-      <c r="O66">
-        <v>9.5862687561023305E-4</v>
+        <v>1.12425566465752E-3</v>
       </c>
       <c r="P66" s="8">
         <f t="shared" si="13"/>
-        <v>0.99965798036547726</v>
-      </c>
-      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="e">
         <f t="shared" si="15"/>
-        <v>9.874335070433548E-4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="B67" s="4"/>
       <c r="D67">
-        <v>1.3300494208176601</v>
+        <v>1.33329826157554</v>
       </c>
       <c r="E67">
-        <v>9.9861477879520603E-3</v>
-      </c>
-      <c r="F67">
-        <v>1.3372073524914401</v>
-      </c>
-      <c r="G67">
-        <v>1.1799011003357E-2</v>
+        <v>1.0127020502582399E-3</v>
       </c>
       <c r="H67" s="7">
         <f t="shared" si="12"/>
-        <v>1.0053817035380381</v>
-      </c>
-      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="e">
         <f t="shared" si="14"/>
-        <v>1.1648027045948387E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J67" s="3"/>
       <c r="L67">
-        <v>1.31486593414251</v>
+        <v>1.31712591718725</v>
       </c>
       <c r="M67">
-        <v>8.9177056244582901E-4</v>
-      </c>
-      <c r="N67">
-        <v>1.31129753244608</v>
-      </c>
-      <c r="O67">
-        <v>7.8150296279425404E-4</v>
+        <v>1.07670919895594E-3</v>
       </c>
       <c r="P67" s="7">
         <f t="shared" si="13"/>
-        <v>0.99728610985822141</v>
-      </c>
-      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="e">
         <f t="shared" si="15"/>
-        <v>9.004190394956773E-4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="B68" s="4"/>
       <c r="D68">
-        <v>1.33175217638606</v>
+        <v>1.32151573265695</v>
       </c>
       <c r="E68">
-        <v>1.42484774222981E-2</v>
-      </c>
-      <c r="F68">
-        <v>1.34134443767434</v>
-      </c>
-      <c r="G68">
-        <v>9.8457440055415898E-3</v>
+        <v>1.3006693362351499E-3</v>
       </c>
       <c r="H68" s="7">
         <f t="shared" si="12"/>
-        <v>1.0072027374599906</v>
-      </c>
-      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="e">
         <f t="shared" si="14"/>
-        <v>1.3068361323806845E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68">
-        <v>1.3080554428553499</v>
+        <v>1.2918988571682599</v>
       </c>
       <c r="M68">
-        <v>1.05245064814075E-3</v>
-      </c>
-      <c r="N68">
-        <v>1.30680092368919</v>
-      </c>
-      <c r="O68">
-        <v>1.1966142360113001E-3</v>
+        <v>1.1007541264065699E-3</v>
       </c>
       <c r="P68" s="8">
         <f t="shared" si="13"/>
-        <v>0.99904092814030765</v>
-      </c>
-      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="e">
         <f t="shared" si="15"/>
-        <v>1.2177819875734308E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="B69" s="4"/>
       <c r="D69">
-        <v>1.34429392392619</v>
+        <v>1.2931453740650001</v>
       </c>
       <c r="E69">
-        <v>1.09613129342569E-2</v>
-      </c>
-      <c r="F69">
-        <v>1.3097253068252801</v>
-      </c>
-      <c r="G69">
-        <v>1.33759550173604E-2</v>
+        <v>9.8555966722236005E-4</v>
       </c>
       <c r="H69" s="7">
         <f t="shared" si="12"/>
-        <v>0.9742849264690957</v>
-      </c>
-      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="e">
         <f t="shared" si="14"/>
-        <v>1.2732534432968911E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J69" s="3"/>
       <c r="L69">
-        <v>1.2992314592619101</v>
+        <v>1.23828567912233</v>
       </c>
       <c r="M69">
-        <v>2.6598085552900302E-3</v>
-      </c>
-      <c r="N69">
-        <v>1.2990352083416801</v>
-      </c>
-      <c r="O69">
-        <v>2.3388362534294302E-3</v>
+        <v>1.26094639154959E-3</v>
       </c>
       <c r="P69" s="7">
         <f t="shared" si="13"/>
-        <v>0.99984894845423344</v>
-      </c>
-      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="e">
         <f t="shared" si="15"/>
-        <v>2.7258832387438308E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="B70" s="4"/>
-      <c r="D70">
-        <v>1.34427610935998</v>
-      </c>
-      <c r="E70">
-        <v>1.5734707106331298E-2</v>
-      </c>
-      <c r="F70">
-        <v>1.31223469976561</v>
-      </c>
-      <c r="G70">
-        <v>1.00903875849934E-2</v>
-      </c>
-      <c r="H70" s="7">
+      <c r="H70" s="7" t="e">
         <f t="shared" si="12"/>
-        <v>0.97616456219725189</v>
-      </c>
-      <c r="I70">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I70" t="e">
         <f t="shared" si="14"/>
-        <v>1.3670980772624434E-2</v>
-      </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J70" s="4"/>
       <c r="L70">
-        <v>1.2754633925346801</v>
+        <v>1.1839603302327899</v>
       </c>
       <c r="M70">
-        <v>2.5670750630042301E-3</v>
-      </c>
-      <c r="N70">
-        <v>1.27508401331121</v>
-      </c>
-      <c r="O70">
-        <v>3.1668437255882899E-3</v>
-      </c>
-      <c r="P70" s="8">
+        <v>9.7670331118084107E-4</v>
+      </c>
+      <c r="P70" s="7">
         <f t="shared" si="13"/>
-        <v>0.9997025557725211</v>
-      </c>
-      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="e">
         <f t="shared" si="15"/>
-        <v>3.1958049501485874E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>500</v>
+        <v>999.99</v>
       </c>
       <c r="B71" s="4"/>
-      <c r="D71">
-        <v>1.3147146084816601</v>
-      </c>
-      <c r="E71">
-        <v>1.0665156996221E-2</v>
-      </c>
-      <c r="F71">
-        <v>1.2883444692741599</v>
-      </c>
-      <c r="G71">
-        <v>1.20569063164959E-2</v>
-      </c>
-      <c r="H71" s="7">
+      <c r="H71" s="7" t="e">
         <f t="shared" si="12"/>
-        <v>0.9799423091236853</v>
-      </c>
-      <c r="I71">
-        <f t="shared" si="14"/>
-        <v>1.2136556287608504E-2</v>
-      </c>
-      <c r="J71" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I71" t="e">
+        <f>H71*((E71/D71)^2 +(G71/F71)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J71" s="4"/>
       <c r="L71">
-        <v>1.21433761848289</v>
+        <v>1.13553758367077</v>
       </c>
       <c r="M71">
-        <v>1.78305037450447E-3</v>
-      </c>
-      <c r="N71">
-        <v>1.2162928747352799</v>
-      </c>
-      <c r="O71">
-        <v>1.78442571980327E-3</v>
-      </c>
-      <c r="P71" s="7">
+        <v>1.1206624657434201E-3</v>
+      </c>
+      <c r="P71" s="8">
         <f t="shared" si="13"/>
-        <v>1.0016101422064423</v>
-      </c>
-      <c r="Q71">
-        <f t="shared" si="15"/>
-        <v>2.0790073532015014E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>750</v>
-      </c>
-      <c r="B72" s="4"/>
-      <c r="D72">
-        <v>1.24826946359702</v>
-      </c>
-      <c r="E72">
-        <v>1.1172085267728501E-2</v>
-      </c>
-      <c r="F72">
-        <v>1.2718255056190799</v>
-      </c>
-      <c r="G72">
-        <v>1.3345569030886101E-2</v>
-      </c>
-      <c r="H72" s="7">
-        <f t="shared" si="12"/>
-        <v>1.0188709591230252</v>
-      </c>
-      <c r="I72">
-        <f t="shared" si="14"/>
-        <v>1.4051985927606269E-2</v>
-      </c>
-      <c r="J72" s="4"/>
-      <c r="L72">
-        <v>1.16893154054166</v>
-      </c>
-      <c r="M72">
-        <v>2.5299483816998E-3</v>
-      </c>
-      <c r="N72">
-        <v>1.1623016999656299</v>
-      </c>
-      <c r="O72">
-        <v>2.3537063605707201E-3</v>
-      </c>
-      <c r="P72" s="7">
-        <f t="shared" si="13"/>
-        <v>0.99432829011273149</v>
-      </c>
-      <c r="Q72">
-        <f t="shared" si="15"/>
-        <v>2.9471542099952473E-3</v>
+        <v>0</v>
+      </c>
+      <c r="Q71" t="e">
+        <f>P71*((M71/L71)^2 +(O71/N71)^2)^0.5</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>999.99</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="D73">
-        <v>1.23608398603043</v>
-      </c>
-      <c r="E73">
-        <v>1.0767330173302701E-2</v>
-      </c>
-      <c r="F73">
-        <v>1.2341574677574501</v>
-      </c>
-      <c r="G73">
-        <v>1.06426817584923E-2</v>
-      </c>
-      <c r="H73" s="7">
-        <f t="shared" si="12"/>
-        <v>0.99844143416244169</v>
-      </c>
-      <c r="I73">
-        <f>H73*((E73/D73)^2 +(G73/F73)^2)^0.5</f>
-        <v>1.223823842295031E-2</v>
-      </c>
-      <c r="J73" s="4"/>
-      <c r="L73">
-        <v>1.1280813456035399</v>
-      </c>
-      <c r="M73">
-        <v>2.4503318989518999E-3</v>
-      </c>
-      <c r="N73">
-        <v>1.1159074766764601</v>
-      </c>
-      <c r="O73">
-        <v>2.3868755353182898E-3</v>
-      </c>
-      <c r="P73" s="8">
-        <f t="shared" si="13"/>
-        <v>0.98920834124726476</v>
-      </c>
-      <c r="Q73">
-        <f>P73*((M73/L73)^2 +(O73/N73)^2)^0.5</f>
-        <v>3.0155845990736735E-3</v>
+      <c r="C73" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C74" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="14"/>
+      <c r="K74" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L74" s="17"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="17"/>
+      <c r="P74" s="17"/>
+      <c r="Q74" s="17"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J75" s="6"/>
+      <c r="K75" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L75" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M75" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N75" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O75" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P75" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q75" s="19" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C76" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
+      <c r="A76">
+        <v>0.1</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2">
+        <v>2.02909902032051E-5</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2.24743175291538E-9</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="7">
+        <f t="shared" ref="H76:H88" si="16">F76/D76</f>
+        <v>0</v>
+      </c>
+      <c r="I76" t="e">
+        <f>H76*((E76/D76)^2 +(G76/F76)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J76" s="3"/>
       <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
+      <c r="L76" s="2">
+        <v>2.4790666762969901E-5</v>
+      </c>
+      <c r="M76" s="2">
+        <v>2.62930916912575E-9</v>
+      </c>
+      <c r="N76" s="2">
+        <v>2.4528682334896999E-5</v>
+      </c>
+      <c r="O76" s="2">
+        <v>3.5040531796592898E-8</v>
+      </c>
+      <c r="P76" s="7">
+        <f t="shared" ref="P76:P88" si="17">N76/L76</f>
+        <v>0.98943213465866797</v>
+      </c>
+      <c r="Q76">
+        <f>P76*((M76/L76)^2 +(O76/N76)^2)^0.5</f>
+        <v>1.4173467854162441E-3</v>
+      </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C77" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="14"/>
-      <c r="K77" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L77" s="17"/>
-      <c r="M77" s="18"/>
-      <c r="N77" s="18"/>
-      <c r="O77" s="17"/>
-      <c r="P77" s="17"/>
-      <c r="Q77" s="17"/>
+      <c r="A77">
+        <v>0.5</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="2"/>
+      <c r="D77">
+        <v>1.0137245509615099E-4</v>
+      </c>
+      <c r="E77" s="2">
+        <v>1.77005795225872E-8</v>
+      </c>
+      <c r="G77" s="2"/>
+      <c r="H77" s="7">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I77" t="e">
+        <f t="shared" ref="I77:I87" si="18">H77*((E77/D77)^2 +(G77/F77)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J77" s="3"/>
+      <c r="L77">
+        <v>1.2382934591149999E-4</v>
+      </c>
+      <c r="M77" s="2">
+        <v>1.9712339612085199E-8</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" s="7">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q77" t="e">
+        <f t="shared" ref="Q77:Q87" si="19">P77*((M77/L77)^2 +(O77/N77)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="s">
+      <c r="A78">
+        <v>1</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="2"/>
+      <c r="D78">
+        <v>2.02642741315636E-4</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2.4405638890132701E-8</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="7">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I78" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J78" s="6"/>
-      <c r="K78" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L78" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M78" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N78" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O78" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P78" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q78" s="19" t="s">
-        <v>12</v>
+      <c r="I78" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="L78">
+        <v>2.4754589215855298E-4</v>
+      </c>
+      <c r="M78" s="2">
+        <v>3.1019310600902002E-8</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" s="7">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q78" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="2">
-        <v>2.0002233294373301E-5</v>
+      <c r="D79">
+        <v>2.0215278732349001E-3</v>
       </c>
       <c r="E79" s="2">
-        <v>1.7030608376628199E-7</v>
-      </c>
-      <c r="F79" s="2">
-        <v>1.9154229282202399E-5</v>
-      </c>
-      <c r="G79" s="2">
-        <v>1.7988696044245199E-6</v>
-      </c>
+        <v>8.3041477691979302E-7</v>
+      </c>
+      <c r="G79" s="2"/>
       <c r="H79" s="7">
-        <f t="shared" ref="H79:H91" si="16">F79/D79</f>
-        <v>0.95760453346929775</v>
-      </c>
-      <c r="I79">
-        <f>H79*((E79/D79)^2 +(G79/F79)^2)^0.5</f>
-        <v>9.0302275173159391E-2</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I79" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="J79" s="3"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2">
-        <v>2.44222139985293E-5</v>
+      <c r="L79">
+        <v>2.4688428331907201E-3</v>
       </c>
       <c r="M79" s="2">
-        <v>3.2540004788240401E-9</v>
-      </c>
-      <c r="N79" s="2">
-        <v>2.5452415896808901E-5</v>
-      </c>
-      <c r="O79" s="2">
-        <v>3.4511677912228998E-8</v>
-      </c>
+        <v>9.25195380739334E-7</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" s="7">
-        <f t="shared" ref="P79:P91" si="17">N79/L79</f>
-        <v>1.0421829854714089</v>
-      </c>
-      <c r="Q79">
-        <f>P79*((M79/L79)^2 +(O79/N79)^2)^0.5</f>
-        <v>1.419932591807686E-3</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q79" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>0.5</v>
+        <v>25</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="2">
-        <v>9.91310272208487E-5</v>
+      <c r="D80">
+        <v>5.0558014839730799E-3</v>
       </c>
       <c r="E80" s="2">
-        <v>1.2117703260356901E-6</v>
-      </c>
-      <c r="F80">
-        <v>1.02061852856601E-4</v>
-      </c>
-      <c r="G80" s="2">
-        <v>1.15006105177774E-5</v>
-      </c>
+        <v>6.1896243078158903E-6</v>
+      </c>
+      <c r="G80" s="2"/>
       <c r="H80" s="7">
         <f t="shared" si="16"/>
-        <v>1.0295651696337502</v>
-      </c>
-      <c r="I80">
-        <f t="shared" ref="I80:I90" si="18">H80*((E80/D80)^2 +(G80/F80)^2)^0.5</f>
-        <v>0.11669487456229509</v>
+        <v>0</v>
+      </c>
+      <c r="I80" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="J80" s="3"/>
       <c r="L80">
-        <v>1.21907844018741E-4</v>
+        <v>6.1582182881184796E-3</v>
       </c>
       <c r="M80" s="2">
-        <v>1.40834939730919E-8</v>
-      </c>
-      <c r="N80">
-        <v>1.27621410906264E-4</v>
-      </c>
-      <c r="O80" s="2">
-        <v>7.9820165373987095E-8</v>
-      </c>
+        <v>9.8842994715634199E-6</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" s="7">
         <f t="shared" si="17"/>
-        <v>1.0468679184142133</v>
-      </c>
-      <c r="Q80">
-        <f t="shared" ref="Q80:Q90" si="19">P80*((M80/L80)^2 +(O80/N80)^2)^0.5</f>
-        <v>6.6583397526143498E-4</v>
+        <v>0</v>
+      </c>
+      <c r="Q80" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="2"/>
       <c r="D81">
-        <v>2.00575852618712E-4</v>
+        <v>1.0087782457006899E-2</v>
       </c>
       <c r="E81" s="2">
-        <v>2.16273397924911E-6</v>
-      </c>
-      <c r="F81">
-        <v>1.9732359623844599E-4</v>
-      </c>
-      <c r="G81" s="2">
-        <v>5.14649711941008E-6</v>
+        <v>1.16986845524187E-5</v>
       </c>
       <c r="H81" s="7">
         <f t="shared" si="16"/>
-        <v>0.98378540418597427</v>
-      </c>
-      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="I81" t="e">
         <f t="shared" si="18"/>
-        <v>2.7764893589842393E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J81" s="3"/>
       <c r="L81">
-        <v>2.4364376203713501E-4</v>
+        <v>1.22887559133099E-2</v>
       </c>
       <c r="M81" s="2">
-        <v>3.6399685613690799E-8</v>
-      </c>
-      <c r="N81">
-        <v>2.5560959700704201E-4</v>
-      </c>
-      <c r="O81" s="2">
-        <v>1.2775665836178299E-7</v>
-      </c>
+        <v>1.29589704180185E-5</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" s="7">
         <f t="shared" si="17"/>
-        <v>1.0491120103788383</v>
-      </c>
-      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="e">
         <f t="shared" si="19"/>
-        <v>5.4728183879285217E-4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="2"/>
       <c r="D82">
-        <v>2.0547440242183199E-3</v>
+        <v>1.50934860556895E-2</v>
       </c>
       <c r="E82" s="2">
-        <v>2.87125014252341E-5</v>
-      </c>
-      <c r="F82">
-        <v>2.0383417165543401E-3</v>
-      </c>
-      <c r="G82" s="2">
-        <v>5.3130482672603703E-5</v>
+        <v>1.70782053665879E-5</v>
       </c>
       <c r="H82" s="7">
         <f t="shared" si="16"/>
-        <v>0.9920173474307975</v>
-      </c>
-      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="I82" t="e">
         <f t="shared" si="18"/>
-        <v>2.9338877352309604E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J82" s="3"/>
       <c r="L82">
-        <v>2.4288696331029799E-3</v>
+        <v>1.8371849012466902E-2</v>
       </c>
       <c r="M82" s="2">
-        <v>9.7964708696651905E-7</v>
-      </c>
-      <c r="N82">
-        <v>2.56202907911283E-3</v>
-      </c>
-      <c r="O82" s="2">
-        <v>1.85007690935801E-6</v>
-      </c>
+        <v>1.8508626230406801E-5</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" s="7">
         <f t="shared" si="17"/>
-        <v>1.0548236283228316</v>
-      </c>
-      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="e">
         <f t="shared" si="19"/>
-        <v>8.7246560513766763E-4</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="2"/>
       <c r="D83">
-        <v>5.0701041950725403E-3</v>
+        <v>2.0092596382124801E-2</v>
       </c>
       <c r="E83" s="2">
-        <v>7.78872602324881E-5</v>
-      </c>
-      <c r="F83">
-        <v>5.0274633111464604E-3</v>
-      </c>
-      <c r="G83" s="2">
-        <v>6.3292812090225907E-5</v>
+        <v>2.9515645920923001E-5</v>
       </c>
       <c r="H83" s="7">
         <f t="shared" si="16"/>
-        <v>0.99158974208705197</v>
-      </c>
-      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="I83" t="e">
         <f t="shared" si="18"/>
-        <v>1.9694637363199229E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J83" s="3"/>
       <c r="L83">
-        <v>6.0546834237900898E-3</v>
+        <v>2.43271897166558E-2</v>
       </c>
       <c r="M83" s="2">
-        <v>3.7968621057748099E-6</v>
-      </c>
-      <c r="N83">
-        <v>6.4137122028123401E-3</v>
-      </c>
-      <c r="O83" s="2">
-        <v>5.4200951411111697E-6</v>
-      </c>
+        <v>3.1299383235957799E-5</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" s="7">
         <f t="shared" si="17"/>
-        <v>1.0592976963273675</v>
-      </c>
-      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="e">
         <f t="shared" si="19"/>
-        <v>1.1147351456962668E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="2"/>
       <c r="D84">
-        <v>1.00278782890249E-2</v>
-      </c>
-      <c r="E84">
-        <v>1.52940678297456E-4</v>
-      </c>
-      <c r="F84">
-        <v>9.93683126794794E-3</v>
-      </c>
-      <c r="G84">
-        <v>1.16287139207722E-4</v>
+        <v>3.00179157888214E-2</v>
+      </c>
+      <c r="E84" s="2">
+        <v>3.4087650495836803E-5</v>
       </c>
       <c r="H84" s="7">
         <f t="shared" si="16"/>
-        <v>0.99092060967905771</v>
-      </c>
-      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="I84" t="e">
         <f t="shared" si="18"/>
-        <v>1.9049440036567715E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J84" s="3"/>
       <c r="L84">
-        <v>1.20608403533201E-2</v>
+        <v>3.6245762780485802E-2</v>
       </c>
       <c r="M84" s="2">
-        <v>1.08240027557222E-5</v>
-      </c>
-      <c r="N84">
-        <v>1.27839027701272E-2</v>
-      </c>
-      <c r="O84" s="2">
-        <v>1.14752038724967E-5</v>
+        <v>3.92808357194154E-5</v>
       </c>
       <c r="P84" s="7">
         <f t="shared" si="17"/>
-        <v>1.0599512468140793</v>
-      </c>
-      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="e">
         <f t="shared" si="19"/>
-        <v>1.3454096255822378E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="2"/>
       <c r="D85">
-        <v>1.48719873659269E-2</v>
-      </c>
-      <c r="E85">
-        <v>1.2461977629631501E-4</v>
-      </c>
-      <c r="F85">
-        <v>1.48683461425556E-2</v>
-      </c>
-      <c r="G85">
-        <v>1.83207975484617E-4</v>
+        <v>4.9734447162320401E-2</v>
+      </c>
+      <c r="E85" s="2">
+        <v>6.4645159030235E-5</v>
       </c>
       <c r="H85" s="7">
         <f t="shared" si="16"/>
-        <v>0.99975516228721106</v>
-      </c>
-      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="I85" t="e">
         <f t="shared" si="18"/>
-        <v>1.4897627132734343E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J85" s="3"/>
       <c r="L85">
-        <v>1.8041215453004699E-2</v>
+        <v>5.9402715051338199E-2</v>
       </c>
       <c r="M85" s="2">
-        <v>1.7714094968001101E-5</v>
-      </c>
-      <c r="N85">
-        <v>1.9051467947753701E-2</v>
-      </c>
-      <c r="O85" s="2">
-        <v>1.1429796000528301E-5</v>
+        <v>6.9304807814503901E-5</v>
       </c>
       <c r="P85" s="7">
         <f t="shared" si="17"/>
-        <v>1.0559969197962629</v>
-      </c>
-      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="e">
         <f t="shared" si="19"/>
-        <v>1.2150834669821305E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="2"/>
       <c r="D86">
-        <v>1.98202597885185E-2</v>
+        <v>9.8175431650812398E-2</v>
       </c>
       <c r="E86">
-        <v>2.6138914306315198E-4</v>
-      </c>
-      <c r="F86">
-        <v>1.9653560006903398E-2</v>
-      </c>
-      <c r="G86">
-        <v>2.40401653483571E-4</v>
+        <v>1.1926647552751499E-4</v>
       </c>
       <c r="H86" s="7">
         <f t="shared" si="16"/>
-        <v>0.9915894249927204</v>
-      </c>
-      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="I86" t="e">
         <f t="shared" si="18"/>
-        <v>1.7836037278114031E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J86" s="3"/>
       <c r="L86">
-        <v>2.3942727421137198E-2</v>
-      </c>
-      <c r="M86" s="2">
-        <v>2.41011922220882E-5</v>
-      </c>
-      <c r="N86">
-        <v>2.5404075273833399E-2</v>
-      </c>
-      <c r="O86" s="2">
-        <v>2.6871581822638802E-5</v>
+        <v>0.114483792434821</v>
+      </c>
+      <c r="M86">
+        <v>1.39194216858858E-4</v>
       </c>
       <c r="P86" s="7">
         <f t="shared" si="17"/>
-        <v>1.0610351455367648</v>
-      </c>
-      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="e">
         <f t="shared" si="19"/>
-        <v>1.5493114902381951E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="B87" s="4"/>
-      <c r="C87" s="2"/>
-      <c r="D87">
-        <v>3.0245264340878899E-2</v>
-      </c>
-      <c r="E87">
-        <v>3.4482423600408198E-4</v>
-      </c>
-      <c r="F87">
-        <v>2.9047097701734199E-2</v>
-      </c>
-      <c r="G87">
-        <v>4.1113748777176802E-4</v>
-      </c>
-      <c r="H87" s="7">
+      <c r="H87" s="7" t="e">
         <f t="shared" si="16"/>
-        <v>0.96038498372370706</v>
-      </c>
-      <c r="I87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I87" t="e">
         <f t="shared" si="18"/>
-        <v>1.7454762203147116E-2</v>
-      </c>
-      <c r="J87" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J87" s="4"/>
       <c r="L87">
-        <v>3.5694610619412301E-2</v>
-      </c>
-      <c r="M87" s="2">
-        <v>8.2524961518027197E-5</v>
-      </c>
-      <c r="N87">
-        <v>3.7961973926613303E-2</v>
-      </c>
-      <c r="O87">
-        <v>1.02905372343833E-4</v>
+        <v>0.16472051968134599</v>
+      </c>
+      <c r="M87">
+        <v>1.6222360707556901E-4</v>
       </c>
       <c r="P87" s="7">
         <f t="shared" si="17"/>
-        <v>1.0635211665810387</v>
-      </c>
-      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="e">
         <f t="shared" si="19"/>
-        <v>3.7890881489905845E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>250</v>
+        <v>999.99</v>
       </c>
       <c r="B88" s="4"/>
-      <c r="C88" s="2"/>
-      <c r="D88">
-        <v>5.0416263518805501E-2</v>
-      </c>
-      <c r="E88">
-        <v>7.2347720793101001E-4</v>
-      </c>
-      <c r="F88">
-        <v>4.9218066442103803E-2</v>
-      </c>
-      <c r="G88">
-        <v>5.9170592270805795E-4</v>
-      </c>
-      <c r="H88" s="7">
+      <c r="H88" s="7" t="e">
         <f t="shared" si="16"/>
-        <v>0.97623391752832367</v>
-      </c>
-      <c r="I88">
-        <f t="shared" si="18"/>
-        <v>1.827556445575958E-2</v>
-      </c>
-      <c r="J88" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I88" t="e">
+        <f>H88*((E88/D88)^2 +(G88/F88)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J88" s="4"/>
       <c r="L88">
-        <v>5.8503285539065399E-2</v>
+        <v>0.21100076304460699</v>
       </c>
       <c r="M88">
-        <v>1.3565230700754799E-4</v>
-      </c>
-      <c r="N88">
-        <v>6.2444533831966298E-2</v>
-      </c>
-      <c r="O88">
-        <v>1.8469627006352599E-4</v>
+        <v>2.47499288497926E-4</v>
       </c>
       <c r="P88" s="7">
         <f t="shared" si="17"/>
-        <v>1.0673679820985291</v>
-      </c>
-      <c r="Q88">
-        <f t="shared" si="19"/>
-        <v>4.0114868768480784E-3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>500</v>
-      </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="2"/>
-      <c r="D89">
-        <v>0.10073975623579599</v>
-      </c>
-      <c r="E89">
-        <v>1.04825820976625E-3</v>
-      </c>
-      <c r="F89">
-        <v>9.7224959993021401E-2</v>
-      </c>
-      <c r="G89">
-        <v>1.18655387397327E-3</v>
-      </c>
-      <c r="H89" s="7">
-        <f t="shared" si="16"/>
-        <v>0.96511013750571617</v>
-      </c>
-      <c r="I89">
-        <f t="shared" si="18"/>
-        <v>1.5478494900700839E-2</v>
-      </c>
-      <c r="J89" s="3"/>
-      <c r="L89">
-        <v>0.111849004597233</v>
-      </c>
-      <c r="M89">
-        <v>1.9399071169807599E-4</v>
-      </c>
-      <c r="N89">
-        <v>0.120228333001437</v>
-      </c>
-      <c r="O89">
-        <v>2.56613265918605E-4</v>
-      </c>
-      <c r="P89" s="7">
-        <f t="shared" si="17"/>
-        <v>1.0749164325098632</v>
-      </c>
-      <c r="Q89">
-        <f t="shared" si="19"/>
-        <v>2.9562598512691846E-3</v>
+        <v>0</v>
+      </c>
+      <c r="Q88" t="e">
+        <f>P88*((M88/L88)^2 +(O88/N88)^2)^0.5</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>750</v>
-      </c>
-      <c r="B90" s="4"/>
-      <c r="D90">
-        <v>0.14276548233861699</v>
-      </c>
-      <c r="E90">
-        <v>1.6010570119940201E-3</v>
-      </c>
-      <c r="F90">
-        <v>0.14479471697963001</v>
-      </c>
-      <c r="G90">
-        <v>1.76129701530317E-3</v>
-      </c>
-      <c r="H90" s="7">
-        <f t="shared" si="16"/>
-        <v>1.0142137623728962</v>
-      </c>
-      <c r="I90">
-        <f t="shared" si="18"/>
-        <v>1.6780024760918215E-2</v>
-      </c>
-      <c r="J90" s="4"/>
-      <c r="L90">
-        <v>0.16223272595004601</v>
-      </c>
-      <c r="M90">
-        <v>4.29274074054726E-4</v>
-      </c>
-      <c r="N90">
-        <v>0.17320049362348</v>
-      </c>
-      <c r="O90">
-        <v>3.4421587306751399E-4</v>
-      </c>
-      <c r="P90" s="7">
-        <f t="shared" si="17"/>
-        <v>1.0676051493877452</v>
-      </c>
-      <c r="Q90">
-        <f t="shared" si="19"/>
-        <v>3.5329852627062406E-3</v>
-      </c>
+      <c r="C90" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="10"/>
+      <c r="H90" s="10"/>
+      <c r="I90" s="10"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>999.99</v>
-      </c>
-      <c r="B91" s="4"/>
-      <c r="D91">
-        <v>0.190903358670658</v>
-      </c>
-      <c r="E91">
-        <v>1.8387457180219901E-3</v>
-      </c>
-      <c r="F91">
-        <v>0.18783135004075499</v>
-      </c>
-      <c r="G91">
-        <v>2.1522124372398499E-3</v>
-      </c>
-      <c r="H91" s="7">
-        <f t="shared" si="16"/>
-        <v>0.98390804304704371</v>
-      </c>
-      <c r="I91">
-        <f>H91*((E91/D91)^2 +(G91/F91)^2)^0.5</f>
-        <v>1.4727844506264298E-2</v>
-      </c>
-      <c r="J91" s="4"/>
-      <c r="L91">
-        <v>0.208953603264767</v>
-      </c>
-      <c r="M91">
-        <v>5.3129443828807302E-4</v>
-      </c>
-      <c r="N91">
-        <v>0.223224252625355</v>
-      </c>
-      <c r="O91">
-        <v>5.6545982801596898E-4</v>
-      </c>
-      <c r="P91" s="7">
-        <f t="shared" si="17"/>
-        <v>1.0682957802000932</v>
-      </c>
-      <c r="Q91">
-        <f>P91*((M91/L91)^2 +(O91/N91)^2)^0.5</f>
-        <v>3.8342543851553339E-3</v>
+      <c r="C91" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="14"/>
+      <c r="K91" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="17"/>
+      <c r="M91" s="18"/>
+      <c r="N91" s="18"/>
+      <c r="O91" s="17"/>
+      <c r="P91" s="17"/>
+      <c r="Q91" s="17"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" s="5"/>
+      <c r="C92" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" s="6"/>
+      <c r="K92" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L92" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M92" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N92" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O92" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P92" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q92" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>0.1</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2">
+        <v>6.1377059341900601E-6</v>
+      </c>
+      <c r="E93" s="2">
+        <v>6.5011853480463401E-10</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="7">
+        <f t="shared" ref="H93:H105" si="20">F93/D93</f>
+        <v>0</v>
+      </c>
+      <c r="I93" t="e">
+        <f>H93*((E93/D93)^2 +(G93/F93)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J93" s="3"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2">
+        <v>1.5930510467711099E-6</v>
+      </c>
+      <c r="M93" s="2">
+        <v>1.65600483830151E-10</v>
+      </c>
+      <c r="N93" s="2">
+        <v>1.5741702493169501E-6</v>
+      </c>
+      <c r="O93" s="2">
+        <v>2.5700779401292402E-9</v>
+      </c>
+      <c r="P93" s="7">
+        <f t="shared" ref="P93:P105" si="21">N93/L93</f>
+        <v>0.98814802733884233</v>
+      </c>
+      <c r="Q93">
+        <f>P93*((M93/L93)^2 +(O93/N93)^2)^0.5</f>
+        <v>1.6165722467163411E-3</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C94" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
+      <c r="A94">
+        <v>0.5</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2">
+        <v>3.0735354469935802E-5</v>
+      </c>
+      <c r="E94" s="2">
+        <v>3.2888347224815601E-9</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="7">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I94" t="e">
+        <f t="shared" ref="I94:I104" si="22">H94*((E94/D94)^2 +(G94/F94)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J94" s="3"/>
+      <c r="L94" s="2">
+        <v>7.9783288855483107E-6</v>
+      </c>
+      <c r="M94" s="2">
+        <v>8.0769164104274605E-10</v>
+      </c>
       <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" s="7">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="Q94" t="e">
+        <f t="shared" ref="Q94:Q104" si="23">P94*((M94/L94)^2 +(O94/N94)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C95" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="14"/>
-      <c r="K95" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L95" s="17"/>
-      <c r="M95" s="18"/>
-      <c r="N95" s="18"/>
-      <c r="O95" s="17"/>
-      <c r="P95" s="17"/>
-      <c r="Q95" s="17"/>
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2">
+        <v>6.1492338452019598E-5</v>
+      </c>
+      <c r="E95" s="2">
+        <v>5.9150812321793704E-9</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="7">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I95" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J95" s="3"/>
+      <c r="L95" s="2">
+        <v>1.5963437915775598E-5</v>
+      </c>
+      <c r="M95" s="2">
+        <v>1.39122184548795E-9</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" s="7">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="Q95" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
+      <c r="A96">
+        <v>10</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="2"/>
+      <c r="D96">
+        <v>6.1359823656618703E-4</v>
+      </c>
+      <c r="E96" s="2">
+        <v>1.7277411502086099E-7</v>
+      </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="7">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H96" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I96" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J96" s="6"/>
-      <c r="K96" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L96" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N96" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O96" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P96" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q96" s="19" t="s">
-        <v>12</v>
+      <c r="I96" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J96" s="3"/>
+      <c r="L96">
+        <v>1.5929141384867101E-4</v>
+      </c>
+      <c r="M96" s="2">
+        <v>4.3762693503452201E-8</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" s="7">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="Q96" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>0.1</v>
+        <v>25</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="2"/>
-      <c r="D97" s="2">
-        <v>6.1707452680724403E-6</v>
+      <c r="D97">
+        <v>1.5261889267198399E-3</v>
       </c>
       <c r="E97" s="2">
-        <v>6.4424852565520702E-8</v>
-      </c>
-      <c r="F97" s="2">
-        <v>5.6806224689815901E-6</v>
-      </c>
-      <c r="G97" s="2">
-        <v>8.7075763768667495E-7</v>
-      </c>
+        <v>1.14318268477437E-6</v>
+      </c>
+      <c r="G97" s="2"/>
       <c r="H97" s="7">
-        <f t="shared" ref="H97:H109" si="20">F97/D97</f>
-        <v>0.92057315967541953</v>
-      </c>
-      <c r="I97">
-        <f>H97*((E97/D97)^2 +(G97/F97)^2)^0.5</f>
-        <v>0.14143754216977653</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I97" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="J97" s="3"/>
-      <c r="K97" s="2"/>
-      <c r="L97" s="2">
-        <v>1.6592058395195499E-6</v>
+      <c r="L97">
+        <v>3.9601961871322503E-4</v>
       </c>
       <c r="M97" s="2">
-        <v>1.41505102275899E-10</v>
-      </c>
-      <c r="N97" s="2">
-        <v>1.8483734702828199E-6</v>
-      </c>
-      <c r="O97" s="2">
-        <v>1.55513175046048E-8</v>
-      </c>
+        <v>3.2948969998976799E-7</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" s="7">
-        <f t="shared" ref="P97:P109" si="21">N97/L97</f>
-        <v>1.1140109480437017</v>
-      </c>
-      <c r="Q97">
-        <f>P97*((M97/L97)^2 +(O97/N97)^2)^0.5</f>
-        <v>9.3732290926810593E-3</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="Q97" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="2"/>
-      <c r="D98" s="2">
-        <v>3.1168296026648497E-5</v>
+      <c r="D98">
+        <v>3.0240386323727099E-3</v>
       </c>
       <c r="E98" s="2">
-        <v>2.37611094273057E-7</v>
-      </c>
-      <c r="F98" s="2">
-        <v>2.9340752914099499E-5</v>
-      </c>
-      <c r="G98" s="2">
-        <v>1.73386889508637E-6</v>
-      </c>
+        <v>2.6402202836250101E-6</v>
+      </c>
+      <c r="G98" s="2"/>
       <c r="H98" s="7">
         <f t="shared" si="20"/>
-        <v>0.94136531843170146</v>
-      </c>
-      <c r="I98">
-        <f t="shared" ref="I98:I108" si="22">H98*((E98/D98)^2 +(G98/F98)^2)^0.5</f>
-        <v>5.6090242266994626E-2</v>
+        <v>0</v>
+      </c>
+      <c r="I98" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="J98" s="3"/>
-      <c r="L98" s="2">
-        <v>8.2939222535956595E-6</v>
+      <c r="L98">
+        <v>7.8399076922384297E-4</v>
       </c>
       <c r="M98" s="2">
-        <v>6.5137642973133701E-10</v>
-      </c>
-      <c r="N98" s="2">
-        <v>9.0584844834530308E-6</v>
-      </c>
-      <c r="O98" s="2">
-        <v>3.4986008675390597E-8</v>
-      </c>
+        <v>5.9026868869718298E-7</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" s="7">
         <f t="shared" si="21"/>
-        <v>1.0921834334202869</v>
-      </c>
-      <c r="Q98">
-        <f t="shared" ref="Q98:Q108" si="23">P98*((M98/L98)^2 +(O98/N98)^2)^0.5</f>
-        <v>4.2191426521967484E-3</v>
+        <v>0</v>
+      </c>
+      <c r="Q98" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="2">
-        <v>6.1716272823234006E-5</v>
+      <c r="D99">
+        <v>4.50679407740522E-3</v>
       </c>
       <c r="E99" s="2">
-        <v>6.1045414632846902E-7</v>
-      </c>
-      <c r="F99" s="2">
-        <v>6.3482932830325706E-5</v>
-      </c>
-      <c r="G99" s="2">
-        <v>3.60978873315252E-6</v>
-      </c>
+        <v>4.2647960521843998E-6</v>
+      </c>
+      <c r="G99" s="2"/>
       <c r="H99" s="7">
         <f t="shared" si="20"/>
-        <v>1.0286255136007925</v>
-      </c>
-      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="I99" t="e">
         <f t="shared" si="22"/>
-        <v>5.9368399452460099E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J99" s="3"/>
-      <c r="L99" s="2">
-        <v>1.6584717487230401E-5</v>
+      <c r="L99">
+        <v>1.1685174391520899E-3</v>
       </c>
       <c r="M99" s="2">
-        <v>9.5827412509581596E-10</v>
-      </c>
-      <c r="N99" s="2">
-        <v>1.8015958629727299E-5</v>
-      </c>
-      <c r="O99" s="2">
-        <v>4.7067091196410602E-8</v>
-      </c>
+        <v>1.1542133311304201E-6</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" s="7">
         <f t="shared" si="21"/>
-        <v>1.0862987954783612</v>
-      </c>
-      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="e">
         <f t="shared" si="23"/>
-        <v>2.8386736943042967E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="2"/>
       <c r="D100">
-        <v>6.0505811187779902E-4</v>
+        <v>5.9662056707135503E-3</v>
       </c>
       <c r="E100" s="2">
-        <v>6.2227048628412204E-6</v>
-      </c>
-      <c r="F100">
-        <v>6.0149819016529205E-4</v>
-      </c>
-      <c r="G100" s="2">
-        <v>9.5041411355122102E-6</v>
-      </c>
+        <v>5.40641051549475E-6</v>
+      </c>
+      <c r="G100" s="2"/>
       <c r="H100" s="7">
         <f t="shared" si="20"/>
-        <v>0.9941163970160507</v>
-      </c>
-      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="I100" t="e">
         <f t="shared" si="22"/>
-        <v>1.8742062977829224E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J100" s="3"/>
       <c r="L100">
-        <v>1.65347418242078E-4</v>
+        <v>1.54673264952424E-3</v>
       </c>
       <c r="M100" s="2">
-        <v>4.4169022911434699E-8</v>
-      </c>
-      <c r="N100">
-        <v>1.7808774168493101E-4</v>
-      </c>
-      <c r="O100" s="2">
-        <v>3.7860183174411499E-7</v>
-      </c>
+        <v>1.51849573172552E-6</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" s="7">
         <f t="shared" si="21"/>
-        <v>1.077051843798374</v>
-      </c>
-      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="e">
         <f t="shared" si="23"/>
-        <v>2.3077404266662912E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="2"/>
       <c r="D101">
-        <v>1.55173323107442E-3</v>
+        <v>8.7899155121648007E-3</v>
       </c>
       <c r="E101" s="2">
-        <v>1.5774639800406199E-5</v>
-      </c>
-      <c r="F101">
-        <v>1.5007024880700499E-3</v>
-      </c>
-      <c r="G101" s="2">
-        <v>3.0023103089761202E-5</v>
+        <v>8.4141165447635294E-6</v>
       </c>
       <c r="H101" s="7">
         <f t="shared" si="20"/>
-        <v>0.96711371388944445</v>
-      </c>
-      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="I101" t="e">
         <f t="shared" si="22"/>
-        <v>2.1702713314854891E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J101" s="3"/>
       <c r="L101">
-        <v>4.1085203990469599E-4</v>
+        <v>2.2773061972286E-3</v>
       </c>
       <c r="M101" s="2">
-        <v>2.4691399158869002E-7</v>
-      </c>
-      <c r="N101">
-        <v>4.4228220783613199E-4</v>
-      </c>
-      <c r="O101" s="2">
-        <v>1.39675310994538E-6</v>
-      </c>
+        <v>1.8388961974808701E-6</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" s="7">
         <f t="shared" si="21"/>
-        <v>1.0764999680632636</v>
-      </c>
-      <c r="Q101">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="e">
         <f t="shared" si="23"/>
-        <v>3.4606604608369345E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="2"/>
       <c r="D102">
-        <v>3.0229060960917302E-3</v>
+        <v>1.42163192656607E-2</v>
       </c>
       <c r="E102" s="2">
-        <v>2.23186778519928E-5</v>
-      </c>
-      <c r="F102">
-        <v>2.977464525343E-3</v>
-      </c>
-      <c r="G102" s="2">
-        <v>3.6104254533129998E-5</v>
+        <v>1.2836259331731899E-5</v>
       </c>
       <c r="H102" s="7">
         <f t="shared" si="20"/>
-        <v>0.98496758771055415</v>
-      </c>
-      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="I102" t="e">
         <f t="shared" si="22"/>
-        <v>1.3983327786787465E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J102" s="3"/>
       <c r="L102">
-        <v>8.1568580924759203E-4</v>
+        <v>3.6770878239360399E-3</v>
       </c>
       <c r="M102" s="2">
-        <v>4.4132856865932101E-7</v>
-      </c>
-      <c r="N102">
-        <v>8.7599322258741696E-4</v>
-      </c>
-      <c r="O102" s="2">
-        <v>2.1248965167792701E-6</v>
-      </c>
+        <v>3.3129308552088702E-6</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" s="7">
         <f t="shared" si="21"/>
-        <v>1.0739346114105552</v>
-      </c>
-      <c r="Q102">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="e">
         <f t="shared" si="23"/>
-        <v>2.6690584383735365E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="2"/>
       <c r="D103">
-        <v>4.5297738748968199E-3</v>
+        <v>2.6357970030464899E-2</v>
       </c>
       <c r="E103" s="2">
-        <v>3.1479306725822998E-5</v>
-      </c>
-      <c r="F103">
-        <v>4.4678272162142502E-3</v>
-      </c>
-      <c r="G103" s="2">
-        <v>5.3376428255693398E-5</v>
+        <v>2.4421328068662499E-5</v>
       </c>
       <c r="H103" s="7">
         <f t="shared" si="20"/>
-        <v>0.98632455826859999</v>
-      </c>
-      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="I103" t="e">
         <f t="shared" si="22"/>
-        <v>1.3632043855754318E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J103" s="3"/>
       <c r="L103">
-        <v>1.21297096634525E-3</v>
+        <v>6.7939382709162497E-3</v>
       </c>
       <c r="M103" s="2">
-        <v>6.5707220069548105E-7</v>
-      </c>
-      <c r="N103">
-        <v>1.3016696026088199E-3</v>
-      </c>
-      <c r="O103" s="2">
-        <v>2.2955550158876999E-6</v>
-      </c>
+        <v>5.8793471054976199E-6</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" s="7">
         <f t="shared" si="21"/>
-        <v>1.0731251107607496</v>
-      </c>
-      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="e">
         <f t="shared" si="23"/>
-        <v>1.9797749930070513E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="B104" s="4"/>
-      <c r="C104" s="2"/>
-      <c r="D104">
-        <v>5.9443297707853001E-3</v>
-      </c>
-      <c r="E104" s="2">
-        <v>4.4197559451229203E-5</v>
-      </c>
-      <c r="F104">
-        <v>5.7736310208035199E-3</v>
-      </c>
-      <c r="G104" s="2">
-        <v>6.5932951855723193E-5</v>
-      </c>
-      <c r="H104" s="7">
+      <c r="H104" s="7" t="e">
         <f t="shared" si="20"/>
-        <v>0.97128376847113762</v>
-      </c>
-      <c r="I104">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I104" t="e">
         <f t="shared" si="22"/>
-        <v>1.3235562537093912E-2</v>
-      </c>
-      <c r="J104" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J104" s="4"/>
       <c r="L104">
-        <v>1.6025253128139399E-3</v>
+        <v>9.5123806968783701E-3</v>
       </c>
       <c r="M104" s="2">
-        <v>8.43601312390377E-7</v>
-      </c>
-      <c r="N104">
-        <v>1.7192967813367899E-3</v>
-      </c>
-      <c r="O104" s="2">
-        <v>2.5653488738575302E-6</v>
-      </c>
+        <v>7.1281968286277104E-6</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" s="7">
         <f t="shared" si="21"/>
-        <v>1.072867160093594</v>
-      </c>
-      <c r="Q104">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="e">
         <f t="shared" si="23"/>
-        <v>1.6975241549356845E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>150</v>
+        <v>999.99</v>
       </c>
       <c r="B105" s="4"/>
-      <c r="C105" s="2"/>
-      <c r="D105">
-        <v>8.8688024294768606E-3</v>
-      </c>
-      <c r="E105" s="2">
-        <v>8.64673685972853E-5</v>
-      </c>
-      <c r="F105">
-        <v>8.9708252184253507E-3</v>
-      </c>
-      <c r="G105">
-        <v>1.07321967977767E-4</v>
-      </c>
-      <c r="H105" s="7">
+      <c r="H105" s="7" t="e">
         <f t="shared" si="20"/>
-        <v>1.0115035586551575</v>
-      </c>
-      <c r="I105">
-        <f t="shared" si="22"/>
-        <v>1.5610580768600358E-2</v>
-      </c>
-      <c r="J105" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I105" t="e">
+        <f>H105*((E105/D105)^2 +(G105/F105)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J105" s="4"/>
       <c r="L105">
-        <v>2.3624849736499499E-3</v>
+        <v>1.18865612101144E-2</v>
       </c>
       <c r="M105" s="2">
-        <v>4.7793189465346599E-6</v>
-      </c>
-      <c r="N105">
-        <v>2.5326367860936398E-3</v>
-      </c>
-      <c r="O105" s="2">
-        <v>1.52949389777083E-5</v>
-      </c>
+        <v>1.1116236336809801E-5</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" s="7">
         <f t="shared" si="21"/>
-        <v>1.0720223892814065</v>
-      </c>
-      <c r="Q105">
-        <f t="shared" si="23"/>
-        <v>6.8276732829171474E-3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>250</v>
-      </c>
-      <c r="B106" s="4"/>
-      <c r="C106" s="2"/>
-      <c r="D106">
-        <v>1.41291716026036E-2</v>
-      </c>
-      <c r="E106">
-        <v>1.2701448940347901E-4</v>
-      </c>
-      <c r="F106">
-        <v>1.4211687544004301E-2</v>
-      </c>
-      <c r="G106">
-        <v>1.35424324665508E-4</v>
-      </c>
-      <c r="H106" s="7">
-        <f t="shared" si="20"/>
-        <v>1.0058401117716975</v>
-      </c>
-      <c r="I106">
-        <f t="shared" si="22"/>
-        <v>1.3176692895934624E-2</v>
-      </c>
-      <c r="J106" s="3"/>
-      <c r="L106">
-        <v>3.8066986683040699E-3</v>
-      </c>
-      <c r="M106" s="2">
-        <v>7.1199445287493598E-6</v>
-      </c>
-      <c r="N106">
-        <v>4.06594125013788E-3</v>
-      </c>
-      <c r="O106" s="2">
-        <v>1.9233271963887199E-5</v>
-      </c>
-      <c r="P106" s="7">
-        <f t="shared" si="21"/>
-        <v>1.0681016819094078</v>
-      </c>
-      <c r="Q106">
-        <f t="shared" si="23"/>
-        <v>5.4330985143524625E-3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>500</v>
-      </c>
-      <c r="B107" s="4"/>
-      <c r="C107" s="2"/>
-      <c r="D107">
-        <v>2.6412920287671102E-2</v>
-      </c>
-      <c r="E107">
-        <v>2.50464228629676E-4</v>
-      </c>
-      <c r="F107">
-        <v>2.6280614429993899E-2</v>
-      </c>
-      <c r="G107">
-        <v>2.1153344132830099E-4</v>
-      </c>
-      <c r="H107" s="7">
-        <f t="shared" si="20"/>
-        <v>0.99499086597633957</v>
-      </c>
-      <c r="I107">
-        <f t="shared" si="22"/>
-        <v>1.2375836533726817E-2</v>
-      </c>
-      <c r="J107" s="3"/>
-      <c r="L107">
-        <v>7.0792469987117704E-3</v>
-      </c>
-      <c r="M107" s="2">
-        <v>1.4039153971000801E-5</v>
-      </c>
-      <c r="N107">
-        <v>7.4545207369257497E-3</v>
-      </c>
-      <c r="O107" s="2">
-        <v>2.74836429813361E-5</v>
-      </c>
-      <c r="P107" s="7">
-        <f t="shared" si="21"/>
-        <v>1.0530104032649614</v>
-      </c>
-      <c r="Q107">
-        <f t="shared" si="23"/>
-        <v>4.4082869149599533E-3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>750</v>
-      </c>
-      <c r="B108" s="4"/>
-      <c r="D108">
-        <v>3.7189611020955998E-2</v>
-      </c>
-      <c r="E108">
-        <v>2.6780446143014698E-4</v>
-      </c>
-      <c r="F108">
-        <v>3.6500899186449498E-2</v>
-      </c>
-      <c r="G108">
-        <v>3.3888685585804502E-4</v>
-      </c>
-      <c r="H108" s="7">
-        <f t="shared" si="20"/>
-        <v>0.98148106915884603</v>
-      </c>
-      <c r="I108">
-        <f t="shared" si="22"/>
-        <v>1.1532056843165576E-2</v>
-      </c>
-      <c r="J108" s="4"/>
-      <c r="L108">
-        <v>9.8591559798638494E-3</v>
-      </c>
-      <c r="M108" s="2">
-        <v>1.78953637014576E-5</v>
-      </c>
-      <c r="N108">
-        <v>1.03866620055335E-2</v>
-      </c>
-      <c r="O108" s="2">
-        <v>3.5045910152349199E-5</v>
-      </c>
-      <c r="P108" s="7">
-        <f t="shared" si="21"/>
-        <v>1.0535041769038871</v>
-      </c>
-      <c r="Q108">
-        <f t="shared" si="23"/>
-        <v>4.0363538835675129E-3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>999.99</v>
-      </c>
-      <c r="B109" s="4"/>
-      <c r="D109">
-        <v>4.6608250330168598E-2</v>
-      </c>
-      <c r="E109">
-        <v>4.8601393337740302E-4</v>
-      </c>
-      <c r="F109">
-        <v>4.6712105802624602E-2</v>
-      </c>
-      <c r="G109">
-        <v>3.0133062649586901E-4</v>
-      </c>
-      <c r="H109" s="7">
-        <f t="shared" si="20"/>
-        <v>1.0022282637026771</v>
-      </c>
-      <c r="I109">
-        <f>H109*((E109/D109)^2 +(G109/F109)^2)^0.5</f>
-        <v>1.2288989739259801E-2</v>
-      </c>
-      <c r="J109" s="4"/>
-      <c r="L109">
-        <v>1.21377195834136E-2</v>
-      </c>
-      <c r="M109" s="2">
-        <v>2.3785825815868901E-5</v>
-      </c>
-      <c r="N109">
-        <v>1.2901873532126599E-2</v>
-      </c>
-      <c r="O109" s="2">
-        <v>3.9818562387638897E-5</v>
-      </c>
-      <c r="P109" s="7">
-        <f t="shared" si="21"/>
-        <v>1.0629569618462127</v>
-      </c>
-      <c r="Q109">
-        <f>P109*((M109/L109)^2 +(O109/N109)^2)^0.5</f>
-        <v>3.8860182732644031E-3</v>
+        <v>0</v>
+      </c>
+      <c r="Q105" t="e">
+        <f>P105*((M105/L105)^2 +(O105/N105)^2)^0.5</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>

--- a/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCF5112-228B-4CCD-9797-84B902552570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E75EC8-2429-4937-84C1-8F69EF79AD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,9 +84,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
@@ -188,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -202,7 +201,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
@@ -355,7 +353,7 @@
             <c:numRef>
               <c:f>'Sheet 1'!$H$22:$H$34</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.60921857304058236</c:v>
@@ -483,7 +481,7 @@
             <c:numRef>
               <c:f>'Sheet 1'!$P$22:$P$34</c:f>
               <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.79502846395901039</c:v>
@@ -611,6 +609,7 @@
         <c:axId val="1123278832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.60000000000000009"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -628,7 +627,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1353,7 +1352,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$59:$A$71</c:f>
+              <c:f>'Sheet 1'!$A$58:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1401,33 +1400,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$59:$H$71</c:f>
+              <c:f>'Sheet 1'!$H$58:$H$70</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.99993437221506987</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.99989465428678881</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.0001118652934071</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1.0006521541936946</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.0008552139696782</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.9985991170648062</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1.000158697400007</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.99934719791660742</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1481,7 +1480,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$59:$A$71</c:f>
+              <c:f>'Sheet 1'!$A$58:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1529,7 +1528,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$59:$P$71</c:f>
+              <c:f>'Sheet 1'!$P$58:$P$70</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1537,40 +1536,40 @@
                   <c:v>0.99993184010427161</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.99992154571058711</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.000128920820752</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1.0007211723260472</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.0010026042601898</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.99988394710871187</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.99879697477531193</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.0012050548156031</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.99847576884532241</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1.0014439295128328</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.99921943172111527</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.0014692509552563</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1.0006593477660861</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1877,7 +1876,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
+              <c:f>'Sheet 1'!$A$75:$A$87</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1925,33 +1924,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$76:$H$88</c:f>
+              <c:f>'Sheet 1'!$H$75:$H$87</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.98601165380192901</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.98603287402090212</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.9855719206675112</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.98634021323125154</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.9862332820411307</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.98647575468924231</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.98895995592999619</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.98981091518856013</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1974,7 +1973,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6C71-4D74-B5A8-4EE6279B7B3D}"/>
+              <c16:uniqueId val="{00000000-5362-4A7B-A534-AD8816811D32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2005,7 +2004,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
+              <c:f>'Sheet 1'!$A$75:$A$87</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2053,7 +2052,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$76:$P$88</c:f>
+              <c:f>'Sheet 1'!$P$75:$P$87</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2061,40 +2060,40 @@
                   <c:v>0.98943213465866797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.98955842468785971</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.99092684983558765</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.99194122282307995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.99181184221971841</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.99043981308751894</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.99105825776439138</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.99365128006879655</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.9912245970448289</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.99416288046614987</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.99302714608761333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.99504565831713798</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.99467808373198352</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2102,7 +2101,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6C71-4D74-B5A8-4EE6279B7B3D}"/>
+              <c16:uniqueId val="{00000001-5362-4A7B-A534-AD8816811D32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2404,7 +2403,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
+              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2452,48 +2451,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$76:$H$88</c:f>
+              <c:f>'Sheet 1'!$H$22:$H$34</c:f>
               <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.60921857304058236</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.6202561947395715</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.61752137885807601</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.63758916509434371</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.66203600474217295</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.70507179114481311</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.7294127014308962</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.75883175130100222</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.79545758961655577</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.84382782080221264</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.90466917724369844</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.93426211404435788</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.94461149030720559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2501,7 +2500,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5362-4A7B-A534-AD8816811D32}"/>
+              <c16:uniqueId val="{00000000-9A88-40A7-9744-FFC75830134C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2532,7 +2531,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$76:$A$88</c:f>
+              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2580,48 +2579,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$76:$P$88</c:f>
+              <c:f>'Sheet 1'!$P$22:$P$34</c:f>
               <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.98943213465866797</c:v>
+                  <c:v>0.79502846395901039</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.79868938528194633</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.79518763707084539</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.80345865035736497</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.81088238286163838</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.82902260635681613</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.83691230418362095</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.85434998565560982</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.87107729502555376</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.89761675786997808</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.93561261604161028</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.94942620263109356</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.95529529971486393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2629,7 +2628,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5362-4A7B-A534-AD8816811D32}"/>
+              <c16:uniqueId val="{00000001-9A88-40A7-9744-FFC75830134C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2641,13 +2640,12 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1342380336"/>
-        <c:axId val="1342369296"/>
+        <c:axId val="1154162240"/>
+        <c:axId val="1123278832"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1342380336"/>
+        <c:axId val="1154162240"/>
         <c:scaling>
-          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -2703,16 +2701,15 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1342369296"/>
+        <c:crossAx val="1123278832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1342369296"/>
+        <c:axId val="1123278832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1.08"/>
-          <c:min val="1.03"/>
+          <c:min val="0.60000000000000009"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2730,7 +2727,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2767,7 +2764,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1342380336"/>
+        <c:crossAx val="1154162240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2931,7 +2928,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
+              <c:f>'Sheet 1'!$A$75:$A$87</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2979,48 +2976,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$22:$H$34</c:f>
+              <c:f>'Sheet 1'!$H$75:$H$87</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.60921857304058236</c:v>
+                  <c:v>0.98601165380192901</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6202561947395715</c:v>
+                  <c:v>0.98603287402090212</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.61752137885807601</c:v>
+                  <c:v>0.9855719206675112</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.63758916509434371</c:v>
+                  <c:v>0.98634021323125154</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.66203600474217295</c:v>
+                  <c:v>0.9862332820411307</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.70507179114481311</c:v>
+                  <c:v>0.98647575468924231</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.7294127014308962</c:v>
+                  <c:v>0.98895995592999619</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.75883175130100222</c:v>
+                  <c:v>0.98981091518856013</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.79545758961655577</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.84382782080221264</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.90466917724369844</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.93426211404435788</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.94461149030720559</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3028,7 +3025,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9A88-40A7-9744-FFC75830134C}"/>
+              <c16:uniqueId val="{00000000-C150-436E-9F5E-D1F4ADB78459}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3059,7 +3056,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$22:$A$34</c:f>
+              <c:f>'Sheet 1'!$A$75:$A$87</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -3107,48 +3104,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$22:$P$34</c:f>
+              <c:f>'Sheet 1'!$P$75:$P$87</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.79502846395901039</c:v>
+                  <c:v>0.98943213465866797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.79868938528194633</c:v>
+                  <c:v>0.98955842468785971</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.79518763707084539</c:v>
+                  <c:v>0.99092684983558765</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.80345865035736497</c:v>
+                  <c:v>0.99194122282307995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.81088238286163838</c:v>
+                  <c:v>0.99181184221971841</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.82902260635681613</c:v>
+                  <c:v>0.99043981308751894</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.83691230418362095</c:v>
+                  <c:v>0.99105825776439138</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.85434998565560982</c:v>
+                  <c:v>0.99365128006879655</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.87107729502555376</c:v>
+                  <c:v>0.9912245970448289</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.89761675786997808</c:v>
+                  <c:v>0.99416288046614987</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.93561261604161028</c:v>
+                  <c:v>0.99302714608761333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.94942620263109356</c:v>
+                  <c:v>0.99504565831713798</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.95529529971486393</c:v>
+                  <c:v>0.99467808373198352</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3156,7 +3153,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9A88-40A7-9744-FFC75830134C}"/>
+              <c16:uniqueId val="{00000001-C150-436E-9F5E-D1F4ADB78459}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3168,11 +3165,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1154162240"/>
-        <c:axId val="1123278832"/>
+        <c:axId val="41004240"/>
+        <c:axId val="41003280"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1154162240"/>
+        <c:axId val="41004240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3229,14 +3226,16 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1123278832"/>
+        <c:crossAx val="41003280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1123278832"/>
+        <c:axId val="41003280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.98"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3254,7 +3253,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3291,7 +3290,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1154162240"/>
+        <c:crossAx val="41004240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6792,13 +6791,13 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>53010</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>159027</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>357810</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6828,49 +6827,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>417444</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>112644</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>112644</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{245022B1-EA92-9A14-99B5-645E9443F9AD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>417444</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>112644</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>112644</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6892,7 +6855,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6902,13 +6865,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>583097</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>278297</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>145775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6923,6 +6886,42 @@
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>66259</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>26503</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57584190-F101-F6B1-333F-2773F4588EAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7202,7 +7201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -7240,71 +7239,71 @@
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="14"/>
-      <c r="K3" s="17" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="13"/>
+      <c r="K3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="15" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="6"/>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="Q4" s="18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -7939,71 +7938,71 @@
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14"/>
-      <c r="K20" s="17" t="s">
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="13"/>
+      <c r="K20" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="17"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="5"/>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="16" t="s">
+      <c r="I21" s="15" t="s">
         <v>12</v>
       </c>
       <c r="J21" s="6"/>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="L21" s="18" t="s">
+      <c r="L21" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="18" t="s">
+      <c r="M21" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="N21" s="18" t="s">
+      <c r="N21" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="18" t="s">
+      <c r="O21" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="P21" s="19" t="s">
+      <c r="P21" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="Q21" s="19" t="s">
+      <c r="Q21" s="18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -8025,7 +8024,7 @@
       <c r="G22" s="2">
         <v>2.0927702439166299E-7</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="20">
         <f t="shared" ref="H22:H34" si="4">F22/D22</f>
         <v>0.60921857304058236</v>
       </c>
@@ -8047,7 +8046,7 @@
       <c r="O22" s="2">
         <v>1.9145364499554299E-7</v>
       </c>
-      <c r="P22" s="7">
+      <c r="P22" s="20">
         <f t="shared" ref="P22:P34" si="5">N22/L22</f>
         <v>0.79502846395901039</v>
       </c>
@@ -8073,7 +8072,7 @@
       <c r="G23" s="2">
         <v>5.7726857720944404E-7</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="20">
         <f t="shared" si="4"/>
         <v>0.6202561947395715</v>
       </c>
@@ -8094,7 +8093,7 @@
       <c r="O23" s="2">
         <v>4.68863518091893E-7</v>
       </c>
-      <c r="P23" s="7">
+      <c r="P23" s="20">
         <f t="shared" si="5"/>
         <v>0.79868938528194633</v>
       </c>
@@ -8120,7 +8119,7 @@
       <c r="G24" s="2">
         <v>5.2379806742420601E-7</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="20">
         <f t="shared" si="4"/>
         <v>0.61752137885807601</v>
       </c>
@@ -8141,7 +8140,7 @@
       <c r="O24" s="2">
         <v>9.0505031340599802E-7</v>
       </c>
-      <c r="P24" s="7">
+      <c r="P24" s="20">
         <f t="shared" si="5"/>
         <v>0.79518763707084539</v>
       </c>
@@ -8167,7 +8166,7 @@
       <c r="G25" s="2">
         <v>7.9830127854263004E-6</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="20">
         <f t="shared" si="4"/>
         <v>0.63758916509434371</v>
       </c>
@@ -8188,7 +8187,7 @@
       <c r="O25" s="2">
         <v>5.9219411899510302E-6</v>
       </c>
-      <c r="P25" s="7">
+      <c r="P25" s="20">
         <f t="shared" si="5"/>
         <v>0.80345865035736497</v>
       </c>
@@ -8214,7 +8213,7 @@
       <c r="G26" s="2">
         <v>3.8471504916950201E-5</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="20">
         <f t="shared" si="4"/>
         <v>0.66203600474217295</v>
       </c>
@@ -8235,7 +8234,7 @@
       <c r="O26" s="2">
         <v>3.18696827410922E-5</v>
       </c>
-      <c r="P26" s="7">
+      <c r="P26" s="20">
         <f t="shared" si="5"/>
         <v>0.81088238286163838</v>
       </c>
@@ -8261,7 +8260,7 @@
       <c r="G27" s="2">
         <v>4.5047478405430597E-5</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="20">
         <f t="shared" si="4"/>
         <v>0.70507179114481311</v>
       </c>
@@ -8282,7 +8281,7 @@
       <c r="O27" s="2">
         <v>3.9763991456282801E-5</v>
       </c>
-      <c r="P27" s="7">
+      <c r="P27" s="20">
         <f t="shared" si="5"/>
         <v>0.82902260635681613</v>
       </c>
@@ -8308,7 +8307,7 @@
       <c r="G28" s="2">
         <v>5.7019554655065601E-5</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="20">
         <f t="shared" si="4"/>
         <v>0.7294127014308962</v>
       </c>
@@ -8329,7 +8328,7 @@
       <c r="O28" s="2">
         <v>7.9317497610751093E-5</v>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="20">
         <f t="shared" si="5"/>
         <v>0.83691230418362095</v>
       </c>
@@ -8355,7 +8354,7 @@
       <c r="G29" s="2">
         <v>6.7768751133343504E-5</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="20">
         <f t="shared" si="4"/>
         <v>0.75883175130100222</v>
       </c>
@@ -8376,7 +8375,7 @@
       <c r="O29" s="2">
         <v>7.3233726308046104E-5</v>
       </c>
-      <c r="P29" s="7">
+      <c r="P29" s="20">
         <f t="shared" si="5"/>
         <v>0.85434998565560982</v>
       </c>
@@ -8402,7 +8401,7 @@
       <c r="G30" s="2">
         <v>8.6284137744803305E-5</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="20">
         <f t="shared" si="4"/>
         <v>0.79545758961655577</v>
       </c>
@@ -8423,7 +8422,7 @@
       <c r="O30" s="2">
         <v>9.2508457557128094E-5</v>
       </c>
-      <c r="P30" s="7">
+      <c r="P30" s="20">
         <f t="shared" si="5"/>
         <v>0.87107729502555376</v>
       </c>
@@ -8449,7 +8448,7 @@
       <c r="G31">
         <v>1.02719911855704E-4</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="20">
         <f t="shared" si="4"/>
         <v>0.84382782080221264</v>
       </c>
@@ -8470,7 +8469,7 @@
       <c r="O31">
         <v>1.27660413881626E-4</v>
       </c>
-      <c r="P31" s="7">
+      <c r="P31" s="20">
         <f t="shared" si="5"/>
         <v>0.89761675786997808</v>
       </c>
@@ -8496,7 +8495,7 @@
       <c r="G32">
         <v>1.76730090656541E-4</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="20">
         <f t="shared" si="4"/>
         <v>0.90466917724369844</v>
       </c>
@@ -8517,7 +8516,7 @@
       <c r="O32">
         <v>1.98888364809949E-4</v>
       </c>
-      <c r="P32" s="7">
+      <c r="P32" s="20">
         <f t="shared" si="5"/>
         <v>0.93561261604161028</v>
       </c>
@@ -8543,7 +8542,7 @@
       <c r="G33">
         <v>2.1338189128953199E-4</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="20">
         <f t="shared" si="4"/>
         <v>0.93426211404435788</v>
       </c>
@@ -8564,7 +8563,7 @@
       <c r="O33">
         <v>1.9611456455849799E-4</v>
       </c>
-      <c r="P33" s="7">
+      <c r="P33" s="20">
         <f t="shared" si="5"/>
         <v>0.94942620263109356</v>
       </c>
@@ -8590,7 +8589,7 @@
       <c r="G34">
         <v>2.5258738046347602E-4</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="20">
         <f t="shared" si="4"/>
         <v>0.94461149030720559</v>
       </c>
@@ -8611,7 +8610,7 @@
       <c r="O34">
         <v>2.6397948509944901E-4</v>
       </c>
-      <c r="P34" s="7">
+      <c r="P34" s="20">
         <f t="shared" si="5"/>
         <v>0.95529529971486393</v>
       </c>
@@ -8620,1062 +8619,1181 @@
         <v>2.0761752123647477E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="4"/>
-      <c r="H35" s="13"/>
-      <c r="J35" s="3"/>
-      <c r="P35" s="7"/>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
+      <c r="C37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="13"/>
+      <c r="K37" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L37" s="16"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="5"/>
       <c r="C38" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J38" s="6"/>
       <c r="K38" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="17"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q38" s="18" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I39" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J39" s="6"/>
-      <c r="K39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M39" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N39" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O39" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P39" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q39" s="19" t="s">
-        <v>12</v>
+      <c r="A39">
+        <v>0.1</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2">
+        <v>3.2099701190028201E-6</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3.5131059351727902E-10</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3.17759079120563E-6</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7.4892039905947602E-9</v>
+      </c>
+      <c r="H39" s="20">
+        <f t="shared" ref="H39:H51" si="8">F39/D39</f>
+        <v>0.98991288809652567</v>
+      </c>
+      <c r="I39">
+        <f>H39*((E39/D39)^2 +(G39/F39)^2)^0.5</f>
+        <v>2.3356211349544811E-3</v>
+      </c>
+      <c r="J39" s="3"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2">
+        <v>9.0972584130535695E-7</v>
+      </c>
+      <c r="M39" s="2">
+        <v>9.7452881785433401E-11</v>
+      </c>
+      <c r="N39" s="2">
+        <v>8.9914371527988803E-7</v>
+      </c>
+      <c r="O39" s="2">
+        <v>2.24423174811288E-9</v>
+      </c>
+      <c r="P39" s="7">
+        <f t="shared" ref="P39:P51" si="9">N39/L39</f>
+        <v>0.98836778560639249</v>
+      </c>
+      <c r="Q39">
+        <f>P39*((M39/L39)^2 +(O39/N39)^2)^0.5</f>
+        <v>2.4692029617883636E-3</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="2"/>
       <c r="D40" s="2">
-        <v>3.2099701190028201E-6</v>
+        <v>1.6134855890052599E-5</v>
       </c>
       <c r="E40" s="2">
-        <v>3.5131059351727902E-10</v>
+        <v>1.4663512326686101E-9</v>
       </c>
       <c r="F40" s="2">
-        <v>3.17759079120563E-6</v>
+        <v>1.5981198165598299E-5</v>
       </c>
       <c r="G40" s="2">
-        <v>7.4892039905947602E-9</v>
-      </c>
-      <c r="H40" s="21">
-        <f t="shared" ref="H40:H52" si="8">F40/D40</f>
-        <v>0.98991288809652567</v>
+        <v>1.4864419278170099E-8</v>
+      </c>
+      <c r="H40" s="20">
+        <f t="shared" si="8"/>
+        <v>0.99047665963046916</v>
       </c>
       <c r="I40">
-        <f>H40*((E40/D40)^2 +(G40/F40)^2)^0.5</f>
-        <v>2.3356211349544811E-3</v>
+        <f t="shared" ref="I40:I50" si="10">H40*((E40/D40)^2 +(G40/F40)^2)^0.5</f>
+        <v>9.2564857174139148E-4</v>
       </c>
       <c r="J40" s="3"/>
-      <c r="K40" s="2"/>
       <c r="L40" s="2">
-        <v>9.0972584130535695E-7</v>
+        <v>4.5736608105268603E-6</v>
       </c>
       <c r="M40" s="2">
-        <v>9.7452881785433401E-11</v>
+        <v>4.4439460683920398E-10</v>
       </c>
       <c r="N40" s="2">
-        <v>8.9914371527988803E-7</v>
+        <v>4.5248201671970701E-6</v>
       </c>
       <c r="O40" s="2">
-        <v>2.24423174811288E-9</v>
+        <v>4.3753358266758202E-9</v>
       </c>
       <c r="P40" s="7">
-        <f t="shared" ref="P40:P52" si="9">N40/L40</f>
-        <v>0.98836778560639249</v>
+        <f t="shared" si="9"/>
+        <v>0.98932132369383907</v>
       </c>
       <c r="Q40">
-        <f>P40*((M40/L40)^2 +(O40/N40)^2)^0.5</f>
-        <v>2.4692029617883636E-3</v>
+        <f t="shared" ref="Q40:Q50" si="11">P40*((M40/L40)^2 +(O40/N40)^2)^0.5</f>
+        <v>9.6145500722271619E-4</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="B41" s="4"/>
       <c r="D41" s="2">
-        <v>1.6134855890052599E-5</v>
+        <v>3.2313738532959303E-5</v>
       </c>
       <c r="E41" s="2">
-        <v>1.4663512326686101E-9</v>
+        <v>3.1962942854569601E-9</v>
       </c>
       <c r="F41" s="2">
-        <v>1.5981198165598299E-5</v>
+        <v>3.2065564782420801E-5</v>
       </c>
       <c r="G41" s="2">
-        <v>1.4864419278170099E-8</v>
-      </c>
-      <c r="H41" s="21">
+        <v>2.3626963147609399E-8</v>
+      </c>
+      <c r="H41" s="20">
         <f t="shared" si="8"/>
-        <v>0.99047665963046916</v>
+        <v>0.99231986882961964</v>
       </c>
       <c r="I41">
-        <f t="shared" ref="I41:I51" si="10">H41*((E41/D41)^2 +(G41/F41)^2)^0.5</f>
-        <v>9.2564857174139148E-4</v>
+        <f t="shared" si="10"/>
+        <v>7.3773278699735829E-4</v>
       </c>
       <c r="J41" s="3"/>
       <c r="L41" s="2">
-        <v>4.5736608105268603E-6</v>
+        <v>9.1603462828245198E-6</v>
       </c>
       <c r="M41" s="2">
-        <v>4.4439460683920398E-10</v>
+        <v>9.3941163470923E-10</v>
       </c>
       <c r="N41" s="2">
-        <v>4.5248201671970701E-6</v>
+        <v>9.0779232505914901E-6</v>
       </c>
       <c r="O41" s="2">
-        <v>4.3753358266758202E-9</v>
+        <v>6.6276429568322101E-9</v>
       </c>
       <c r="P41" s="7">
         <f t="shared" si="9"/>
-        <v>0.98932132369383907</v>
+        <v>0.9910021925276371</v>
       </c>
       <c r="Q41">
-        <f t="shared" ref="Q41:Q51" si="11">P41*((M41/L41)^2 +(O41/N41)^2)^0.5</f>
-        <v>9.6145500722271619E-4</v>
+        <f t="shared" si="11"/>
+        <v>7.3061732078473008E-4</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B42" s="4"/>
-      <c r="D42" s="2">
-        <v>3.2313738532959303E-5</v>
+      <c r="D42">
+        <v>3.2313466424565402E-4</v>
       </c>
       <c r="E42" s="2">
-        <v>3.1962942854569601E-9</v>
-      </c>
-      <c r="F42" s="2">
-        <v>3.2065564782420801E-5</v>
+        <v>1.07210572664496E-7</v>
+      </c>
+      <c r="F42">
+        <v>3.2203551019660299E-4</v>
       </c>
       <c r="G42" s="2">
-        <v>2.3626963147609399E-8</v>
-      </c>
-      <c r="H42" s="21">
+        <v>2.0328657361107299E-7</v>
+      </c>
+      <c r="H42" s="20">
         <f t="shared" si="8"/>
-        <v>0.99231986882961964</v>
+        <v>0.9965984644463417</v>
       </c>
       <c r="I42">
         <f t="shared" si="10"/>
-        <v>7.3773278699735829E-4</v>
+        <v>7.1071026643292393E-4</v>
       </c>
       <c r="J42" s="3"/>
       <c r="L42" s="2">
-        <v>9.1603462828245198E-6</v>
+        <v>9.1589301211133205E-5</v>
       </c>
       <c r="M42" s="2">
-        <v>9.3941163470923E-10</v>
+        <v>3.0347199669865102E-8</v>
       </c>
       <c r="N42" s="2">
-        <v>9.0779232505914901E-6</v>
+        <v>9.1214157329342301E-5</v>
       </c>
       <c r="O42" s="2">
-        <v>6.6276429568322101E-9</v>
+        <v>6.40943486895766E-8</v>
       </c>
       <c r="P42" s="7">
         <f t="shared" si="9"/>
-        <v>0.9910021925276371</v>
+        <v>0.99590406437400247</v>
       </c>
       <c r="Q42">
         <f t="shared" si="11"/>
-        <v>7.3061732078473008E-4</v>
+        <v>7.736996230761808E-4</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B43" s="4"/>
       <c r="D43">
-        <v>3.2313466424565402E-4</v>
+        <v>8.0491667998632097E-4</v>
       </c>
       <c r="E43" s="2">
-        <v>1.07210572664496E-7</v>
+        <v>9.736275950164889E-7</v>
       </c>
       <c r="F43">
-        <v>3.2203551019660299E-4</v>
+        <v>8.03016350656239E-4</v>
       </c>
       <c r="G43" s="2">
-        <v>2.0328657361107299E-7</v>
-      </c>
-      <c r="H43" s="21">
+        <v>1.71923510353115E-6</v>
+      </c>
+      <c r="H43" s="20">
         <f t="shared" si="8"/>
-        <v>0.9965984644463417</v>
+        <v>0.99763909808638296</v>
       </c>
       <c r="I43">
         <f t="shared" si="10"/>
-        <v>7.1071026643292393E-4</v>
+        <v>2.4532373787551002E-3</v>
       </c>
       <c r="J43" s="3"/>
-      <c r="L43" s="2">
-        <v>9.1589301211133205E-5</v>
+      <c r="L43">
+        <v>2.2814984705325501E-4</v>
       </c>
       <c r="M43" s="2">
-        <v>3.0347199669865102E-8</v>
-      </c>
-      <c r="N43" s="2">
-        <v>9.1214157329342301E-5</v>
+        <v>3.1680978680584301E-7</v>
+      </c>
+      <c r="N43">
+        <v>2.2747099914478301E-4</v>
       </c>
       <c r="O43" s="2">
-        <v>6.40943486895766E-8</v>
+        <v>5.1766354897946596E-7</v>
       </c>
       <c r="P43" s="7">
         <f t="shared" si="9"/>
-        <v>0.99590406437400247</v>
+        <v>0.99702455242797716</v>
       </c>
       <c r="Q43">
         <f t="shared" si="11"/>
-        <v>7.736996230761808E-4</v>
+        <v>2.657998552514734E-3</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B44" s="4"/>
       <c r="D44">
-        <v>8.0491667998632097E-4</v>
+        <v>1.6028552618401299E-3</v>
       </c>
       <c r="E44" s="2">
-        <v>9.736275950164889E-7</v>
+        <v>1.94658668768657E-6</v>
       </c>
       <c r="F44">
-        <v>8.03016350656239E-4</v>
+        <v>1.5995099007293299E-3</v>
       </c>
       <c r="G44" s="2">
-        <v>1.71923510353115E-6</v>
-      </c>
-      <c r="H44" s="21">
+        <v>2.61096709145502E-6</v>
+      </c>
+      <c r="H44" s="20">
         <f t="shared" si="8"/>
-        <v>0.99763909808638296</v>
+        <v>0.99791287386300909</v>
       </c>
       <c r="I44">
         <f t="shared" si="10"/>
-        <v>2.4532373787551002E-3</v>
+        <v>2.0303219773658665E-3</v>
       </c>
       <c r="J44" s="3"/>
       <c r="L44">
-        <v>2.2814984705325501E-4</v>
+        <v>4.53914678418702E-4</v>
       </c>
       <c r="M44" s="2">
-        <v>3.1680978680584301E-7</v>
+        <v>6.4832174109510199E-7</v>
       </c>
       <c r="N44">
-        <v>2.2747099914478301E-4</v>
+        <v>4.515470476236E-4</v>
       </c>
       <c r="O44" s="2">
-        <v>5.1766354897946596E-7</v>
+        <v>8.0551677883601002E-7</v>
       </c>
       <c r="P44" s="7">
         <f t="shared" si="9"/>
-        <v>0.99702455242797716</v>
+        <v>0.99478397393239171</v>
       </c>
       <c r="Q44">
         <f t="shared" si="11"/>
-        <v>2.657998552514734E-3</v>
+        <v>2.2733212468731513E-3</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B45" s="4"/>
       <c r="D45">
-        <v>1.6028552618401299E-3</v>
+        <v>2.3922480224080099E-3</v>
       </c>
       <c r="E45" s="2">
-        <v>1.94658668768657E-6</v>
+        <v>2.30362531217378E-6</v>
       </c>
       <c r="F45">
-        <v>1.5995099007293299E-3</v>
+        <v>2.3832071578495199E-3</v>
       </c>
       <c r="G45" s="2">
-        <v>2.61096709145502E-6</v>
-      </c>
-      <c r="H45" s="21">
+        <v>2.9328311472635502E-6</v>
+      </c>
+      <c r="H45" s="20">
         <f t="shared" si="8"/>
-        <v>0.99791287386300909</v>
+        <v>0.99622076621077549</v>
       </c>
       <c r="I45">
         <f t="shared" si="10"/>
-        <v>2.0303219773658665E-3</v>
+        <v>1.5566935117403559E-3</v>
       </c>
       <c r="J45" s="3"/>
       <c r="L45">
-        <v>4.53914678418702E-4</v>
+        <v>6.7626891461544203E-4</v>
       </c>
       <c r="M45" s="2">
-        <v>6.4832174109510199E-7</v>
+        <v>7.9860980174835503E-7</v>
       </c>
       <c r="N45">
-        <v>4.515470476236E-4</v>
+        <v>6.7325507529300901E-4</v>
       </c>
       <c r="O45" s="2">
-        <v>8.0551677883601002E-7</v>
+        <v>9.3889317052476902E-7</v>
       </c>
       <c r="P45" s="7">
         <f t="shared" si="9"/>
-        <v>0.99478397393239171</v>
+        <v>0.99554343064231066</v>
       </c>
       <c r="Q45">
         <f t="shared" si="11"/>
-        <v>2.2733212468731513E-3</v>
+        <v>1.8192394881123154E-3</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B46" s="4"/>
       <c r="D46">
-        <v>2.3922480224080099E-3</v>
+        <v>3.1688203926765E-3</v>
       </c>
       <c r="E46" s="2">
-        <v>2.30362531217378E-6</v>
+        <v>3.8700195546849801E-6</v>
       </c>
       <c r="F46">
-        <v>2.3832071578495199E-3</v>
+        <v>3.1541405310738201E-3</v>
       </c>
       <c r="G46" s="2">
-        <v>2.9328311472635502E-6</v>
-      </c>
-      <c r="H46" s="21">
+        <v>5.7204379219245103E-6</v>
+      </c>
+      <c r="H46" s="20">
         <f t="shared" si="8"/>
-        <v>0.99622076621077549</v>
+        <v>0.99536740496980936</v>
       </c>
       <c r="I46">
         <f t="shared" si="10"/>
-        <v>1.5566935117403559E-3</v>
+        <v>2.1763688947192732E-3</v>
       </c>
       <c r="J46" s="3"/>
       <c r="L46">
-        <v>6.7626891461544203E-4</v>
+        <v>8.9635371842954504E-4</v>
       </c>
       <c r="M46" s="2">
-        <v>7.9860980174835503E-7</v>
+        <v>1.0741074178410501E-6</v>
       </c>
       <c r="N46">
-        <v>6.7325507529300901E-4</v>
+        <v>8.9292512144540401E-4</v>
       </c>
       <c r="O46" s="2">
-        <v>9.3889317052476902E-7</v>
+        <v>1.5443417647520601E-6</v>
       </c>
       <c r="P46" s="7">
         <f t="shared" si="9"/>
-        <v>0.99554343064231066</v>
+        <v>0.99617495089979868</v>
       </c>
       <c r="Q46">
         <f t="shared" si="11"/>
-        <v>1.8192394881123154E-3</v>
+        <v>2.09604744411438E-3</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="B47" s="4"/>
       <c r="D47">
-        <v>3.1688203926765E-3</v>
+        <v>4.7002672379747703E-3</v>
       </c>
       <c r="E47" s="2">
-        <v>3.8700195546849801E-6</v>
+        <v>5.5830943137030297E-6</v>
       </c>
       <c r="F47">
-        <v>3.1541405310738201E-3</v>
+        <v>4.6888544824096002E-3</v>
       </c>
       <c r="G47" s="2">
-        <v>5.7204379219245103E-6</v>
-      </c>
-      <c r="H47" s="21">
+        <v>6.9665355992869402E-6</v>
+      </c>
+      <c r="H47" s="20">
         <f t="shared" si="8"/>
-        <v>0.99536740496980936</v>
+        <v>0.99757189219520048</v>
       </c>
       <c r="I47">
         <f t="shared" si="10"/>
-        <v>2.1763688947192732E-3</v>
+        <v>1.8975971265847125E-3</v>
       </c>
       <c r="J47" s="3"/>
       <c r="L47">
-        <v>8.9635371842954504E-4</v>
+        <v>1.32567671857899E-3</v>
       </c>
       <c r="M47" s="2">
-        <v>1.0741074178410501E-6</v>
+        <v>1.5318368895278E-6</v>
       </c>
       <c r="N47">
-        <v>8.9292512144540401E-4</v>
+        <v>1.3245956550701E-3</v>
       </c>
       <c r="O47" s="2">
-        <v>1.5443417647520601E-6</v>
+        <v>2.0064771481250101E-6</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="9"/>
-        <v>0.99617495089979868</v>
+        <v>0.99918451950333054</v>
       </c>
       <c r="Q47">
         <f t="shared" si="11"/>
-        <v>2.09604744411438E-3</v>
+        <v>1.9036453265773162E-3</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="B48" s="4"/>
       <c r="D48">
-        <v>4.7002672379747703E-3</v>
+        <v>7.6621384469752396E-3</v>
       </c>
       <c r="E48" s="2">
-        <v>5.5830943137030297E-6</v>
+        <v>8.9439539283184293E-6</v>
       </c>
       <c r="F48">
-        <v>4.6888544824096002E-3</v>
+        <v>7.6581425799841299E-3</v>
       </c>
       <c r="G48" s="2">
-        <v>6.9665355992869402E-6</v>
-      </c>
-      <c r="H48" s="21">
+        <v>9.5373623923301102E-6</v>
+      </c>
+      <c r="H48" s="20">
         <f t="shared" si="8"/>
-        <v>0.99757189219520048</v>
+        <v>0.99947849193553961</v>
       </c>
       <c r="I48">
         <f t="shared" si="10"/>
-        <v>1.8975971265847125E-3</v>
+        <v>1.7060261538065647E-3</v>
       </c>
       <c r="J48" s="3"/>
       <c r="L48">
-        <v>1.32567671857899E-3</v>
+        <v>2.1556137545463202E-3</v>
       </c>
       <c r="M48" s="2">
-        <v>1.5318368895278E-6</v>
+        <v>2.8917617520134201E-6</v>
       </c>
       <c r="N48">
-        <v>1.3245956550701E-3</v>
+        <v>2.1557775197990998E-3</v>
       </c>
       <c r="O48" s="2">
-        <v>2.0064771481250101E-6</v>
+        <v>3.4267184077591398E-6</v>
       </c>
       <c r="P48" s="7">
         <f t="shared" si="9"/>
-        <v>0.99918451950333054</v>
+        <v>1.0000759715196816</v>
       </c>
       <c r="Q48">
         <f t="shared" si="11"/>
-        <v>1.9036453265773162E-3</v>
+        <v>2.08013448905876E-3</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="B49" s="4"/>
       <c r="D49">
-        <v>7.6621384469752396E-3</v>
+        <v>1.4528827469945001E-2</v>
       </c>
       <c r="E49" s="2">
-        <v>8.9439539283184293E-6</v>
+        <v>1.9512128215526801E-5</v>
       </c>
       <c r="F49">
-        <v>7.6581425799841299E-3</v>
+        <v>1.4510294900252E-2</v>
       </c>
       <c r="G49" s="2">
-        <v>9.5373623923301102E-6</v>
-      </c>
-      <c r="H49" s="21">
+        <v>1.7632674389988701E-5</v>
+      </c>
+      <c r="H49" s="20">
         <f t="shared" si="8"/>
-        <v>0.99947849193553961</v>
+        <v>0.99872442771232994</v>
       </c>
       <c r="I49">
         <f t="shared" si="10"/>
-        <v>1.7060261538065647E-3</v>
+        <v>1.808850802137127E-3</v>
       </c>
       <c r="J49" s="3"/>
       <c r="L49">
-        <v>2.1556137545463202E-3</v>
+        <v>4.0692513404583797E-3</v>
       </c>
       <c r="M49" s="2">
-        <v>2.8917617520134201E-6</v>
+        <v>5.5675919373717998E-6</v>
       </c>
       <c r="N49">
-        <v>2.1557775197990998E-3</v>
+        <v>4.0569357875227304E-3</v>
       </c>
       <c r="O49" s="2">
-        <v>3.4267184077591398E-6</v>
+        <v>5.2496418363288303E-6</v>
       </c>
       <c r="P49" s="7">
         <f t="shared" si="9"/>
-        <v>1.0000759715196816</v>
+        <v>0.99697350890735048</v>
       </c>
       <c r="Q49">
         <f t="shared" si="11"/>
-        <v>2.08013448905876E-3</v>
+        <v>1.8774931839575925E-3</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="B50" s="4"/>
       <c r="D50">
-        <v>1.4528827469945001E-2</v>
+        <v>2.0701772563261001E-2</v>
       </c>
       <c r="E50" s="2">
-        <v>1.9512128215526801E-5</v>
+        <v>1.94778367259042E-5</v>
       </c>
       <c r="F50">
-        <v>1.4510294900252E-2</v>
+        <v>2.0670832742657502E-2</v>
       </c>
       <c r="G50" s="2">
-        <v>1.7632674389988701E-5</v>
-      </c>
-      <c r="H50" s="21">
+        <v>2.4165486313225001E-5</v>
+      </c>
+      <c r="H50" s="20">
         <f t="shared" si="8"/>
-        <v>0.99872442771232994</v>
+        <v>0.99850545065602703</v>
       </c>
       <c r="I50">
         <f t="shared" si="10"/>
-        <v>1.808850802137127E-3</v>
+        <v>1.498409392449824E-3</v>
       </c>
       <c r="J50" s="3"/>
       <c r="L50">
-        <v>4.0692513404583797E-3</v>
+        <v>5.7649672577643396E-3</v>
       </c>
       <c r="M50" s="2">
-        <v>5.5675919373717998E-6</v>
+        <v>6.73190263055258E-6</v>
       </c>
       <c r="N50">
-        <v>4.0569357875227304E-3</v>
+        <v>5.7622824448929303E-3</v>
       </c>
       <c r="O50" s="2">
-        <v>5.2496418363288303E-6</v>
+        <v>7.5386609948647098E-6</v>
       </c>
       <c r="P50" s="7">
         <f t="shared" si="9"/>
-        <v>0.99697350890735048</v>
+        <v>0.99953428827062407</v>
       </c>
       <c r="Q50">
         <f t="shared" si="11"/>
-        <v>1.8774931839575925E-3</v>
+        <v>1.7528003368185298E-3</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>750</v>
+        <v>999.99</v>
       </c>
       <c r="B51" s="4"/>
       <c r="D51">
-        <v>2.0701772563261001E-2</v>
+        <v>2.6254111956257101E-2</v>
       </c>
       <c r="E51" s="2">
-        <v>1.94778367259042E-5</v>
+        <v>3.1518519557492703E-5</v>
       </c>
       <c r="F51">
-        <v>2.0670832742657502E-2</v>
+        <v>2.6241236871756501E-2</v>
       </c>
       <c r="G51" s="2">
-        <v>2.4165486313225001E-5</v>
-      </c>
-      <c r="H51" s="21">
+        <v>3.3019156397098597E-5</v>
+      </c>
+      <c r="H51" s="20">
         <f t="shared" si="8"/>
-        <v>0.99850545065602703</v>
+        <v>0.9995095974100342</v>
       </c>
       <c r="I51">
-        <f t="shared" si="10"/>
-        <v>1.498409392449824E-3</v>
+        <f>H51*((E51/D51)^2 +(G51/F51)^2)^0.5</f>
+        <v>1.7382683540267973E-3</v>
       </c>
       <c r="J51" s="3"/>
       <c r="L51">
-        <v>5.7649672577643396E-3</v>
+        <v>7.3065547855977898E-3</v>
       </c>
       <c r="M51" s="2">
-        <v>6.73190263055258E-6</v>
+        <v>7.6217629536129497E-6</v>
       </c>
       <c r="N51">
-        <v>5.7622824448929303E-3</v>
+        <v>7.2989569527415503E-3</v>
       </c>
       <c r="O51" s="2">
-        <v>7.5386609948647098E-6</v>
+        <v>8.3743748627356196E-6</v>
       </c>
       <c r="P51" s="7">
         <f t="shared" si="9"/>
-        <v>0.99953428827062407</v>
+        <v>0.99896013469012568</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="11"/>
-        <v>1.7528003368185298E-3</v>
+        <f>P51*((M51/L51)^2 +(O51/N51)^2)^0.5</f>
+        <v>1.5490415302505404E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>999.99</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="D52">
-        <v>2.6254111956257101E-2</v>
-      </c>
-      <c r="E52" s="2">
-        <v>3.1518519557492703E-5</v>
-      </c>
-      <c r="F52">
-        <v>2.6241236871756501E-2</v>
-      </c>
-      <c r="G52" s="2">
-        <v>3.3019156397098597E-5</v>
-      </c>
-      <c r="H52" s="21">
-        <f t="shared" si="8"/>
-        <v>0.9995095974100342</v>
-      </c>
-      <c r="I52">
-        <f>H52*((E52/D52)^2 +(G52/F52)^2)^0.5</f>
-        <v>1.7382683540267973E-3</v>
-      </c>
-      <c r="J52" s="3"/>
-      <c r="L52">
-        <v>7.3065547855977898E-3</v>
-      </c>
-      <c r="M52" s="2">
-        <v>7.6217629536129497E-6</v>
-      </c>
-      <c r="N52">
-        <v>7.2989569527415503E-3</v>
-      </c>
-      <c r="O52" s="2">
-        <v>8.3743748627356196E-6</v>
-      </c>
-      <c r="P52" s="7">
-        <f t="shared" si="9"/>
-        <v>0.99896013469012568</v>
-      </c>
-      <c r="Q52">
-        <f>P52*((M52/L52)^2 +(O52/N52)^2)^0.5</f>
-        <v>1.5490415302505404E-3</v>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C54" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C55" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="C55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C56" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
+      <c r="C56" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="13"/>
+      <c r="K56" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L56" s="16"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="16"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="5"/>
       <c r="C57" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57" s="6"/>
       <c r="K57" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="17"/>
-      <c r="M57" s="18"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="L57" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O57" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P57" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q57" s="18" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H58" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I58" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L58" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M58" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N58" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O58" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P58" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q58" s="19" t="s">
-        <v>12</v>
+      <c r="A58">
+        <v>0.1</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="D58">
+        <v>1.35349035541185</v>
+      </c>
+      <c r="E58" s="2">
+        <v>9.6553174997388497E-5</v>
+      </c>
+      <c r="F58">
+        <v>1.3534015288379</v>
+      </c>
+      <c r="G58" s="2">
+        <v>9.3759020527858203E-5</v>
+      </c>
+      <c r="H58" s="7">
+        <f t="shared" ref="H58:H70" si="12">F58/D58</f>
+        <v>0.99993437221506987</v>
+      </c>
+      <c r="I58">
+        <f>H58*((E58/D58)^2 +(G58/F58)^2)^0.5</f>
+        <v>9.9432552933769036E-5</v>
+      </c>
+      <c r="J58" s="3"/>
+      <c r="L58">
+        <v>1.3534796781066101</v>
+      </c>
+      <c r="M58" s="2">
+        <v>9.4365811729444995E-5</v>
+      </c>
+      <c r="N58">
+        <v>1.3533874250728799</v>
+      </c>
+      <c r="O58" s="2">
+        <v>9.25744561728887E-5</v>
+      </c>
+      <c r="P58" s="7">
+        <f t="shared" ref="P58:P70" si="13">N58/L58</f>
+        <v>0.99993184010427161</v>
+      </c>
+      <c r="Q58">
+        <f>P58*((M58/L58)^2 +(O58/N58)^2)^0.5</f>
+        <v>9.766545498253321E-5</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B59" s="4"/>
       <c r="D59">
-        <v>1.35349035541185</v>
-      </c>
-      <c r="E59" s="2">
-        <v>9.6553174997388497E-5</v>
+        <v>1.3525055888533599</v>
+      </c>
+      <c r="E59">
+        <v>1.3350945350493499E-4</v>
+      </c>
+      <c r="F59">
+        <v>1.3523631081874801</v>
+      </c>
+      <c r="G59">
+        <v>1.04497562087403E-4</v>
       </c>
       <c r="H59" s="7">
-        <f t="shared" ref="H59:H71" si="12">F59/D59</f>
-        <v>0</v>
-      </c>
-      <c r="I59" t="e">
-        <f>H59*((E59/D59)^2 +(G59/F59)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <f t="shared" si="12"/>
+        <v>0.99989465428678881</v>
+      </c>
+      <c r="I59">
+        <f t="shared" ref="I59:I69" si="14">H59*((E59/D59)^2 +(G59/F59)^2)^0.5</f>
+        <v>1.2534587622454844E-4</v>
       </c>
       <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
       <c r="L59">
-        <v>1.3534796781066101</v>
-      </c>
-      <c r="M59" s="2">
-        <v>9.4365811729444995E-5</v>
+        <v>1.3523816661130299</v>
+      </c>
+      <c r="M59">
+        <v>1.49314446515367E-4</v>
       </c>
       <c r="N59">
-        <v>1.3533874250728799</v>
-      </c>
-      <c r="O59" s="2">
-        <v>9.25744561728887E-5</v>
-      </c>
-      <c r="P59" s="7">
-        <f t="shared" ref="P59:P71" si="13">N59/L59</f>
-        <v>0.99993184010427161</v>
+        <v>1.3522755659704</v>
+      </c>
+      <c r="O59">
+        <v>1.0988210288705301E-4</v>
+      </c>
+      <c r="P59" s="8">
+        <f t="shared" si="13"/>
+        <v>0.99992154571058711</v>
       </c>
       <c r="Q59">
-        <f>P59*((M59/L59)^2 +(O59/N59)^2)^0.5</f>
-        <v>9.766545498253321E-5</v>
+        <f t="shared" ref="Q59:Q69" si="15">P59*((M59/L59)^2 +(O59/N59)^2)^0.5</f>
+        <v>1.3707596618126611E-4</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="B60" s="4"/>
       <c r="D60">
-        <v>1.3525055888533599</v>
+        <v>1.35196691014248</v>
       </c>
       <c r="E60">
-        <v>1.3350945350493499E-4</v>
+        <v>1.06286820978399E-4</v>
+      </c>
+      <c r="F60">
+        <v>1.3521181483175599</v>
+      </c>
+      <c r="G60">
+        <v>1.5169758245579099E-4</v>
       </c>
       <c r="H60" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I60" t="e">
-        <f t="shared" ref="I60:I70" si="14">H60*((E60/D60)^2 +(G60/F60)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <v>1.0001118652934071</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="14"/>
+        <v>1.3701062533005715E-4</v>
       </c>
       <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
       <c r="L60">
-        <v>1.3523816661130299</v>
+        <v>1.3518170844189801</v>
       </c>
       <c r="M60">
-        <v>1.49314446515367E-4</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" s="8">
+        <v>1.14380157051306E-4</v>
+      </c>
+      <c r="N60">
+        <v>1.3519913617870101</v>
+      </c>
+      <c r="O60">
+        <v>1.48348598450422E-4</v>
+      </c>
+      <c r="P60" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q60" t="e">
-        <f t="shared" ref="Q60:Q70" si="15">P60*((M60/L60)^2 +(O60/N60)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <v>1.000128920820752</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="15"/>
+        <v>1.385783590344851E-4</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B61" s="4"/>
       <c r="D61">
-        <v>1.35196691014248</v>
+        <v>1.3496449964439701</v>
       </c>
       <c r="E61">
-        <v>1.06286820978399E-4</v>
+        <v>3.34573859265803E-4</v>
+      </c>
+      <c r="F61">
+        <v>1.3505251730884</v>
+      </c>
+      <c r="G61">
+        <v>3.1320147404522098E-4</v>
       </c>
       <c r="H61" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I61" t="e">
+        <v>1.0006521541936946</v>
+      </c>
+      <c r="I61">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>3.3968553714387918E-4</v>
       </c>
       <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
       <c r="L61">
-        <v>1.3518170844189801</v>
+        <v>1.3484991014567</v>
       </c>
       <c r="M61">
-        <v>1.14380157051306E-4</v>
-      </c>
-      <c r="P61" s="7">
+        <v>3.7805904699346899E-4</v>
+      </c>
+      <c r="N61">
+        <v>1.3494716016903701</v>
+      </c>
+      <c r="O61">
+        <v>2.8869581860669599E-4</v>
+      </c>
+      <c r="P61" s="8">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q61" t="e">
+        <v>1.0007211723260472</v>
+      </c>
+      <c r="Q61">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>3.5291035880064285E-4</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B62" s="4"/>
       <c r="D62">
-        <v>1.3496449964439701</v>
+        <v>1.34878568413012</v>
       </c>
       <c r="E62">
-        <v>3.34573859265803E-4</v>
+        <v>1.09258372127255E-3</v>
+      </c>
+      <c r="F62">
+        <v>1.3499391844892901</v>
+      </c>
+      <c r="G62">
+        <v>1.3707183810184799E-3</v>
       </c>
       <c r="H62" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I62" t="e">
+        <v>1.0008552139696782</v>
+      </c>
+      <c r="I62">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>1.300034709477677E-3</v>
       </c>
       <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
       <c r="L62">
-        <v>1.3484991014567</v>
+        <v>1.34496639056255</v>
       </c>
       <c r="M62">
-        <v>3.7805904699346899E-4</v>
-      </c>
-      <c r="P62" s="8">
+        <v>1.6184768350052301E-3</v>
+      </c>
+      <c r="N62">
+        <v>1.3463148595955401</v>
+      </c>
+      <c r="O62">
+        <v>1.2267224814702E-3</v>
+      </c>
+      <c r="P62" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q62" t="e">
+        <v>1.0010026042601898</v>
+      </c>
+      <c r="Q62">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.5109184058008226E-3</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B63" s="4"/>
       <c r="D63">
-        <v>1.34878568413012</v>
+        <v>1.3474610818274699</v>
       </c>
       <c r="E63">
-        <v>1.09258372127255E-3</v>
+        <v>1.17516294196242E-3</v>
+      </c>
+      <c r="F63">
+        <v>1.3455734465921001</v>
+      </c>
+      <c r="G63">
+        <v>1.2217446853760999E-3</v>
       </c>
       <c r="H63" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I63" t="e">
+        <v>0.9985991170648062</v>
+      </c>
+      <c r="I63">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>1.2572154111851082E-3</v>
       </c>
       <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
       <c r="L63">
-        <v>1.34496639056255</v>
+        <v>1.34058997335879</v>
       </c>
       <c r="M63">
-        <v>1.6184768350052301E-3</v>
-      </c>
-      <c r="P63" s="7">
+        <v>1.0490060790073401E-3</v>
+      </c>
+      <c r="N63">
+        <v>1.3404343940163499</v>
+      </c>
+      <c r="O63">
+        <v>1.4420881112400499E-3</v>
+      </c>
+      <c r="P63" s="8">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q63" t="e">
+        <v>0.99988394710871187</v>
+      </c>
+      <c r="Q63">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.3301552387791574E-3</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B64" s="4"/>
       <c r="D64">
-        <v>1.3474610818274699</v>
+        <v>1.3427752965748101</v>
       </c>
       <c r="E64">
-        <v>1.17516294196242E-3</v>
+        <v>1.07490457255542E-3</v>
+      </c>
+      <c r="F64">
+        <v>1.34298839152317</v>
+      </c>
+      <c r="G64">
+        <v>1.06421993303281E-3</v>
       </c>
       <c r="H64" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I64" t="e">
+        <v>1.000158697400007</v>
+      </c>
+      <c r="I64">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>1.126569384497018E-3</v>
       </c>
       <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
       <c r="L64">
-        <v>1.34058997335879</v>
+        <v>1.3360765153922001</v>
       </c>
       <c r="M64">
-        <v>1.0490060790073401E-3</v>
-      </c>
-      <c r="P64" s="8">
+        <v>1.1632843834853399E-3</v>
+      </c>
+      <c r="N64">
+        <v>1.33446918164207</v>
+      </c>
+      <c r="O64">
+        <v>1.3857869032541199E-3</v>
+      </c>
+      <c r="P64" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q64" t="e">
+        <v>0.99879697477531193</v>
+      </c>
+      <c r="Q64">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.353530062079468E-3</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B65" s="4"/>
       <c r="D65">
-        <v>1.3427752965748101</v>
+        <v>1.34074242473516</v>
       </c>
       <c r="E65">
-        <v>1.07490457255542E-3</v>
+        <v>1.39655871426836E-3</v>
+      </c>
+      <c r="F65">
+        <v>1.3398671852870001</v>
+      </c>
+      <c r="G65">
+        <v>1.287880398712E-3</v>
       </c>
       <c r="H65" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I65" t="e">
+        <v>0.99934719791660742</v>
+      </c>
+      <c r="I65">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>1.416431589537991E-3</v>
       </c>
       <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
       <c r="L65">
-        <v>1.3360765153922001</v>
+        <v>1.32701226510564</v>
       </c>
       <c r="M65">
-        <v>1.1632843834853399E-3</v>
-      </c>
-      <c r="P65" s="7">
+        <v>1.12425566465752E-3</v>
+      </c>
+      <c r="N65">
+        <v>1.3286113876260699</v>
+      </c>
+      <c r="O65">
+        <v>1.3450656516196099E-3</v>
+      </c>
+      <c r="P65" s="8">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q65" t="e">
+        <v>1.0012050548156031</v>
+      </c>
+      <c r="Q65">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.3216984553462278E-3</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="B66" s="4"/>
       <c r="D66">
-        <v>1.34074242473516</v>
+        <v>1.33329826157554</v>
       </c>
       <c r="E66">
-        <v>1.39655871426836E-3</v>
+        <v>1.0127020502582399E-3</v>
       </c>
       <c r="H66" s="7">
         <f t="shared" si="12"/>
@@ -9686,32 +9804,37 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
       <c r="L66">
-        <v>1.32701226510564</v>
+        <v>1.31712591718725</v>
       </c>
       <c r="M66">
-        <v>1.12425566465752E-3</v>
-      </c>
-      <c r="P66" s="8">
+        <v>1.07670919895594E-3</v>
+      </c>
+      <c r="N66">
+        <v>1.31511831282964</v>
+      </c>
+      <c r="O66">
+        <v>1.0460965227932701E-3</v>
+      </c>
+      <c r="P66" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q66" t="e">
+        <v>0.99847576884532241</v>
+      </c>
+      <c r="Q66">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.138865863749726E-3</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="B67" s="4"/>
       <c r="D67">
-        <v>1.33329826157554</v>
+        <v>1.32151573265695</v>
       </c>
       <c r="E67">
-        <v>1.0127020502582399E-3</v>
+        <v>1.3006693362351499E-3</v>
       </c>
       <c r="H67" s="7">
         <f t="shared" si="12"/>
@@ -9722,31 +9845,38 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
       <c r="L67">
-        <v>1.31712591718725</v>
+        <v>1.2918988571682599</v>
       </c>
       <c r="M67">
-        <v>1.07670919895594E-3</v>
-      </c>
-      <c r="P67" s="7">
+        <v>1.1007541264065699E-3</v>
+      </c>
+      <c r="N67">
+        <v>1.29376426805572</v>
+      </c>
+      <c r="O67">
+        <v>1.08946870381198E-3</v>
+      </c>
+      <c r="P67" s="8">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q67" t="e">
+        <v>1.0014439295128328</v>
+      </c>
+      <c r="Q67">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.1996852761766263E-3</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="B68" s="4"/>
       <c r="D68">
-        <v>1.32151573265695</v>
+        <v>1.2931453740650001</v>
       </c>
       <c r="E68">
-        <v>1.3006693362351499E-3</v>
+        <v>9.8555966722236005E-4</v>
       </c>
       <c r="H68" s="7">
         <f t="shared" si="12"/>
@@ -9757,32 +9887,37 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
       <c r="L68">
-        <v>1.2918988571682599</v>
+        <v>1.23828567912233</v>
       </c>
       <c r="M68">
-        <v>1.1007541264065699E-3</v>
-      </c>
-      <c r="P68" s="8">
+        <v>1.26094639154959E-3</v>
+      </c>
+      <c r="N68">
+        <v>1.2373191126010099</v>
+      </c>
+      <c r="O68">
+        <v>1.7104225594344201E-3</v>
+      </c>
+      <c r="P68" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q68" t="e">
+        <v>0.99921943172111527</v>
+      </c>
+      <c r="Q68">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.7155928133229267E-3</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="B69" s="4"/>
       <c r="D69">
-        <v>1.2931453740650001</v>
+        <v>1.2595818024588099</v>
       </c>
       <c r="E69">
-        <v>9.8555966722236005E-4</v>
+        <v>1.23221884565407E-3</v>
       </c>
       <c r="H69" s="7">
         <f t="shared" si="12"/>
@@ -9792,446 +9927,549 @@
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J69" s="3"/>
+      <c r="J69" s="4"/>
       <c r="L69">
-        <v>1.23828567912233</v>
+        <v>1.1839603302327899</v>
       </c>
       <c r="M69">
-        <v>1.26094639154959E-3</v>
+        <v>9.7670331118084107E-4</v>
+      </c>
+      <c r="N69">
+        <v>1.1856998650789701</v>
+      </c>
+      <c r="O69">
+        <v>1.12439487305431E-3</v>
       </c>
       <c r="P69" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q69" t="e">
+        <v>1.0014692509552563</v>
+      </c>
+      <c r="Q69">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.2587483955646352E-3</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>750</v>
+        <v>999.99</v>
       </c>
       <c r="B70" s="4"/>
-      <c r="H70" s="7" t="e">
+      <c r="D70">
+        <v>1.22576284834815</v>
+      </c>
+      <c r="E70">
+        <v>1.2327349655244699E-3</v>
+      </c>
+      <c r="H70" s="7">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I70" t="e">
-        <f t="shared" si="14"/>
+        <f>H70*((E70/D70)^2 +(G70/F70)^2)^0.5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J70" s="4"/>
       <c r="L70">
-        <v>1.1839603302327899</v>
+        <v>1.13553758367077</v>
       </c>
       <c r="M70">
-        <v>9.7670331118084107E-4</v>
-      </c>
-      <c r="P70" s="7">
+        <v>1.1206624657434201E-3</v>
+      </c>
+      <c r="N70">
+        <v>1.13628629783987</v>
+      </c>
+      <c r="O70">
+        <v>1.2732667465119099E-3</v>
+      </c>
+      <c r="P70" s="8">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q70" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>1.0006593477660861</v>
+      </c>
+      <c r="Q70">
+        <f>P70*((M70/L70)^2 +(O70/N70)^2)^0.5</f>
+        <v>1.4941713528427928E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>999.99</v>
-      </c>
-      <c r="B71" s="4"/>
-      <c r="H71" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I71" t="e">
-        <f>H71*((E71/D71)^2 +(G71/F71)^2)^0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J71" s="4"/>
-      <c r="L71">
-        <v>1.13553758367077</v>
-      </c>
-      <c r="M71">
-        <v>1.1206624657434201E-3</v>
-      </c>
-      <c r="P71" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q71" t="e">
-        <f>P71*((M71/L71)^2 +(O71/N71)^2)^0.5</f>
-        <v>#DIV/0!</v>
-      </c>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C72" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="10"/>
+      <c r="I72" s="10"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C73" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
+      <c r="C73" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="13"/>
+      <c r="K73" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L73" s="16"/>
+      <c r="M73" s="17"/>
+      <c r="N73" s="17"/>
+      <c r="O73" s="16"/>
+      <c r="P73" s="16"/>
+      <c r="Q73" s="16"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="5"/>
       <c r="C74" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J74" s="6"/>
       <c r="K74" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L74" s="17"/>
-      <c r="M74" s="18"/>
-      <c r="N74" s="18"/>
-      <c r="O74" s="17"/>
-      <c r="P74" s="17"/>
-      <c r="Q74" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="L74" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M74" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O74" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P74" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q74" s="18" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H75" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I75" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J75" s="6"/>
-      <c r="K75" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L75" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M75" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N75" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O75" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P75" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q75" s="19" t="s">
-        <v>12</v>
+      <c r="A75">
+        <v>0.1</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2">
+        <v>2.02909902032051E-5</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2.24743175291538E-9</v>
+      </c>
+      <c r="F75" s="2">
+        <v>2.0007152807541001E-5</v>
+      </c>
+      <c r="G75" s="2">
+        <v>3.4711645219164801E-8</v>
+      </c>
+      <c r="H75" s="7">
+        <f t="shared" ref="H75:H87" si="16">F75/D75</f>
+        <v>0.98601165380192901</v>
+      </c>
+      <c r="I75">
+        <f>H75*((E75/D75)^2 +(G75/F75)^2)^0.5</f>
+        <v>1.7141749885399009E-3</v>
+      </c>
+      <c r="J75" s="3"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2">
+        <v>2.4790666762969901E-5</v>
+      </c>
+      <c r="M75" s="2">
+        <v>2.62930916912575E-9</v>
+      </c>
+      <c r="N75" s="2">
+        <v>2.4528682334896999E-5</v>
+      </c>
+      <c r="O75" s="2">
+        <v>3.5040531796592898E-8</v>
+      </c>
+      <c r="P75" s="7">
+        <f t="shared" ref="P75:P87" si="17">N75/L75</f>
+        <v>0.98943213465866797</v>
+      </c>
+      <c r="Q75">
+        <f>P75*((M75/L75)^2 +(O75/N75)^2)^0.5</f>
+        <v>1.4173467854162441E-3</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="2">
-        <v>2.02909902032051E-5</v>
+      <c r="D76">
+        <v>1.0137245509615099E-4</v>
       </c>
       <c r="E76" s="2">
-        <v>2.24743175291538E-9</v>
-      </c>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
+        <v>1.77005795225872E-8</v>
+      </c>
+      <c r="F76" s="2">
+        <v>9.9956573245012605E-5</v>
+      </c>
+      <c r="G76" s="2">
+        <v>7.2050260970812403E-8</v>
+      </c>
       <c r="H76" s="7">
-        <f t="shared" ref="H76:H88" si="16">F76/D76</f>
-        <v>0</v>
-      </c>
-      <c r="I76" t="e">
-        <f>H76*((E76/D76)^2 +(G76/F76)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <f t="shared" si="16"/>
+        <v>0.98603287402090212</v>
+      </c>
+      <c r="I76">
+        <f t="shared" ref="I76:I86" si="18">H76*((E76/D76)^2 +(G76/F76)^2)^0.5</f>
+        <v>7.3130383685799619E-4</v>
       </c>
       <c r="J76" s="3"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2">
-        <v>2.4790666762969901E-5</v>
+      <c r="L76">
+        <v>1.2382934591149999E-4</v>
       </c>
       <c r="M76" s="2">
-        <v>2.62930916912575E-9</v>
-      </c>
-      <c r="N76" s="2">
-        <v>2.4528682334896999E-5</v>
+        <v>1.9712339612085199E-8</v>
+      </c>
+      <c r="N76">
+        <v>1.2253637247031199E-4</v>
       </c>
       <c r="O76" s="2">
-        <v>3.5040531796592898E-8</v>
+        <v>7.3716805324193805E-8</v>
       </c>
       <c r="P76" s="7">
-        <f t="shared" ref="P76:P88" si="17">N76/L76</f>
-        <v>0.98943213465866797</v>
+        <f t="shared" si="17"/>
+        <v>0.98955842468785971</v>
       </c>
       <c r="Q76">
-        <f>P76*((M76/L76)^2 +(O76/N76)^2)^0.5</f>
-        <v>1.4173467854162441E-3</v>
+        <f t="shared" ref="Q76:Q86" si="19">P76*((M76/L76)^2 +(O76/N76)^2)^0.5</f>
+        <v>6.1579904211881168E-4</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="2"/>
       <c r="D77">
-        <v>1.0137245509615099E-4</v>
+        <v>2.02642741315636E-4</v>
       </c>
       <c r="E77" s="2">
-        <v>1.77005795225872E-8</v>
-      </c>
-      <c r="G77" s="2"/>
+        <v>2.4405638890132701E-8</v>
+      </c>
+      <c r="F77">
+        <v>1.9971899576778099E-4</v>
+      </c>
+      <c r="G77" s="2">
+        <v>1.02609766232894E-7</v>
+      </c>
       <c r="H77" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I77" t="e">
-        <f t="shared" ref="I77:I87" si="18">H77*((E77/D77)^2 +(G77/F77)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <v>0.9855719206675112</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="18"/>
+        <v>5.2008448089518248E-4</v>
       </c>
       <c r="J77" s="3"/>
       <c r="L77">
-        <v>1.2382934591149999E-4</v>
+        <v>2.4754589215855298E-4</v>
       </c>
       <c r="M77" s="2">
-        <v>1.9712339612085199E-8</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>3.1019310600902002E-8</v>
+      </c>
+      <c r="N77">
+        <v>2.4529987110641501E-4</v>
+      </c>
+      <c r="O77" s="2">
+        <v>1.0882622972029E-7</v>
+      </c>
       <c r="P77" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" t="e">
-        <f t="shared" ref="Q77:Q87" si="19">P77*((M77/L77)^2 +(O77/N77)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <v>0.99092684983558765</v>
+      </c>
+      <c r="Q77">
+        <f t="shared" si="19"/>
+        <v>4.5681987639143909E-4</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="2"/>
       <c r="D78">
-        <v>2.02642741315636E-4</v>
+        <v>2.0215278732349001E-3</v>
       </c>
       <c r="E78" s="2">
-        <v>2.4405638890132701E-8</v>
-      </c>
-      <c r="G78" s="2"/>
+        <v>8.3041477691979302E-7</v>
+      </c>
+      <c r="F78">
+        <v>1.9939142335394298E-3</v>
+      </c>
+      <c r="G78" s="2">
+        <v>9.6453719046818291E-7</v>
+      </c>
       <c r="H78" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I78" t="e">
+        <v>0.98634021323125154</v>
+      </c>
+      <c r="I78">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
+        <v>6.2595689243500469E-4</v>
       </c>
       <c r="J78" s="3"/>
       <c r="L78">
-        <v>2.4754589215855298E-4</v>
+        <v>2.4688428331907201E-3</v>
       </c>
       <c r="M78" s="2">
-        <v>3.1019310600902002E-8</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>9.25195380739334E-7</v>
+      </c>
+      <c r="N78">
+        <v>2.4489469789132001E-3</v>
+      </c>
+      <c r="O78" s="2">
+        <v>1.5097897712746E-6</v>
+      </c>
       <c r="P78" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q78" t="e">
+        <v>0.99194122282307995</v>
+      </c>
+      <c r="Q78">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>7.1565365199815936E-4</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="2"/>
       <c r="D79">
-        <v>2.0215278732349001E-3</v>
+        <v>5.0558014839730799E-3</v>
       </c>
       <c r="E79" s="2">
-        <v>8.3041477691979302E-7</v>
-      </c>
-      <c r="G79" s="2"/>
+        <v>6.1896243078158903E-6</v>
+      </c>
+      <c r="F79">
+        <v>4.9861996908871897E-3</v>
+      </c>
+      <c r="G79" s="2">
+        <v>9.0283699818245308E-6</v>
+      </c>
       <c r="H79" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I79" t="e">
+        <v>0.9862332820411307</v>
+      </c>
+      <c r="I79">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
+        <v>2.1556244820606987E-3</v>
       </c>
       <c r="J79" s="3"/>
       <c r="L79">
-        <v>2.4688428331907201E-3</v>
+        <v>6.1582182881184796E-3</v>
       </c>
       <c r="M79" s="2">
-        <v>9.25195380739334E-7</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>9.8842994715634199E-6</v>
+      </c>
+      <c r="N79">
+        <v>6.1077938251299499E-3</v>
+      </c>
+      <c r="O79" s="2">
+        <v>9.6205617748834506E-6</v>
+      </c>
       <c r="P79" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q79" t="e">
+        <v>0.99181184221971841</v>
+      </c>
+      <c r="Q79">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>2.2304176516532194E-3</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="2"/>
       <c r="D80">
-        <v>5.0558014839730799E-3</v>
+        <v>1.0087782457006899E-2</v>
       </c>
       <c r="E80" s="2">
-        <v>6.1896243078158903E-6</v>
-      </c>
-      <c r="G80" s="2"/>
+        <v>1.16986845524187E-5</v>
+      </c>
+      <c r="F80">
+        <v>9.9513528124167798E-3</v>
+      </c>
+      <c r="G80" s="2">
+        <v>1.49150381505163E-5</v>
+      </c>
       <c r="H80" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I80" t="e">
+        <v>0.98647575468924231</v>
+      </c>
+      <c r="I80">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
+        <v>1.869433707231689E-3</v>
       </c>
       <c r="J80" s="3"/>
       <c r="L80">
-        <v>6.1582182881184796E-3</v>
+        <v>1.22887559133099E-2</v>
       </c>
       <c r="M80" s="2">
-        <v>9.8842994715634199E-6</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>1.29589704180185E-5</v>
+      </c>
+      <c r="N80">
+        <v>1.2171273109856801E-2</v>
+      </c>
+      <c r="O80" s="2">
+        <v>2.1324546647608199E-5</v>
+      </c>
       <c r="P80" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q80" t="e">
+        <v>0.99043981308751894</v>
+      </c>
+      <c r="Q80">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>2.0253690793008185E-3</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="2"/>
       <c r="D81">
-        <v>1.0087782457006899E-2</v>
+        <v>1.50934860556895E-2</v>
       </c>
       <c r="E81" s="2">
-        <v>1.16986845524187E-5</v>
+        <v>1.70782053665879E-5</v>
+      </c>
+      <c r="F81">
+        <v>1.49268533044647E-2</v>
+      </c>
+      <c r="G81" s="2">
+        <v>1.3857646507231E-5</v>
       </c>
       <c r="H81" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I81" t="e">
+        <v>0.98895995592999619</v>
+      </c>
+      <c r="I81">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
+        <v>1.4474510813786332E-3</v>
       </c>
       <c r="J81" s="3"/>
       <c r="L81">
-        <v>1.22887559133099E-2</v>
+        <v>1.8371849012466902E-2</v>
       </c>
       <c r="M81" s="2">
-        <v>1.29589704180185E-5</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>1.8508626230406801E-5</v>
+      </c>
+      <c r="N81">
+        <v>1.8207572674205901E-2</v>
+      </c>
+      <c r="O81" s="2">
+        <v>2.44581035990221E-5</v>
+      </c>
       <c r="P81" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q81" t="e">
+        <v>0.99105825776439138</v>
+      </c>
+      <c r="Q81">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1.664087211902877E-3</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="2"/>
       <c r="D82">
-        <v>1.50934860556895E-2</v>
+        <v>2.0092596382124801E-2</v>
       </c>
       <c r="E82" s="2">
-        <v>1.70782053665879E-5</v>
+        <v>2.9515645920923001E-5</v>
+      </c>
+      <c r="F82">
+        <v>1.9887871213505302E-2</v>
+      </c>
+      <c r="G82" s="2">
+        <v>2.55615407262553E-5</v>
       </c>
       <c r="H82" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I82" t="e">
+        <v>0.98981091518856013</v>
+      </c>
+      <c r="I82">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
+        <v>1.9319977820100973E-3</v>
       </c>
       <c r="J82" s="3"/>
       <c r="L82">
-        <v>1.8371849012466902E-2</v>
+        <v>2.43271897166558E-2</v>
       </c>
       <c r="M82" s="2">
-        <v>1.8508626230406801E-5</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>3.1299383235957799E-5</v>
+      </c>
+      <c r="N82">
+        <v>2.4172743202431499E-2</v>
+      </c>
+      <c r="O82" s="2">
+        <v>3.2228791995716999E-5</v>
+      </c>
       <c r="P82" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q82" t="e">
+        <v>0.99365128006879655</v>
+      </c>
+      <c r="Q82">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1.8410592624697934E-3</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="2"/>
       <c r="D83">
-        <v>2.0092596382124801E-2</v>
+        <v>3.00179157888214E-2</v>
       </c>
       <c r="E83" s="2">
-        <v>2.9515645920923001E-5</v>
+        <v>3.4087650495836803E-5</v>
       </c>
       <c r="H83" s="7">
         <f t="shared" si="16"/>
@@ -10243,32 +10481,37 @@
       </c>
       <c r="J83" s="3"/>
       <c r="L83">
-        <v>2.43271897166558E-2</v>
+        <v>3.6245762780485802E-2</v>
       </c>
       <c r="M83" s="2">
-        <v>3.1299383235957799E-5</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>3.92808357194154E-5</v>
+      </c>
+      <c r="N83">
+        <v>3.5927691606669497E-2</v>
+      </c>
+      <c r="O83" s="2">
+        <v>3.5331045630474298E-5</v>
+      </c>
       <c r="P83" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q83" t="e">
+        <v>0.9912245970448289</v>
+      </c>
+      <c r="Q83">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1.4505601412026115E-3</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="2"/>
       <c r="D84">
-        <v>3.00179157888214E-2</v>
+        <v>4.9734447162320401E-2</v>
       </c>
       <c r="E84" s="2">
-        <v>3.4087650495836803E-5</v>
+        <v>6.4645159030235E-5</v>
       </c>
       <c r="H84" s="7">
         <f t="shared" si="16"/>
@@ -10280,31 +10523,37 @@
       </c>
       <c r="J84" s="3"/>
       <c r="L84">
-        <v>3.6245762780485802E-2</v>
+        <v>5.9402715051338199E-2</v>
       </c>
       <c r="M84" s="2">
-        <v>3.92808357194154E-5</v>
+        <v>6.9304807814503901E-5</v>
+      </c>
+      <c r="N84">
+        <v>5.9055974302948303E-2</v>
+      </c>
+      <c r="O84" s="2">
+        <v>6.6492878086677994E-5</v>
       </c>
       <c r="P84" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q84" t="e">
+        <v>0.99416288046614987</v>
+      </c>
+      <c r="Q84">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1.6119220123475947E-3</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="2"/>
       <c r="D85">
-        <v>4.9734447162320401E-2</v>
-      </c>
-      <c r="E85" s="2">
-        <v>6.4645159030235E-5</v>
+        <v>9.8175431650812398E-2</v>
+      </c>
+      <c r="E85">
+        <v>1.1926647552751499E-4</v>
       </c>
       <c r="H85" s="7">
         <f t="shared" si="16"/>
@@ -10316,31 +10565,36 @@
       </c>
       <c r="J85" s="3"/>
       <c r="L85">
-        <v>5.9402715051338199E-2</v>
-      </c>
-      <c r="M85" s="2">
-        <v>6.9304807814503901E-5</v>
+        <v>0.114483792434821</v>
+      </c>
+      <c r="M85">
+        <v>1.39194216858858E-4</v>
+      </c>
+      <c r="N85">
+        <v>0.11368551367483699</v>
+      </c>
+      <c r="O85">
+        <v>1.8467223694082401E-4</v>
       </c>
       <c r="P85" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q85" t="e">
+        <v>0.99302714608761333</v>
+      </c>
+      <c r="Q85">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>2.0148885303333877E-3</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="B86" s="4"/>
-      <c r="C86" s="2"/>
       <c r="D86">
-        <v>9.8175431650812398E-2</v>
+        <v>0.144214003795889</v>
       </c>
       <c r="E86">
-        <v>1.1926647552751499E-4</v>
+        <v>1.74858178010965E-4</v>
       </c>
       <c r="H86" s="7">
         <f t="shared" si="16"/>
@@ -10350,454 +10604,550 @@
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J86" s="3"/>
+      <c r="J86" s="4"/>
       <c r="L86">
-        <v>0.114483792434821</v>
+        <v>0.16472051968134599</v>
       </c>
       <c r="M86">
-        <v>1.39194216858858E-4</v>
+        <v>1.6222360707556901E-4</v>
+      </c>
+      <c r="N86">
+        <v>0.163904437944666</v>
+      </c>
+      <c r="O86">
+        <v>1.80982992571986E-4</v>
       </c>
       <c r="P86" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q86" t="e">
+        <v>0.99504565831713798</v>
+      </c>
+      <c r="Q86">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1.4722528853940004E-3</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>750</v>
+        <v>999.99</v>
       </c>
       <c r="B87" s="4"/>
-      <c r="H87" s="7" t="e">
+      <c r="D87">
+        <v>0.187638403751725</v>
+      </c>
+      <c r="E87">
+        <v>2.42561007731545E-4</v>
+      </c>
+      <c r="H87" s="7">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I87" t="e">
-        <f t="shared" si="18"/>
+        <f>H87*((E87/D87)^2 +(G87/F87)^2)^0.5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J87" s="4"/>
       <c r="L87">
-        <v>0.16472051968134599</v>
+        <v>0.21100076304460699</v>
       </c>
       <c r="M87">
-        <v>1.6222360707556901E-4</v>
+        <v>2.47499288497926E-4</v>
+      </c>
+      <c r="N87">
+        <v>0.209877834651196</v>
+      </c>
+      <c r="O87">
+        <v>2.8421294903727698E-4</v>
       </c>
       <c r="P87" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q87" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.99467808373198352</v>
+      </c>
+      <c r="Q87">
+        <f>P87*((M87/L87)^2 +(O87/N87)^2)^0.5</f>
+        <v>1.7820258962268976E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>999.99</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="H88" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I88" t="e">
-        <f>H88*((E88/D88)^2 +(G88/F88)^2)^0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J88" s="4"/>
-      <c r="L88">
-        <v>0.21100076304460699</v>
-      </c>
-      <c r="M88">
-        <v>2.47499288497926E-4</v>
-      </c>
-      <c r="P88" s="7">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q88" t="e">
-        <f>P88*((M88/L88)^2 +(O88/N88)^2)^0.5</f>
-        <v>#DIV/0!</v>
-      </c>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C89" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="10"/>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C90" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
+      <c r="C90" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="13"/>
+      <c r="K90" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L90" s="16"/>
+      <c r="M90" s="17"/>
+      <c r="N90" s="17"/>
+      <c r="O90" s="16"/>
+      <c r="P90" s="16"/>
+      <c r="Q90" s="16"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="5"/>
       <c r="C91" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
-      <c r="I91" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I91" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91" s="6"/>
       <c r="K91" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="17"/>
-      <c r="M91" s="18"/>
-      <c r="N91" s="18"/>
-      <c r="O91" s="17"/>
-      <c r="P91" s="17"/>
-      <c r="Q91" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="L91" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N91" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O91" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P91" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q91" s="18" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E92" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H92" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I92" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J92" s="6"/>
-      <c r="K92" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L92" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M92" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N92" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O92" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P92" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q92" s="19" t="s">
-        <v>12</v>
+      <c r="A92">
+        <v>0.1</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2">
+        <v>6.1377059341900601E-6</v>
+      </c>
+      <c r="E92" s="2">
+        <v>6.5011853480463401E-10</v>
+      </c>
+      <c r="F92" s="2">
+        <v>6.0745991893579203E-6</v>
+      </c>
+      <c r="G92" s="2">
+        <v>8.9451721369474302E-9</v>
+      </c>
+      <c r="H92" s="7">
+        <f t="shared" ref="H92:H104" si="20">F92/D92</f>
+        <v>0.98971818697265956</v>
+      </c>
+      <c r="I92">
+        <f>H92*((E92/D92)^2 +(G92/F92)^2)^0.5</f>
+        <v>1.4611784548978087E-3</v>
+      </c>
+      <c r="J92" s="3"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2">
+        <v>1.5930510467711099E-6</v>
+      </c>
+      <c r="M92" s="2">
+        <v>1.65600483830151E-10</v>
+      </c>
+      <c r="N92" s="2">
+        <v>1.5741702493169501E-6</v>
+      </c>
+      <c r="O92" s="2">
+        <v>2.5700779401292402E-9</v>
+      </c>
+      <c r="P92" s="7">
+        <f t="shared" ref="P92:P104" si="21">N92/L92</f>
+        <v>0.98814802733884233</v>
+      </c>
+      <c r="Q92">
+        <f>P92*((M92/L92)^2 +(O92/N92)^2)^0.5</f>
+        <v>1.6165722467163411E-3</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2">
-        <v>6.1377059341900601E-6</v>
+        <v>3.0735354469935802E-5</v>
       </c>
       <c r="E93" s="2">
-        <v>6.5011853480463401E-10</v>
-      </c>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
+        <v>3.2888347224815601E-9</v>
+      </c>
+      <c r="F93" s="2">
+        <v>3.04885957059744E-5</v>
+      </c>
+      <c r="G93" s="2">
+        <v>2.0677466656789801E-8</v>
+      </c>
       <c r="H93" s="7">
-        <f t="shared" ref="H93:H105" si="20">F93/D93</f>
-        <v>0</v>
-      </c>
-      <c r="I93" t="e">
-        <f>H93*((E93/D93)^2 +(G93/F93)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <f t="shared" si="20"/>
+        <v>0.99197150095656872</v>
+      </c>
+      <c r="I93">
+        <f t="shared" ref="I93:I103" si="22">H93*((E93/D93)^2 +(G93/F93)^2)^0.5</f>
+        <v>6.8108057665906764E-4</v>
       </c>
       <c r="J93" s="3"/>
-      <c r="K93" s="2"/>
       <c r="L93" s="2">
-        <v>1.5930510467711099E-6</v>
+        <v>7.9783288855483107E-6</v>
       </c>
       <c r="M93" s="2">
-        <v>1.65600483830151E-10</v>
+        <v>8.0769164104274605E-10</v>
       </c>
       <c r="N93" s="2">
-        <v>1.5741702493169501E-6</v>
+        <v>7.9038252433909995E-6</v>
       </c>
       <c r="O93" s="2">
-        <v>2.5700779401292402E-9</v>
+        <v>5.7304767339735299E-9</v>
       </c>
       <c r="P93" s="7">
-        <f t="shared" ref="P93:P105" si="21">N93/L93</f>
-        <v>0.98814802733884233</v>
+        <f t="shared" si="21"/>
+        <v>0.99066174844054566</v>
       </c>
       <c r="Q93">
-        <f>P93*((M93/L93)^2 +(O93/N93)^2)^0.5</f>
-        <v>1.6165722467163411E-3</v>
+        <f t="shared" ref="Q93:Q103" si="23">P93*((M93/L93)^2 +(O93/N93)^2)^0.5</f>
+        <v>7.2522325975314477E-4</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2">
-        <v>3.0735354469935802E-5</v>
+        <v>6.1492338452019598E-5</v>
       </c>
       <c r="E94" s="2">
-        <v>3.2888347224815601E-9</v>
-      </c>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
+        <v>5.9150812321793704E-9</v>
+      </c>
+      <c r="F94" s="2">
+        <v>6.1000177340110403E-5</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2.8830433758120402E-8</v>
+      </c>
       <c r="H94" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I94" t="e">
-        <f t="shared" ref="I94:I104" si="22">H94*((E94/D94)^2 +(G94/F94)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <v>0.9919963832194606</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="22"/>
+        <v>4.7845787199425399E-4</v>
       </c>
       <c r="J94" s="3"/>
       <c r="L94" s="2">
-        <v>7.9783288855483107E-6</v>
+        <v>1.5963437915775598E-5</v>
       </c>
       <c r="M94" s="2">
-        <v>8.0769164104274605E-10</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>1.39122184548795E-9</v>
+      </c>
+      <c r="N94" s="2">
+        <v>1.5817958052602401E-5</v>
+      </c>
+      <c r="O94" s="2">
+        <v>8.6283519166794296E-9</v>
+      </c>
       <c r="P94" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q94" t="e">
-        <f t="shared" ref="Q94:Q104" si="23">P94*((M94/L94)^2 +(O94/N94)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <v>0.99088668343618957</v>
+      </c>
+      <c r="Q94">
+        <f t="shared" si="23"/>
+        <v>5.4736218274390727E-4</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="2"/>
-      <c r="D95" s="2">
-        <v>6.1492338452019598E-5</v>
+      <c r="D95">
+        <v>6.1359823656618703E-4</v>
       </c>
       <c r="E95" s="2">
-        <v>5.9150812321793704E-9</v>
-      </c>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
+        <v>1.7277411502086099E-7</v>
+      </c>
+      <c r="F95">
+        <v>6.1055975015409498E-4</v>
+      </c>
+      <c r="G95" s="2">
+        <v>3.3461909743024802E-7</v>
+      </c>
       <c r="H95" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I95" t="e">
+        <v>0.99504808483626683</v>
+      </c>
+      <c r="I95">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>6.1310365380674501E-4</v>
       </c>
       <c r="J95" s="3"/>
-      <c r="L95" s="2">
-        <v>1.5963437915775598E-5</v>
+      <c r="L95">
+        <v>1.5929141384867101E-4</v>
       </c>
       <c r="M95" s="2">
-        <v>1.39122184548795E-9</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>4.3762693503452201E-8</v>
+      </c>
+      <c r="N95">
+        <v>1.5839837724063901E-4</v>
+      </c>
+      <c r="O95" s="2">
+        <v>9.7089667713491904E-8</v>
+      </c>
       <c r="P95" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q95" t="e">
+        <v>0.99439369275182399</v>
+      </c>
+      <c r="Q95">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>6.6793464964274413E-4</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="2"/>
       <c r="D96">
-        <v>6.1359823656618703E-4</v>
+        <v>1.5261889267198399E-3</v>
       </c>
       <c r="E96" s="2">
-        <v>1.7277411502086099E-7</v>
-      </c>
-      <c r="G96" s="2"/>
+        <v>1.14318268477437E-6</v>
+      </c>
+      <c r="F96">
+        <v>1.5176360020393699E-3</v>
+      </c>
+      <c r="G96" s="2">
+        <v>2.27044904094612E-6</v>
+      </c>
       <c r="H96" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I96" t="e">
+        <v>0.99439589389574967</v>
+      </c>
+      <c r="I96">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>1.6637085029707901E-3</v>
       </c>
       <c r="J96" s="3"/>
       <c r="L96">
-        <v>1.5929141384867101E-4</v>
+        <v>3.9601961871322503E-4</v>
       </c>
       <c r="M96" s="2">
-        <v>4.3762693503452201E-8</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>3.2948969998976799E-7</v>
+      </c>
+      <c r="N96">
+        <v>3.9349421991561798E-4</v>
+      </c>
+      <c r="O96" s="2">
+        <v>5.9433254474399601E-7</v>
+      </c>
       <c r="P96" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q96" t="e">
+        <v>0.99362304623742437</v>
+      </c>
+      <c r="Q96">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.713396075801996E-3</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="2"/>
       <c r="D97">
-        <v>1.5261889267198399E-3</v>
+        <v>3.0240386323727099E-3</v>
       </c>
       <c r="E97" s="2">
-        <v>1.14318268477437E-6</v>
-      </c>
-      <c r="G97" s="2"/>
+        <v>2.6402202836250101E-6</v>
+      </c>
+      <c r="F97">
+        <v>3.0107720026164402E-3</v>
+      </c>
+      <c r="G97" s="2">
+        <v>3.3765387186651799E-6</v>
+      </c>
       <c r="H97" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I97" t="e">
+        <v>0.99561294303113435</v>
+      </c>
+      <c r="I97">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>1.4150302261022782E-3</v>
       </c>
       <c r="J97" s="3"/>
       <c r="L97">
-        <v>3.9601961871322503E-4</v>
+        <v>7.8399076922384297E-4</v>
       </c>
       <c r="M97" s="2">
-        <v>3.2948969998976799E-7</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>5.9026868869718298E-7</v>
+      </c>
+      <c r="N97">
+        <v>7.80852204299984E-4</v>
+      </c>
+      <c r="O97" s="2">
+        <v>9.7406487421364095E-7</v>
+      </c>
       <c r="P97" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q97" t="e">
+        <v>0.99599668127857399</v>
+      </c>
+      <c r="Q97">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.4512066100184763E-3</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="2"/>
       <c r="D98">
-        <v>3.0240386323727099E-3</v>
+        <v>4.50679407740522E-3</v>
       </c>
       <c r="E98" s="2">
-        <v>2.6402202836250101E-6</v>
-      </c>
-      <c r="G98" s="2"/>
+        <v>4.2647960521843998E-6</v>
+      </c>
+      <c r="F98">
+        <v>4.4935620809677798E-3</v>
+      </c>
+      <c r="G98" s="2">
+        <v>3.6952965727364501E-6</v>
+      </c>
       <c r="H98" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I98" t="e">
+        <v>0.99706398912171768</v>
+      </c>
+      <c r="I98">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>1.2500160874864088E-3</v>
       </c>
       <c r="J98" s="3"/>
       <c r="L98">
-        <v>7.8399076922384297E-4</v>
+        <v>1.1685174391520899E-3</v>
       </c>
       <c r="M98" s="2">
-        <v>5.9026868869718298E-7</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>1.1542133311304201E-6</v>
+      </c>
+      <c r="N98">
+        <v>1.1646109982718701E-3</v>
+      </c>
+      <c r="O98" s="2">
+        <v>1.11497766509073E-6</v>
+      </c>
       <c r="P98" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q98" t="e">
+        <v>0.99665692547724882</v>
+      </c>
+      <c r="Q98">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.3709912639735175E-3</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="2"/>
       <c r="D99">
-        <v>4.50679407740522E-3</v>
+        <v>5.9662056707135503E-3</v>
       </c>
       <c r="E99" s="2">
-        <v>4.2647960521843998E-6</v>
-      </c>
-      <c r="G99" s="2"/>
+        <v>5.40641051549475E-6</v>
+      </c>
+      <c r="F99">
+        <v>5.9346035425855304E-3</v>
+      </c>
+      <c r="G99" s="2">
+        <v>5.5032901510436297E-6</v>
+      </c>
       <c r="H99" s="7">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I99" t="e">
+        <v>0.99470314469996468</v>
+      </c>
+      <c r="I99">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>1.2896950309998858E-3</v>
       </c>
       <c r="J99" s="3"/>
       <c r="L99">
-        <v>1.1685174391520899E-3</v>
+        <v>1.54673264952424E-3</v>
       </c>
       <c r="M99" s="2">
-        <v>1.1542133311304201E-6</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>1.51849573172552E-6</v>
+      </c>
+      <c r="N99">
+        <v>1.5382311816428799E-3</v>
+      </c>
+      <c r="O99" s="2">
+        <v>1.4500464744755799E-6</v>
+      </c>
       <c r="P99" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q99" t="e">
+        <v>0.9945035957675199</v>
+      </c>
+      <c r="Q99">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.353566839850045E-3</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="2"/>
       <c r="D100">
-        <v>5.9662056707135503E-3</v>
+        <v>8.7899155121648007E-3</v>
       </c>
       <c r="E100" s="2">
-        <v>5.40641051549475E-6</v>
-      </c>
-      <c r="G100" s="2"/>
+        <v>8.4141165447635294E-6</v>
+      </c>
       <c r="H100" s="7">
         <f t="shared" si="20"/>
         <v>0</v>
@@ -10808,32 +11158,37 @@
       </c>
       <c r="J100" s="3"/>
       <c r="L100">
-        <v>1.54673264952424E-3</v>
+        <v>2.2773061972286E-3</v>
       </c>
       <c r="M100" s="2">
-        <v>1.51849573172552E-6</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>1.8388961974808701E-6</v>
+      </c>
+      <c r="N100">
+        <v>2.2697569755679901E-3</v>
+      </c>
+      <c r="O100" s="2">
+        <v>2.1584319185391E-6</v>
+      </c>
       <c r="P100" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q100" t="e">
+        <v>0.99668502124580483</v>
+      </c>
+      <c r="Q100">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.2434009620595613E-3</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="2"/>
       <c r="D101">
-        <v>8.7899155121648007E-3</v>
+        <v>1.42163192656607E-2</v>
       </c>
       <c r="E101" s="2">
-        <v>8.4141165447635294E-6</v>
+        <v>1.2836259331731899E-5</v>
       </c>
       <c r="H101" s="7">
         <f t="shared" si="20"/>
@@ -10845,32 +11200,37 @@
       </c>
       <c r="J101" s="3"/>
       <c r="L101">
-        <v>2.2773061972286E-3</v>
+        <v>3.6770878239360399E-3</v>
       </c>
       <c r="M101" s="2">
-        <v>1.8388961974808701E-6</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>3.3129308552088702E-6</v>
+      </c>
+      <c r="N101">
+        <v>3.6628404748051801E-3</v>
+      </c>
+      <c r="O101" s="2">
+        <v>3.67639490119231E-6</v>
+      </c>
       <c r="P101" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q101" t="e">
+        <v>0.99612537154045744</v>
+      </c>
+      <c r="Q101">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.3435343559292461E-3</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="2"/>
       <c r="D102">
-        <v>1.42163192656607E-2</v>
+        <v>2.6357970030464899E-2</v>
       </c>
       <c r="E102" s="2">
-        <v>1.2836259331731899E-5</v>
+        <v>2.4421328068662499E-5</v>
       </c>
       <c r="H102" s="7">
         <f t="shared" si="20"/>
@@ -10882,32 +11242,36 @@
       </c>
       <c r="J102" s="3"/>
       <c r="L102">
-        <v>3.6770878239360399E-3</v>
+        <v>6.7939382709162497E-3</v>
       </c>
       <c r="M102" s="2">
-        <v>3.3129308552088702E-6</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>5.8793471054976199E-6</v>
+      </c>
+      <c r="N102">
+        <v>6.76993363102317E-3</v>
+      </c>
+      <c r="O102" s="2">
+        <v>6.0233973532027101E-6</v>
+      </c>
       <c r="P102" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q102" t="e">
+        <v>0.99646675625596426</v>
+      </c>
+      <c r="Q102">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.2367835060891773E-3</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="B103" s="4"/>
-      <c r="C103" s="2"/>
       <c r="D103">
-        <v>2.6357970030464899E-2</v>
+        <v>3.7020582201278698E-2</v>
       </c>
       <c r="E103" s="2">
-        <v>2.4421328068662499E-5</v>
+        <v>3.84860034148077E-5</v>
       </c>
       <c r="H103" s="7">
         <f t="shared" si="20"/>
@@ -10917,81 +11281,67 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J103" s="3"/>
+      <c r="J103" s="4"/>
       <c r="L103">
-        <v>6.7939382709162497E-3</v>
+        <v>9.5123806968783701E-3</v>
       </c>
       <c r="M103" s="2">
-        <v>5.8793471054976199E-6</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>7.1281968286277104E-6</v>
+      </c>
+      <c r="N103">
+        <v>9.4892912197387692E-3</v>
+      </c>
+      <c r="O103" s="2">
+        <v>8.32761033818195E-6</v>
+      </c>
       <c r="P103" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q103" t="e">
+        <v>0.99757269206570154</v>
+      </c>
+      <c r="Q103">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>1.151186180212625E-3</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>750</v>
+        <v>999.99</v>
       </c>
       <c r="B104" s="4"/>
-      <c r="H104" s="7" t="e">
+      <c r="D104">
+        <v>4.6422474047507503E-2</v>
+      </c>
+      <c r="E104" s="2">
+        <v>4.3252132292944603E-5</v>
+      </c>
+      <c r="H104" s="7">
         <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I104" t="e">
-        <f t="shared" si="22"/>
+        <f>H104*((E104/D104)^2 +(G104/F104)^2)^0.5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J104" s="4"/>
       <c r="L104">
-        <v>9.5123806968783701E-3</v>
+        <v>1.18865612101144E-2</v>
       </c>
       <c r="M104" s="2">
-        <v>7.1281968286277104E-6</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>1.1116236336809801E-5</v>
+      </c>
+      <c r="N104">
+        <v>1.1839679458885701E-2</v>
+      </c>
+      <c r="O104" s="2">
+        <v>1.4447158718593701E-5</v>
+      </c>
       <c r="P104" s="7">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q104" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>999.99</v>
-      </c>
-      <c r="B105" s="4"/>
-      <c r="H105" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I105" t="e">
-        <f>H105*((E105/D105)^2 +(G105/F105)^2)^0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J105" s="4"/>
-      <c r="L105">
-        <v>1.18865612101144E-2</v>
-      </c>
-      <c r="M105" s="2">
-        <v>1.1116236336809801E-5</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" s="7">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q105" t="e">
-        <f>P105*((M105/L105)^2 +(O105/N105)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <v>0.99605590293105062</v>
+      </c>
+      <c r="Q104">
+        <f>P104*((M104/L104)^2 +(O104/N104)^2)^0.5</f>
+        <v>1.5313218046202142E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-04-10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E75EC8-2429-4937-84C1-8F69EF79AD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97DF041-600A-46A8-9EE0-5D5D403F2AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -208,7 +208,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -240,37 +240,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -678,6 +648,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.69577799650043737"/>
+          <c:y val="0.59697852328854795"/>
+          <c:w val="0.24177734033245843"/>
+          <c:h val="7.9196805432479436E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6718,15 +6698,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>583097</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>484037</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>167641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>278297</xdr:colOff>
+      <xdr:colOff>179237</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>145775</xdr:rowOff>
+      <xdr:rowOff>130535</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
